--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9DE485-5C25-4596-8598-7226BD0393F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB6A5C-3513-4B56-9B33-8E979A674B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="450" windowWidth="25575" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1128,10 +1128,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チョコレッティ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>さくらの花びら</t>
     <rPh sb="4" eb="5">
       <t>ハナ</t>
@@ -2643,6 +2639,10 @@
   </si>
   <si>
     <t>キンキンの</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ショコラ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3102,7 +3102,7 @@
         <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -3150,13 +3150,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
         <v>290</v>
-      </c>
-      <c r="C5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D5" t="s">
-        <v>291</v>
       </c>
       <c r="E5">
         <v>20</v>
@@ -3204,13 +3204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" t="s">
         <v>357</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>358</v>
-      </c>
-      <c r="D7" t="s">
-        <v>359</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>207</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -3258,13 +3258,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" t="s">
         <v>360</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>361</v>
-      </c>
-      <c r="D9" t="s">
-        <v>362</v>
       </c>
       <c r="E9">
         <v>12</v>
@@ -3291,7 +3291,7 @@
         <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -3318,7 +3318,7 @@
         <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -3339,13 +3339,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D12" t="s">
         <v>285</v>
-      </c>
-      <c r="C12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D12" t="s">
-        <v>286</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -3354,7 +3354,7 @@
         <v>80</v>
       </c>
       <c r="G12">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -3366,13 +3366,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" t="s">
         <v>299</v>
       </c>
-      <c r="C13" t="s">
-        <v>300</v>
-      </c>
       <c r="D13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -3399,7 +3399,7 @@
         <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -3435,7 +3435,7 @@
         <v>50</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H15">
         <v>10</v>
@@ -3480,7 +3480,7 @@
         <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -3501,13 +3501,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" t="s">
         <v>363</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>364</v>
-      </c>
-      <c r="D18" t="s">
-        <v>365</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -3528,13 +3528,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" t="s">
         <v>366</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>367</v>
-      </c>
-      <c r="D19" t="s">
-        <v>368</v>
       </c>
       <c r="E19">
         <v>15</v>
@@ -3615,7 +3615,7 @@
         <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -3636,13 +3636,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" t="s">
         <v>369</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>370</v>
-      </c>
-      <c r="D23" t="s">
-        <v>371</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -3696,7 +3696,7 @@
         <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -3750,7 +3750,7 @@
         <v>134</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -3771,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>371</v>
+      </c>
+      <c r="C28" t="s">
         <v>372</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>373</v>
-      </c>
-      <c r="D28" t="s">
-        <v>374</v>
       </c>
       <c r="E28">
         <v>-2</v>
@@ -3798,13 +3798,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" t="s">
         <v>250</v>
       </c>
-      <c r="C29" t="s">
-        <v>251</v>
-      </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E29">
         <v>8</v>
@@ -3825,13 +3825,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>291</v>
+      </c>
+      <c r="C30" t="s">
         <v>292</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>293</v>
-      </c>
-      <c r="D30" t="s">
-        <v>294</v>
       </c>
       <c r="E30">
         <v>20</v>
@@ -3852,13 +3852,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
+        <v>374</v>
+      </c>
+      <c r="C31" t="s">
         <v>375</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>376</v>
-      </c>
-      <c r="D31" t="s">
-        <v>377</v>
       </c>
       <c r="E31">
         <v>20</v>
@@ -3879,13 +3879,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>377</v>
+      </c>
+      <c r="C32" t="s">
         <v>378</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>379</v>
-      </c>
-      <c r="D32" t="s">
-        <v>380</v>
       </c>
       <c r="E32">
         <v>20</v>
@@ -3906,13 +3906,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
+        <v>382</v>
+      </c>
+      <c r="C33" t="s">
         <v>383</v>
       </c>
-      <c r="C33" t="s">
-        <v>384</v>
-      </c>
       <c r="D33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E33">
         <v>8</v>
@@ -3933,13 +3933,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>380</v>
+      </c>
+      <c r="C34" t="s">
         <v>381</v>
       </c>
-      <c r="C34" t="s">
-        <v>382</v>
-      </c>
       <c r="D34" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3966,7 +3966,7 @@
         <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3987,13 +3987,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>384</v>
+      </c>
+      <c r="C36" t="s">
         <v>385</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>386</v>
-      </c>
-      <c r="D36" t="s">
-        <v>387</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -4014,13 +4014,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>286</v>
+      </c>
+      <c r="C37" t="s">
         <v>287</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>288</v>
-      </c>
-      <c r="D37" t="s">
-        <v>289</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -4245,7 +4245,7 @@
         <v>20</v>
       </c>
       <c r="G45">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -4272,7 +4272,7 @@
         <v>15</v>
       </c>
       <c r="G46">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -4284,13 +4284,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" t="s">
         <v>305</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>306</v>
-      </c>
-      <c r="D47" t="s">
-        <v>307</v>
       </c>
       <c r="E47">
         <v>10</v>
@@ -4299,7 +4299,7 @@
         <v>20</v>
       </c>
       <c r="G47">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -4311,13 +4311,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" t="s">
+        <v>273</v>
+      </c>
+      <c r="D48" t="s">
         <v>270</v>
-      </c>
-      <c r="C48" t="s">
-        <v>274</v>
-      </c>
-      <c r="D48" t="s">
-        <v>271</v>
       </c>
       <c r="E48">
         <v>15</v>
@@ -4326,7 +4326,7 @@
         <v>30</v>
       </c>
       <c r="G48">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -4338,13 +4338,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" t="s">
+        <v>274</v>
+      </c>
+      <c r="D49" t="s">
         <v>272</v>
-      </c>
-      <c r="C49" t="s">
-        <v>275</v>
-      </c>
-      <c r="D49" t="s">
-        <v>273</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -4353,7 +4353,7 @@
         <v>30</v>
       </c>
       <c r="G49">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -4398,7 +4398,7 @@
         <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E51">
         <v>15</v>
@@ -4422,10 +4422,10 @@
         <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -4452,7 +4452,7 @@
         <v>53</v>
       </c>
       <c r="D53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -4479,7 +4479,7 @@
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E54">
         <v>2</v>
@@ -4500,13 +4500,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>251</v>
+      </c>
+      <c r="C55" t="s">
+        <v>259</v>
+      </c>
+      <c r="D55" t="s">
         <v>252</v>
-      </c>
-      <c r="C55" t="s">
-        <v>260</v>
-      </c>
-      <c r="D55" t="s">
-        <v>253</v>
       </c>
       <c r="E55">
         <v>30</v>
@@ -4527,13 +4527,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
+        <v>254</v>
+      </c>
+      <c r="C56" t="s">
         <v>255</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>256</v>
-      </c>
-      <c r="D56" t="s">
-        <v>257</v>
       </c>
       <c r="E56">
         <v>20</v>
@@ -4554,13 +4554,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" t="s">
         <v>268</v>
       </c>
-      <c r="C57" t="s">
-        <v>269</v>
-      </c>
       <c r="D57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E57">
         <v>6</v>
@@ -4581,13 +4581,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" t="s">
         <v>279</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>280</v>
-      </c>
-      <c r="D58" t="s">
-        <v>281</v>
       </c>
       <c r="E58">
         <v>15</v>
@@ -4611,10 +4611,10 @@
         <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -4641,7 +4641,7 @@
         <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -4662,13 +4662,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>281</v>
+      </c>
+      <c r="C61" t="s">
         <v>282</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>283</v>
-      </c>
-      <c r="D61" t="s">
-        <v>284</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -5040,13 +5040,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
+        <v>260</v>
+      </c>
+      <c r="C75" t="s">
         <v>261</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>262</v>
-      </c>
-      <c r="D75" t="s">
-        <v>263</v>
       </c>
       <c r="E75">
         <v>10</v>
@@ -5067,13 +5067,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" t="s">
+        <v>294</v>
+      </c>
+      <c r="D76" t="s">
         <v>295</v>
-      </c>
-      <c r="D76" t="s">
-        <v>296</v>
       </c>
       <c r="E76">
         <v>10</v>
@@ -5094,13 +5094,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
+        <v>275</v>
+      </c>
+      <c r="C77" t="s">
         <v>276</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>277</v>
-      </c>
-      <c r="D77" t="s">
-        <v>278</v>
       </c>
       <c r="E77">
         <v>15</v>
@@ -5154,7 +5154,7 @@
         <v>140</v>
       </c>
       <c r="D79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E79">
         <v>5</v>
@@ -5175,13 +5175,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>428</v>
+      </c>
+      <c r="C80" t="s">
+        <v>427</v>
+      </c>
+      <c r="D80" t="s">
         <v>429</v>
-      </c>
-      <c r="C80" t="s">
-        <v>428</v>
-      </c>
-      <c r="D80" t="s">
-        <v>430</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -5202,13 +5202,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>321</v>
+      </c>
+      <c r="C81" t="s">
         <v>322</v>
       </c>
-      <c r="C81" t="s">
-        <v>323</v>
-      </c>
       <c r="D81" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E81">
         <v>12</v>
@@ -5445,13 +5445,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
+        <v>257</v>
+      </c>
+      <c r="C90" t="s">
         <v>258</v>
       </c>
-      <c r="C90" t="s">
-        <v>259</v>
-      </c>
       <c r="D90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E90">
         <v>30</v>
@@ -5532,7 +5532,7 @@
         <v>41</v>
       </c>
       <c r="D93" t="s">
-        <v>214</v>
+        <v>447</v>
       </c>
       <c r="E93">
         <v>15</v>
@@ -5541,7 +5541,7 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="H93">
         <v>12</v>
@@ -5556,10 +5556,10 @@
         <v>42</v>
       </c>
       <c r="C94" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D94" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E94">
         <v>5</v>
@@ -5568,7 +5568,7 @@
         <v>10</v>
       </c>
       <c r="G94">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H94">
         <v>3</v>
@@ -5622,7 +5622,7 @@
         <v>10</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H96">
         <v>5</v>
@@ -5640,7 +5640,7 @@
         <v>144</v>
       </c>
       <c r="D97" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E97">
         <v>8</v>
@@ -5649,7 +5649,7 @@
         <v>12</v>
       </c>
       <c r="G97">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H97">
         <v>7</v>
@@ -5664,10 +5664,10 @@
         <v>48</v>
       </c>
       <c r="C98" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D98" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E98">
         <v>5</v>
@@ -5676,7 +5676,7 @@
         <v>14</v>
       </c>
       <c r="G98">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H98">
         <v>6</v>
@@ -5691,10 +5691,10 @@
         <v>49</v>
       </c>
       <c r="C99" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D99" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E99">
         <v>5</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="G99">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H99">
         <v>5</v>
@@ -5718,10 +5718,10 @@
         <v>50</v>
       </c>
       <c r="C100" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D100" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E100">
         <v>5</v>
@@ -5730,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="G100">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H100">
         <v>5</v>
@@ -5748,7 +5748,7 @@
         <v>143</v>
       </c>
       <c r="D101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E101">
         <v>5</v>
@@ -5757,7 +5757,7 @@
         <v>5</v>
       </c>
       <c r="G101">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H101">
         <v>3</v>
@@ -5775,7 +5775,7 @@
         <v>151</v>
       </c>
       <c r="D102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E102">
         <v>6</v>
@@ -5802,7 +5802,7 @@
         <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -5829,7 +5829,7 @@
         <v>199</v>
       </c>
       <c r="D104" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E104">
         <v>8</v>
@@ -5856,7 +5856,7 @@
         <v>154</v>
       </c>
       <c r="D105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E105">
         <v>6</v>
@@ -5865,7 +5865,7 @@
         <v>35</v>
       </c>
       <c r="G105">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H105">
         <v>10</v>
@@ -5877,13 +5877,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
+        <v>393</v>
+      </c>
+      <c r="C106" t="s">
         <v>394</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>395</v>
-      </c>
-      <c r="D106" t="s">
-        <v>396</v>
       </c>
       <c r="E106">
         <v>6</v>
@@ -5931,13 +5931,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
+        <v>387</v>
+      </c>
+      <c r="C108" t="s">
         <v>388</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>389</v>
-      </c>
-      <c r="D108" t="s">
-        <v>390</v>
       </c>
       <c r="E108">
         <v>-30</v>
@@ -5958,13 +5958,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
+        <v>264</v>
+      </c>
+      <c r="C109" t="s">
+        <v>263</v>
+      </c>
+      <c r="D109" t="s">
         <v>265</v>
-      </c>
-      <c r="C109" t="s">
-        <v>264</v>
-      </c>
-      <c r="D109" t="s">
-        <v>266</v>
       </c>
       <c r="E109">
         <v>-20</v>
@@ -5973,7 +5973,7 @@
         <v>-10</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H109">
         <v>-10</v>
@@ -5985,13 +5985,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
+        <v>390</v>
+      </c>
+      <c r="C110" t="s">
         <v>391</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>392</v>
-      </c>
-      <c r="D110" t="s">
-        <v>393</v>
       </c>
       <c r="E110">
         <v>-20</v>
@@ -6000,7 +6000,7 @@
         <v>-10</v>
       </c>
       <c r="G110">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H110">
         <v>-10</v>
@@ -6039,14 +6039,14 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
+        <v>339</v>
+      </c>
+      <c r="C112" t="s">
         <v>340</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>341</v>
       </c>
-      <c r="D112" t="s">
-        <v>342</v>
-      </c>
       <c r="E112">
         <v>10</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>10</v>
       </c>
       <c r="G112">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H112">
         <v>3</v>
@@ -6066,13 +6066,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
+        <v>342</v>
+      </c>
+      <c r="C113" t="s">
         <v>343</v>
       </c>
-      <c r="C113" t="s">
-        <v>344</v>
-      </c>
       <c r="D113" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E113">
         <v>10</v>
@@ -6081,7 +6081,7 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H113">
         <v>3</v>
@@ -6093,14 +6093,14 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
+        <v>344</v>
+      </c>
+      <c r="C114" t="s">
         <v>345</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>346</v>
       </c>
-      <c r="D114" t="s">
-        <v>347</v>
-      </c>
       <c r="E114">
         <v>10</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>10</v>
       </c>
       <c r="G114">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H114">
         <v>3</v>
@@ -6120,13 +6120,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
+        <v>347</v>
+      </c>
+      <c r="C115" t="s">
         <v>348</v>
       </c>
-      <c r="C115" t="s">
-        <v>349</v>
-      </c>
       <c r="D115" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E115">
         <v>10</v>
@@ -6135,7 +6135,7 @@
         <v>10</v>
       </c>
       <c r="G115">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H115">
         <v>3</v>
@@ -6147,13 +6147,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
+        <v>349</v>
+      </c>
+      <c r="C116" t="s">
         <v>350</v>
       </c>
-      <c r="C116" t="s">
-        <v>351</v>
-      </c>
       <c r="D116" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E116">
         <v>10</v>
@@ -6162,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="G116">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -6174,13 +6174,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
+        <v>351</v>
+      </c>
+      <c r="C117" t="s">
         <v>352</v>
       </c>
-      <c r="C117" t="s">
-        <v>353</v>
-      </c>
       <c r="D117" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E117">
         <v>10</v>
@@ -6189,7 +6189,7 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -6201,14 +6201,14 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
+        <v>353</v>
+      </c>
+      <c r="C118" t="s">
         <v>354</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>355</v>
       </c>
-      <c r="D118" t="s">
-        <v>356</v>
-      </c>
       <c r="E118">
         <v>10</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>10</v>
       </c>
       <c r="G118">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="H118">
         <v>3</v>
@@ -6228,13 +6228,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C119" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D119" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E119">
         <v>-30</v>
@@ -6270,7 +6270,7 @@
         <v>5</v>
       </c>
       <c r="G120">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H120">
         <v>2</v>
@@ -6288,7 +6288,7 @@
         <v>141</v>
       </c>
       <c r="D121" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E121">
         <v>20</v>
@@ -6312,10 +6312,10 @@
         <v>107</v>
       </c>
       <c r="C122" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" t="s">
         <v>219</v>
-      </c>
-      <c r="D122" t="s">
-        <v>220</v>
       </c>
       <c r="E122">
         <v>-10</v>
@@ -6444,13 +6444,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C127" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D127" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E127">
         <v>5</v>
@@ -6459,7 +6459,7 @@
         <v>10</v>
       </c>
       <c r="G127">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H127">
         <v>10</v>
@@ -6471,13 +6471,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C128" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D128" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E128">
         <v>5</v>
@@ -6486,7 +6486,7 @@
         <v>15</v>
       </c>
       <c r="G128">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H128">
         <v>20</v>
@@ -6498,13 +6498,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
+        <v>308</v>
+      </c>
+      <c r="C129" t="s">
         <v>309</v>
       </c>
-      <c r="C129" t="s">
-        <v>310</v>
-      </c>
       <c r="D129" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E129">
         <v>5</v>
@@ -6513,7 +6513,7 @@
         <v>15</v>
       </c>
       <c r="G129">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H129">
         <v>20</v>
@@ -6525,13 +6525,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D130" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E130">
         <v>5</v>
@@ -6540,7 +6540,7 @@
         <v>15</v>
       </c>
       <c r="G130">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H130">
         <v>30</v>
@@ -6552,13 +6552,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C131" t="s">
+        <v>313</v>
+      </c>
+      <c r="D131" t="s">
         <v>314</v>
-      </c>
-      <c r="D131" t="s">
-        <v>315</v>
       </c>
       <c r="E131">
         <v>5</v>
@@ -6567,7 +6567,7 @@
         <v>15</v>
       </c>
       <c r="G131">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H131">
         <v>30</v>
@@ -6579,13 +6579,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
+        <v>326</v>
+      </c>
+      <c r="C132" t="s">
         <v>327</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>328</v>
-      </c>
-      <c r="D132" t="s">
-        <v>329</v>
       </c>
       <c r="E132">
         <v>5</v>
@@ -6594,7 +6594,7 @@
         <v>15</v>
       </c>
       <c r="G132">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H132">
         <v>30</v>
@@ -6606,13 +6606,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
+        <v>329</v>
+      </c>
+      <c r="C133" t="s">
+        <v>331</v>
+      </c>
+      <c r="D133" t="s">
         <v>330</v>
-      </c>
-      <c r="C133" t="s">
-        <v>332</v>
-      </c>
-      <c r="D133" t="s">
-        <v>331</v>
       </c>
       <c r="E133">
         <v>5</v>
@@ -6621,7 +6621,7 @@
         <v>15</v>
       </c>
       <c r="G133">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H133">
         <v>30</v>
@@ -6633,13 +6633,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
+        <v>332</v>
+      </c>
+      <c r="C134" t="s">
         <v>333</v>
       </c>
-      <c r="C134" t="s">
-        <v>334</v>
-      </c>
       <c r="D134" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E134">
         <v>5</v>
@@ -6648,7 +6648,7 @@
         <v>15</v>
       </c>
       <c r="G134">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H134">
         <v>30</v>
@@ -6660,13 +6660,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
+        <v>336</v>
+      </c>
+      <c r="C135" t="s">
         <v>337</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
         <v>338</v>
-      </c>
-      <c r="D135" t="s">
-        <v>339</v>
       </c>
       <c r="E135">
         <v>5</v>
@@ -6675,7 +6675,7 @@
         <v>15</v>
       </c>
       <c r="G135">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H135">
         <v>30</v>
@@ -6687,13 +6687,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
+        <v>315</v>
+      </c>
+      <c r="C136" t="s">
         <v>316</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
         <v>317</v>
-      </c>
-      <c r="D136" t="s">
-        <v>318</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -6702,7 +6702,7 @@
         <v>15</v>
       </c>
       <c r="G136">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H136">
         <v>50</v>
@@ -6714,13 +6714,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
+        <v>318</v>
+      </c>
+      <c r="C137" t="s">
         <v>319</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
         <v>320</v>
-      </c>
-      <c r="D137" t="s">
-        <v>321</v>
       </c>
       <c r="E137">
         <v>5</v>
@@ -6729,7 +6729,7 @@
         <v>15</v>
       </c>
       <c r="G137">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H137">
         <v>50</v>
@@ -6741,14 +6741,14 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
+        <v>430</v>
+      </c>
+      <c r="C138" t="s">
         <v>431</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>432</v>
       </c>
-      <c r="D138" t="s">
-        <v>433</v>
-      </c>
       <c r="E138">
         <v>5</v>
       </c>
@@ -6756,7 +6756,7 @@
         <v>10</v>
       </c>
       <c r="G138">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H138">
         <v>10</v>
@@ -6768,14 +6768,14 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
+        <v>436</v>
+      </c>
+      <c r="C139" t="s">
         <v>437</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>438</v>
       </c>
-      <c r="D139" t="s">
-        <v>439</v>
-      </c>
       <c r="E139">
         <v>5</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>10</v>
       </c>
       <c r="G139">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H139">
         <v>10</v>
@@ -6795,13 +6795,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
+        <v>398</v>
+      </c>
+      <c r="C140" t="s">
+        <v>400</v>
+      </c>
+      <c r="D140" t="s">
         <v>399</v>
-      </c>
-      <c r="C140" t="s">
-        <v>401</v>
-      </c>
-      <c r="D140" t="s">
-        <v>400</v>
       </c>
       <c r="E140">
         <v>5</v>
@@ -6822,13 +6822,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C141" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D141" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E141">
         <v>5</v>
@@ -6849,13 +6849,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
+        <v>402</v>
+      </c>
+      <c r="C142" t="s">
         <v>403</v>
       </c>
-      <c r="C142" t="s">
+      <c r="D142" t="s">
         <v>404</v>
-      </c>
-      <c r="D142" t="s">
-        <v>405</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -6876,13 +6876,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
+        <v>405</v>
+      </c>
+      <c r="C143" t="s">
         <v>406</v>
       </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
         <v>407</v>
-      </c>
-      <c r="D143" t="s">
-        <v>408</v>
       </c>
       <c r="E143">
         <v>5</v>
@@ -6903,13 +6903,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
+        <v>408</v>
+      </c>
+      <c r="C144" t="s">
         <v>409</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
         <v>410</v>
-      </c>
-      <c r="D144" t="s">
-        <v>411</v>
       </c>
       <c r="E144">
         <v>5</v>
@@ -6930,13 +6930,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
+        <v>412</v>
+      </c>
+      <c r="C145" t="s">
+        <v>416</v>
+      </c>
+      <c r="D145" t="s">
         <v>413</v>
-      </c>
-      <c r="C145" t="s">
-        <v>417</v>
-      </c>
-      <c r="D145" t="s">
-        <v>414</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -6957,13 +6957,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
+        <v>414</v>
+      </c>
+      <c r="C146" t="s">
         <v>415</v>
       </c>
-      <c r="C146" t="s">
-        <v>416</v>
-      </c>
       <c r="D146" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -6984,13 +6984,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
+        <v>418</v>
+      </c>
+      <c r="C147" t="s">
         <v>419</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>420</v>
-      </c>
-      <c r="D147" t="s">
-        <v>421</v>
       </c>
       <c r="E147">
         <v>5</v>
@@ -7011,13 +7011,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
+        <v>421</v>
+      </c>
+      <c r="C148" t="s">
         <v>422</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>423</v>
-      </c>
-      <c r="D148" t="s">
-        <v>424</v>
       </c>
       <c r="E148">
         <v>5</v>
@@ -7038,13 +7038,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
+        <v>424</v>
+      </c>
+      <c r="C149" t="s">
         <v>425</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>426</v>
-      </c>
-      <c r="D149" t="s">
-        <v>427</v>
       </c>
       <c r="E149">
         <v>-5</v>
@@ -7065,13 +7065,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
+        <v>433</v>
+      </c>
+      <c r="C150" t="s">
         <v>434</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>435</v>
-      </c>
-      <c r="D150" t="s">
-        <v>436</v>
       </c>
       <c r="E150">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB6A5C-3513-4B56-9B33-8E979A674B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B7858B-E21D-4B01-8DDC-D743679E9832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="451">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -2643,6 +2643,24 @@
   </si>
   <si>
     <t>ショコラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MermaidHarb</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほのかに甘い香り</t>
+    <rPh sb="4" eb="5">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マーメイド</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3026,7 +3044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3065,7 +3083,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A151" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A152" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -5958,25 +5976,25 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>448</v>
       </c>
       <c r="C109" t="s">
-        <v>263</v>
+        <v>450</v>
       </c>
       <c r="D109" t="s">
-        <v>265</v>
+        <v>449</v>
       </c>
       <c r="E109">
-        <v>-20</v>
+        <v>7</v>
       </c>
       <c r="F109">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G109">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H109">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -5985,13 +6003,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="C110" t="s">
-        <v>391</v>
+        <v>263</v>
       </c>
       <c r="D110" t="s">
-        <v>392</v>
+        <v>265</v>
       </c>
       <c r="E110">
         <v>-20</v>
@@ -6012,25 +6030,25 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="C111" t="s">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="D111" t="s">
-        <v>142</v>
+        <v>392</v>
       </c>
       <c r="E111">
-        <v>7</v>
+        <v>-20</v>
       </c>
       <c r="F111">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="G111">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H111">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
@@ -6039,25 +6057,25 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F112">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G112">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H112">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
@@ -6066,13 +6084,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C113" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D113" t="s">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="E113">
         <v>10</v>
@@ -6093,13 +6111,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D114" t="s">
-        <v>346</v>
+        <v>442</v>
       </c>
       <c r="E114">
         <v>10</v>
@@ -6120,13 +6138,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C115" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D115" t="s">
-        <v>443</v>
+        <v>346</v>
       </c>
       <c r="E115">
         <v>10</v>
@@ -6147,13 +6165,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D116" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E116">
         <v>10</v>
@@ -6162,7 +6180,7 @@
         <v>10</v>
       </c>
       <c r="G116">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H116">
         <v>3</v>
@@ -6174,13 +6192,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C117" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D117" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E117">
         <v>10</v>
@@ -6189,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -6201,13 +6219,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D118" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="E118">
         <v>10</v>
@@ -6228,25 +6246,25 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>396</v>
+        <v>353</v>
       </c>
       <c r="C119" t="s">
-        <v>439</v>
+        <v>354</v>
       </c>
       <c r="D119" t="s">
-        <v>446</v>
+        <v>355</v>
       </c>
       <c r="E119">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G119">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
@@ -6255,22 +6273,22 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>396</v>
       </c>
       <c r="C120" t="s">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="D120" t="s">
-        <v>78</v>
+        <v>446</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H120">
         <v>2</v>
@@ -6282,25 +6300,25 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C121" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="D121" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E121">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F121">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G121">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -6309,22 +6327,22 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C122" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E122">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="F122">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G122">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -6336,25 +6354,25 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="C123" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D123" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E123">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="F123">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G123">
         <v>150</v>
       </c>
       <c r="H123">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -6363,13 +6381,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C124" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D124" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -6390,22 +6408,22 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="C125" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="D125" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="E125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G125">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H125">
         <v>10</v>
@@ -6417,25 +6435,25 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C126" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D126" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E126">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F126">
+        <v>10</v>
+      </c>
+      <c r="G126">
         <v>30</v>
       </c>
-      <c r="G126">
-        <v>300</v>
-      </c>
       <c r="H126">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6444,25 +6462,25 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="C127" t="s">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="D127" t="s">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F127">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G127">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -6471,25 +6489,25 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D128" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E128">
         <v>5</v>
       </c>
       <c r="F128">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G128">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H128">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -6498,13 +6516,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C129" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D129" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E129">
         <v>5</v>
@@ -6525,13 +6543,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C130" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D130" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E130">
         <v>5</v>
@@ -6540,10 +6558,10 @@
         <v>15</v>
       </c>
       <c r="G130">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H130">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6552,13 +6570,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C131" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D131" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E131">
         <v>5</v>
@@ -6579,13 +6597,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C132" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D132" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E132">
         <v>5</v>
@@ -6606,13 +6624,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C133" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D133" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E133">
         <v>5</v>
@@ -6633,13 +6651,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C134" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D134" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E134">
         <v>5</v>
@@ -6648,7 +6666,7 @@
         <v>15</v>
       </c>
       <c r="G134">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H134">
         <v>30</v>
@@ -6660,13 +6678,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C135" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D135" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E135">
         <v>5</v>
@@ -6687,13 +6705,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C136" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D136" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -6702,10 +6720,10 @@
         <v>15</v>
       </c>
       <c r="G136">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H136">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -6714,13 +6732,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C137" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D137" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E137">
         <v>5</v>
@@ -6741,25 +6759,25 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>430</v>
+        <v>318</v>
       </c>
       <c r="C138" t="s">
-        <v>431</v>
+        <v>319</v>
       </c>
       <c r="D138" t="s">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="E138">
         <v>5</v>
       </c>
       <c r="F138">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G138">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H138">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -6768,13 +6786,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D139" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E139">
         <v>5</v>
@@ -6783,7 +6801,7 @@
         <v>10</v>
       </c>
       <c r="G139">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H139">
         <v>10</v>
@@ -6795,13 +6813,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C140" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="D140" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="E140">
         <v>5</v>
@@ -6810,7 +6828,7 @@
         <v>10</v>
       </c>
       <c r="G140">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H140">
         <v>10</v>
@@ -6822,13 +6840,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C141" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D141" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E141">
         <v>5</v>
@@ -6849,13 +6867,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C142" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -6876,13 +6894,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C143" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E143">
         <v>5</v>
@@ -6903,13 +6921,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C144" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E144">
         <v>5</v>
@@ -6930,13 +6948,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C145" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -6957,13 +6975,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C146" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D146" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -6984,13 +7002,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C147" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D147" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E147">
         <v>5</v>
@@ -7011,25 +7029,25 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C148" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D148" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G148">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H148">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -7038,25 +7056,25 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C149" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D149" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E149">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F149">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="G149">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H149">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7065,25 +7083,25 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C150" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D150" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E150">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F150">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="G150">
         <v>300</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7092,24 +7110,51 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="C151" t="s">
-        <v>86</v>
+        <v>434</v>
       </c>
       <c r="D151" t="s">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="E151">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="F151">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G151">
         <v>300</v>
       </c>
       <c r="H151">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A152">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="B152" t="s">
+        <v>85</v>
+      </c>
+      <c r="C152" t="s">
+        <v>86</v>
+      </c>
+      <c r="D152" t="s">
+        <v>87</v>
+      </c>
+      <c r="E152">
+        <v>150</v>
+      </c>
+      <c r="F152">
+        <v>100</v>
+      </c>
+      <c r="G152">
+        <v>300</v>
+      </c>
+      <c r="H152">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B7858B-E21D-4B01-8DDC-D743679E9832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ED9492-B7D3-42C0-ACE0-9079683814AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2925" yWindow="990" windowWidth="25560" windowHeight="14340" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55ED9492-B7D3-42C0-ACE0-9079683814AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B591DF12-E27F-4A0C-979A-01AC1DC733C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="990" windowWidth="25560" windowHeight="14340" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="457">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -2661,6 +2661,45 @@
   </si>
   <si>
     <t>マーメイド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mint_Concent</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>濃縮ミント</t>
+    <rPh sb="0" eb="2">
+      <t>ノウシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>深いミントの</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mermaid_Concent</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>濃縮マーメイド</t>
+    <rPh sb="0" eb="2">
+      <t>ノウシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ねっとり甘い香り</t>
+    <rPh sb="4" eb="5">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3044,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3083,7 +3122,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A152" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A154" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -6273,25 +6312,25 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>396</v>
+        <v>451</v>
       </c>
       <c r="C120" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="D120" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E120">
-        <v>-30</v>
+        <v>10</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G120">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
@@ -6300,25 +6339,25 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>76</v>
+        <v>454</v>
       </c>
       <c r="C121" t="s">
-        <v>77</v>
+        <v>455</v>
       </c>
       <c r="D121" t="s">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="F121">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G121">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H121">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -6327,25 +6366,25 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>106</v>
+        <v>396</v>
       </c>
       <c r="C122" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="D122" t="s">
-        <v>228</v>
+        <v>446</v>
       </c>
       <c r="E122">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="F122">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -6354,25 +6393,25 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C123" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="D123" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="E123">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="F123">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="G123">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -6381,25 +6420,25 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="C124" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="D124" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E124">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F124">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G124">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H124">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
@@ -6408,25 +6447,25 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="C125" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D125" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E125">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="F125">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G125">
         <v>150</v>
       </c>
       <c r="H125">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -6435,22 +6474,22 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="C126" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="D126" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="E126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G126">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H126">
         <v>10</v>
@@ -6462,25 +6501,25 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="C127" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D127" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="E127">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F127">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G127">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -6489,13 +6528,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>303</v>
+        <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>302</v>
+        <v>99</v>
       </c>
       <c r="D128" t="s">
-        <v>301</v>
+        <v>91</v>
       </c>
       <c r="E128">
         <v>5</v>
@@ -6504,7 +6543,7 @@
         <v>10</v>
       </c>
       <c r="G128">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H128">
         <v>10</v>
@@ -6516,25 +6555,25 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="C129" t="s">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="D129" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F129">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G129">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H129">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -6543,25 +6582,25 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C130" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D130" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E130">
         <v>5</v>
       </c>
       <c r="F130">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G130">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H130">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6570,13 +6609,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C131" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D131" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E131">
         <v>5</v>
@@ -6585,10 +6624,10 @@
         <v>15</v>
       </c>
       <c r="G131">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H131">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -6597,13 +6636,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C132" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D132" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E132">
         <v>5</v>
@@ -6612,10 +6651,10 @@
         <v>15</v>
       </c>
       <c r="G132">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H132">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -6624,13 +6663,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C133" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D133" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E133">
         <v>5</v>
@@ -6651,13 +6690,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C134" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D134" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="E134">
         <v>5</v>
@@ -6678,13 +6717,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C135" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D135" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="E135">
         <v>5</v>
@@ -6693,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="G135">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H135">
         <v>30</v>
@@ -6705,13 +6744,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C136" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D136" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -6720,7 +6759,7 @@
         <v>15</v>
       </c>
       <c r="G136">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H136">
         <v>30</v>
@@ -6732,13 +6771,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="C137" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="D137" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="E137">
         <v>5</v>
@@ -6747,10 +6786,10 @@
         <v>15</v>
       </c>
       <c r="G137">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H137">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -6759,13 +6798,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C138" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="D138" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="E138">
         <v>5</v>
@@ -6774,10 +6813,10 @@
         <v>15</v>
       </c>
       <c r="G138">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H138">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -6786,25 +6825,25 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>430</v>
+        <v>315</v>
       </c>
       <c r="C139" t="s">
-        <v>431</v>
+        <v>316</v>
       </c>
       <c r="D139" t="s">
-        <v>432</v>
+        <v>317</v>
       </c>
       <c r="E139">
         <v>5</v>
       </c>
       <c r="F139">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G139">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H139">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -6813,25 +6852,25 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>436</v>
+        <v>318</v>
       </c>
       <c r="C140" t="s">
-        <v>437</v>
+        <v>319</v>
       </c>
       <c r="D140" t="s">
-        <v>438</v>
+        <v>320</v>
       </c>
       <c r="E140">
         <v>5</v>
       </c>
       <c r="F140">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G140">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="H140">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
@@ -6840,13 +6879,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="C141" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="D141" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="E141">
         <v>5</v>
@@ -6855,7 +6894,7 @@
         <v>10</v>
       </c>
       <c r="G141">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H141">
         <v>10</v>
@@ -6867,13 +6906,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="C142" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="D142" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -6882,7 +6921,7 @@
         <v>10</v>
       </c>
       <c r="G142">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H142">
         <v>10</v>
@@ -6894,13 +6933,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C143" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E143">
         <v>5</v>
@@ -6921,13 +6960,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C144" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E144">
         <v>5</v>
@@ -6948,13 +6987,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C145" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D145" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -6975,13 +7014,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C146" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -7002,13 +7041,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C147" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D147" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E147">
         <v>5</v>
@@ -7029,13 +7068,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C148" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D148" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="E148">
         <v>5</v>
@@ -7056,25 +7095,25 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C149" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="D149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G149">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H149">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7083,19 +7122,19 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C150" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D150" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E150">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F150">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G150">
         <v>300</v>
@@ -7110,25 +7149,25 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C151" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D151" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G151">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H151">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7137,24 +7176,78 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>85</v>
+        <v>424</v>
       </c>
       <c r="C152" t="s">
-        <v>86</v>
+        <v>425</v>
       </c>
       <c r="D152" t="s">
-        <v>87</v>
+        <v>426</v>
       </c>
       <c r="E152">
-        <v>150</v>
+        <v>-5</v>
       </c>
       <c r="F152">
-        <v>100</v>
+        <v>-10</v>
       </c>
       <c r="G152">
         <v>300</v>
       </c>
       <c r="H152">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A153">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="B153" t="s">
+        <v>433</v>
+      </c>
+      <c r="C153" t="s">
+        <v>434</v>
+      </c>
+      <c r="D153" t="s">
+        <v>435</v>
+      </c>
+      <c r="E153">
+        <v>5</v>
+      </c>
+      <c r="F153">
+        <v>15</v>
+      </c>
+      <c r="G153">
+        <v>300</v>
+      </c>
+      <c r="H153">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A154">
+        <f t="shared" si="0"/>
+        <v>152</v>
+      </c>
+      <c r="B154" t="s">
+        <v>85</v>
+      </c>
+      <c r="C154" t="s">
+        <v>86</v>
+      </c>
+      <c r="D154" t="s">
+        <v>87</v>
+      </c>
+      <c r="E154">
+        <v>150</v>
+      </c>
+      <c r="F154">
+        <v>100</v>
+      </c>
+      <c r="G154">
+        <v>300</v>
+      </c>
+      <c r="H154">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B591DF12-E27F-4A0C-979A-01AC1DC733C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577BE309-AB63-401F-A85C-523A714EB026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3324,7 +3324,7 @@
         <v>361</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>15</v>
@@ -3405,7 +3405,7 @@
         <v>285</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>80</v>
@@ -3432,7 +3432,7 @@
         <v>233</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F13">
         <v>80</v>
@@ -3441,7 +3441,7 @@
         <v>500</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -3576,7 +3576,7 @@
         <v>30</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -3594,7 +3594,7 @@
         <v>367</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -3603,7 +3603,7 @@
         <v>30</v>
       </c>
       <c r="H19">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -3711,7 +3711,7 @@
         <v>90</v>
       </c>
       <c r="H23">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -3900,7 +3900,7 @@
         <v>250</v>
       </c>
       <c r="H30">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -3927,7 +3927,7 @@
         <v>250</v>
       </c>
       <c r="H31">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -4089,7 +4089,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -4710,7 +4710,7 @@
         <v>120</v>
       </c>
       <c r="H60">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
@@ -6600,7 +6600,7 @@
         <v>100</v>
       </c>
       <c r="H130">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6627,7 +6627,7 @@
         <v>250</v>
       </c>
       <c r="H131">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -6654,7 +6654,7 @@
         <v>250</v>
       </c>
       <c r="H132">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -6681,7 +6681,7 @@
         <v>350</v>
       </c>
       <c r="H133">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -6708,7 +6708,7 @@
         <v>350</v>
       </c>
       <c r="H134">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -6735,7 +6735,7 @@
         <v>350</v>
       </c>
       <c r="H135">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -6762,7 +6762,7 @@
         <v>350</v>
       </c>
       <c r="H136">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -6789,7 +6789,7 @@
         <v>400</v>
       </c>
       <c r="H137">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -6816,7 +6816,7 @@
         <v>400</v>
       </c>
       <c r="H138">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -6843,7 +6843,7 @@
         <v>750</v>
       </c>
       <c r="H139">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -6870,7 +6870,7 @@
         <v>750</v>
       </c>
       <c r="H140">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
@@ -6924,7 +6924,7 @@
         <v>1000</v>
       </c>
       <c r="H142">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -6951,7 +6951,7 @@
         <v>300</v>
       </c>
       <c r="H143">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -6978,7 +6978,7 @@
         <v>300</v>
       </c>
       <c r="H144">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7005,7 +7005,7 @@
         <v>300</v>
       </c>
       <c r="H145">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.4">
@@ -7113,7 +7113,7 @@
         <v>300</v>
       </c>
       <c r="H149">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577BE309-AB63-401F-A85C-523A714EB026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D4D60D-548B-4D5B-B71A-3E925E20AF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1845" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="460">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -2699,6 +2699,33 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>StarPowderGlow</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光る星たち</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光る星を散りばめた</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>チ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3083,7 +3110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3122,7 +3149,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A154" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A155" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -5313,25 +5340,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>457</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>458</v>
       </c>
       <c r="D83" t="s">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="E83">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F83">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G83">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H83">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5340,16 +5367,16 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="E84">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F84">
         <v>10</v>
@@ -5358,7 +5385,7 @@
         <v>240</v>
       </c>
       <c r="H84">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -5367,19 +5394,19 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C85" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E85">
         <v>20</v>
       </c>
       <c r="F85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G85">
         <v>240</v>
@@ -5394,13 +5421,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E86">
         <v>20</v>
@@ -5421,19 +5448,19 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E87">
         <v>20</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G87">
         <v>240</v>
@@ -5448,13 +5475,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="E88">
         <v>20</v>
@@ -5475,13 +5502,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -5502,19 +5529,19 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="C90" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="D90" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="E90">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F90">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G90">
         <v>240</v>
@@ -5529,19 +5556,19 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="C91" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="D91" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="E91">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F91">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G91">
         <v>240</v>
@@ -5556,25 +5583,25 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>211</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G92">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.4">
@@ -5583,25 +5610,25 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="D93" t="s">
-        <v>447</v>
+        <v>44</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F93">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G93">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="H93">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
@@ -5610,25 +5637,25 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C94" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
       <c r="D94" t="s">
-        <v>225</v>
+        <v>447</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F94">
         <v>10</v>
       </c>
       <c r="G94">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
@@ -5637,25 +5664,25 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C95" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="D95" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="E95">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F95">
         <v>10</v>
       </c>
       <c r="G95">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H95">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -5664,22 +5691,22 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D96" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F96">
         <v>10</v>
       </c>
       <c r="G96">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H96">
         <v>5</v>
@@ -5691,25 +5718,25 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D97" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="E97">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G97">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H97">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
@@ -5718,25 +5745,25 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C98" t="s">
-        <v>237</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="E98">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F98">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G98">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H98">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -5745,25 +5772,25 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D99" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E99">
         <v>5</v>
       </c>
       <c r="F99">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G99">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -5772,22 +5799,22 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C100" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D100" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E100">
         <v>5</v>
       </c>
       <c r="F100">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G100">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H100">
         <v>5</v>
@@ -5799,25 +5826,25 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="D101" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E101">
         <v>5</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G101">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
@@ -5826,25 +5853,25 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="C102" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D102" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F102">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G102">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H102">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
@@ -5853,25 +5880,25 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D103" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E103">
         <v>6</v>
       </c>
       <c r="F103">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G103">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H103">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
@@ -5880,16 +5907,16 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="C104" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="D104" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E104">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F104">
         <v>25</v>
@@ -5898,7 +5925,7 @@
         <v>350</v>
       </c>
       <c r="H104">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
@@ -5907,25 +5934,25 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="C105" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="D105" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E105">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F105">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G105">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H105">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
@@ -5934,13 +5961,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>394</v>
+        <v>154</v>
       </c>
       <c r="D106" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
       <c r="E106">
         <v>6</v>
@@ -5949,7 +5976,7 @@
         <v>35</v>
       </c>
       <c r="G106">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -5961,25 +5988,25 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>393</v>
       </c>
       <c r="C107" t="s">
-        <v>75</v>
+        <v>394</v>
       </c>
       <c r="D107" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="E107">
-        <v>-30</v>
+        <v>6</v>
       </c>
       <c r="F107">
-        <v>-5</v>
+        <v>35</v>
       </c>
       <c r="G107">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="H107">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -5988,13 +6015,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="D108" t="s">
-        <v>389</v>
+        <v>121</v>
       </c>
       <c r="E108">
         <v>-30</v>
@@ -6015,25 +6042,25 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>448</v>
+        <v>387</v>
       </c>
       <c r="C109" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="D109" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="E109">
-        <v>7</v>
+        <v>-30</v>
       </c>
       <c r="F109">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="G109">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H109">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -6042,25 +6069,25 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>264</v>
+        <v>448</v>
       </c>
       <c r="C110" t="s">
-        <v>263</v>
+        <v>450</v>
       </c>
       <c r="D110" t="s">
-        <v>265</v>
+        <v>449</v>
       </c>
       <c r="E110">
-        <v>-20</v>
+        <v>7</v>
       </c>
       <c r="F110">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G110">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H110">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
@@ -6069,13 +6096,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>391</v>
+        <v>263</v>
       </c>
       <c r="D111" t="s">
-        <v>392</v>
+        <v>265</v>
       </c>
       <c r="E111">
         <v>-20</v>
@@ -6096,25 +6123,25 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="C112" t="s">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="D112" t="s">
-        <v>142</v>
+        <v>392</v>
       </c>
       <c r="E112">
-        <v>7</v>
+        <v>-20</v>
       </c>
       <c r="F112">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="G112">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H112">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
@@ -6123,25 +6150,25 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="D113" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="E113">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F113">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G113">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
@@ -6150,13 +6177,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C114" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D114" t="s">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="E114">
         <v>10</v>
@@ -6177,13 +6204,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C115" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D115" t="s">
-        <v>346</v>
+        <v>442</v>
       </c>
       <c r="E115">
         <v>10</v>
@@ -6204,13 +6231,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C116" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D116" t="s">
-        <v>443</v>
+        <v>346</v>
       </c>
       <c r="E116">
         <v>10</v>
@@ -6231,13 +6258,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C117" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D117" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E117">
         <v>10</v>
@@ -6246,7 +6273,7 @@
         <v>10</v>
       </c>
       <c r="G117">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H117">
         <v>3</v>
@@ -6258,13 +6285,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E118">
         <v>10</v>
@@ -6273,7 +6300,7 @@
         <v>10</v>
       </c>
       <c r="G118">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H118">
         <v>3</v>
@@ -6285,13 +6312,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C119" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D119" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="E119">
         <v>10</v>
@@ -6312,13 +6339,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>451</v>
+        <v>353</v>
       </c>
       <c r="C120" t="s">
-        <v>452</v>
+        <v>354</v>
       </c>
       <c r="D120" t="s">
-        <v>453</v>
+        <v>355</v>
       </c>
       <c r="E120">
         <v>10</v>
@@ -6327,7 +6354,7 @@
         <v>10</v>
       </c>
       <c r="G120">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="H120">
         <v>3</v>
@@ -6339,22 +6366,22 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C121" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D121" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E121">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F121">
         <v>10</v>
       </c>
       <c r="G121">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H121">
         <v>3</v>
@@ -6366,25 +6393,25 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>396</v>
+        <v>454</v>
       </c>
       <c r="C122" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="D122" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="E122">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G122">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H122">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -6393,22 +6420,22 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>396</v>
       </c>
       <c r="C123" t="s">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="D123" t="s">
-        <v>78</v>
+        <v>446</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H123">
         <v>2</v>
@@ -6420,25 +6447,25 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C124" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="D124" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E124">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F124">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G124">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
@@ -6447,22 +6474,22 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="D125" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E125">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="F125">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G125">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -6474,25 +6501,25 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="C126" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D126" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E126">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="F126">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G126">
         <v>150</v>
       </c>
       <c r="H126">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6501,13 +6528,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C127" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D127" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E127">
         <v>3</v>
@@ -6528,22 +6555,22 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="C128" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="D128" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F128">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G128">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H128">
         <v>10</v>
@@ -6555,25 +6582,25 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C129" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D129" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E129">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F129">
+        <v>10</v>
+      </c>
+      <c r="G129">
         <v>30</v>
       </c>
-      <c r="G129">
-        <v>300</v>
-      </c>
       <c r="H129">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -6582,25 +6609,25 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="C130" t="s">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="D130" t="s">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E130">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F130">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G130">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H130">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6609,25 +6636,25 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C131" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D131" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E131">
         <v>5</v>
       </c>
       <c r="F131">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G131">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -6636,13 +6663,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C132" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D132" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E132">
         <v>5</v>
@@ -6663,13 +6690,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C133" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D133" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E133">
         <v>5</v>
@@ -6678,10 +6705,10 @@
         <v>15</v>
       </c>
       <c r="G133">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H133">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -6690,13 +6717,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C134" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D134" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E134">
         <v>5</v>
@@ -6717,13 +6744,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C135" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D135" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E135">
         <v>5</v>
@@ -6744,13 +6771,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C136" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D136" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E136">
         <v>5</v>
@@ -6771,13 +6798,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C137" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D137" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E137">
         <v>5</v>
@@ -6786,7 +6813,7 @@
         <v>15</v>
       </c>
       <c r="G137">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H137">
         <v>15</v>
@@ -6798,13 +6825,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C138" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D138" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E138">
         <v>5</v>
@@ -6825,13 +6852,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C139" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D139" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E139">
         <v>5</v>
@@ -6840,10 +6867,10 @@
         <v>15</v>
       </c>
       <c r="G139">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H139">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -6852,13 +6879,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C140" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D140" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E140">
         <v>5</v>
@@ -6879,25 +6906,25 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>430</v>
+        <v>318</v>
       </c>
       <c r="C141" t="s">
-        <v>431</v>
+        <v>319</v>
       </c>
       <c r="D141" t="s">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="E141">
         <v>5</v>
       </c>
       <c r="F141">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G141">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H141">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
@@ -6906,13 +6933,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C142" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D142" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -6921,10 +6948,10 @@
         <v>10</v>
       </c>
       <c r="G142">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H142">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -6933,13 +6960,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C143" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="D143" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="E143">
         <v>5</v>
@@ -6948,10 +6975,10 @@
         <v>10</v>
       </c>
       <c r="G143">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H143">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -6960,13 +6987,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C144" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E144">
         <v>5</v>
@@ -6978,7 +7005,7 @@
         <v>300</v>
       </c>
       <c r="H144">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -6987,13 +7014,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D145" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -7014,13 +7041,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C146" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -7032,7 +7059,7 @@
         <v>300</v>
       </c>
       <c r="H146">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.4">
@@ -7041,13 +7068,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C147" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E147">
         <v>5</v>
@@ -7068,13 +7095,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C148" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E148">
         <v>5</v>
@@ -7095,13 +7122,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C149" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E149">
         <v>5</v>
@@ -7113,7 +7140,7 @@
         <v>300</v>
       </c>
       <c r="H149">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7122,13 +7149,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C150" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D150" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E150">
         <v>5</v>
@@ -7140,7 +7167,7 @@
         <v>300</v>
       </c>
       <c r="H150">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7149,25 +7176,25 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C151" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D151" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G151">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H151">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7176,25 +7203,25 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C152" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D152" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E152">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F152">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="G152">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H152">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7203,25 +7230,25 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C153" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D153" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F153">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="G153">
         <v>300</v>
       </c>
       <c r="H153">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7230,24 +7257,51 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="C154" t="s">
-        <v>86</v>
+        <v>434</v>
       </c>
       <c r="D154" t="s">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="E154">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="F154">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G154">
         <v>300</v>
       </c>
       <c r="H154">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A155">
+        <f t="shared" si="0"/>
+        <v>153</v>
+      </c>
+      <c r="B155" t="s">
+        <v>85</v>
+      </c>
+      <c r="C155" t="s">
+        <v>86</v>
+      </c>
+      <c r="D155" t="s">
+        <v>87</v>
+      </c>
+      <c r="E155">
+        <v>150</v>
+      </c>
+      <c r="F155">
+        <v>100</v>
+      </c>
+      <c r="G155">
+        <v>300</v>
+      </c>
+      <c r="H155">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D4D60D-548B-4D5B-B71A-3E925E20AF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5143D677-CB97-4C47-92BC-3F03F1C7CD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2490" yWindow="1620" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="509">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -2726,6 +2726,298 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SodaSuger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュワシュワ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュワシュワソーダ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコの羽飾り</t>
+    <rPh sb="4" eb="5">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スタイリッシュ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateArc</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateArcGreen</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>和風の羽飾り</t>
+    <rPh sb="0" eb="2">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雅な</t>
+    <rPh sb="0" eb="1">
+      <t>ミヤビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateArcBlue</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>青色の羽飾り</t>
+    <rPh sb="0" eb="2">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>洗練された</t>
+    <rPh sb="0" eb="2">
+      <t>センレン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CandyArc</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャンディ羽飾り</t>
+    <rPh sb="5" eb="6">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャンディ飾りの</t>
+    <rPh sb="5" eb="6">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateMessage</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メッセージ入り</t>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GoldLeaf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>金箔</t>
+    <rPh sb="0" eb="2">
+      <t>キンパク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豪華な</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FreezedFlower</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フラワーアレンジ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>花びら舞い散る</t>
+    <rPh sb="0" eb="1">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FrozenRaspberry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>凍ったラズベリ</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラズベリーアクセント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FrozenRedberry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>凍ったいちご</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ストロベリーアクセント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FrozenBlueberry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>凍ったブルベリ</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブルーベリーアクセント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FrozenRainbowberry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>凍った七色</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ナナイロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レインボーアクセント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Doroflower</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>どろ花</t>
+    <rPh sb="2" eb="3">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>どろ花の</t>
+    <rPh sb="2" eb="3">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>WhipeedCreamMaron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マロンクリーム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マロンクリーム添え</t>
+    <rPh sb="7" eb="8">
+      <t>ソ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LittleMilkGlow</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>真珠色の光</t>
+    <rPh sb="0" eb="3">
+      <t>シンジュイロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まっしろに光る</t>
+    <rPh sb="5" eb="6">
+      <t>ヒカリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateBear</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>くまチョコ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>妹くまチョコ</t>
+    <rPh sb="0" eb="1">
+      <t>イモウト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateBearWhite</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白くまチョコ</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3110,7 +3402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3149,7 +3441,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A155" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A172" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -4233,25 +4525,25 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>495</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>496</v>
       </c>
       <c r="D42" t="s">
-        <v>20</v>
+        <v>497</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>-30</v>
       </c>
       <c r="F42">
-        <v>15</v>
+        <v>-30</v>
       </c>
       <c r="G42">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -4260,22 +4552,22 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -4287,22 +4579,22 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>8</v>
       </c>
       <c r="G44">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -4314,22 +4606,22 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45">
         <v>8</v>
       </c>
-      <c r="F45">
-        <v>20</v>
-      </c>
       <c r="G45">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -4341,19 +4633,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G46">
         <v>120</v>
@@ -4368,22 +4660,22 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>305</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="E47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G47">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -4395,22 +4687,22 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="C48" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G48">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -4422,13 +4714,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -4449,22 +4741,22 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>271</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>272</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -4476,25 +4768,25 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="D51" t="s">
-        <v>233</v>
+        <v>23</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>777</v>
+        <v>10</v>
       </c>
       <c r="H51">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
@@ -4503,25 +4795,25 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F52">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="G52">
-        <v>150</v>
+        <v>777</v>
       </c>
       <c r="H52">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
@@ -4530,25 +4822,25 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>229</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E53">
         <v>3</v>
       </c>
       <c r="F53">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G53">
         <v>150</v>
       </c>
       <c r="H53">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
@@ -4557,25 +4849,25 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G54">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
@@ -4584,25 +4876,25 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>251</v>
+        <v>460</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>461</v>
       </c>
       <c r="D55" t="s">
-        <v>252</v>
+        <v>462</v>
       </c>
       <c r="E55">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G55">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
@@ -4611,25 +4903,25 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>254</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>255</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="E56">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G56">
         <v>60</v>
       </c>
       <c r="H56">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
@@ -4638,25 +4930,25 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C57" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G57">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
@@ -4665,25 +4957,25 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="E58">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F58">
         <v>50</v>
       </c>
       <c r="G58">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -4692,16 +4984,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="C59" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -4719,25 +5011,25 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="D60" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F60">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="G60">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H60">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
@@ -4746,25 +5038,25 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="D61" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61">
         <v>3</v>
       </c>
-      <c r="F61">
-        <v>5</v>
-      </c>
       <c r="G61">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
@@ -4773,25 +5065,25 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="E62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G62">
         <v>120</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
@@ -4800,16 +5092,16 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>281</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>282</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>283</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -4818,7 +5110,7 @@
         <v>120</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
@@ -4827,25 +5119,25 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="E64">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G64">
         <v>120</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
@@ -4854,13 +5146,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="D65" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="E65">
         <v>10</v>
@@ -4881,25 +5173,25 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="E66">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G66">
         <v>120</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
@@ -4908,13 +5200,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E67">
         <v>10</v>
@@ -4935,13 +5227,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>147</v>
+        <v>70</v>
       </c>
       <c r="E68">
         <v>10</v>
@@ -4962,13 +5254,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>64</v>
       </c>
       <c r="C69" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="E69">
         <v>10</v>
@@ -4989,13 +5281,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="D70" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E70">
         <v>10</v>
@@ -5016,13 +5308,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D71" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E71">
         <v>10</v>
@@ -5043,13 +5335,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="D72" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="E72">
         <v>10</v>
@@ -5070,13 +5362,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="C73" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D73" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E73">
         <v>10</v>
@@ -5097,13 +5389,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="E74">
         <v>10</v>
@@ -5124,13 +5416,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="E75">
         <v>10</v>
@@ -5151,13 +5443,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>296</v>
+        <v>69</v>
       </c>
       <c r="C76" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="D76" t="s">
-        <v>295</v>
+        <v>148</v>
       </c>
       <c r="E76">
         <v>10</v>
@@ -5169,7 +5461,7 @@
         <v>120</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.4">
@@ -5178,19 +5470,19 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="D77" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E77">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F77">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G77">
         <v>120</v>
@@ -5205,22 +5497,22 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>296</v>
       </c>
       <c r="C78" t="s">
-        <v>58</v>
+        <v>294</v>
       </c>
       <c r="D78" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="E78">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -5232,25 +5524,25 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="C79" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="D79" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="E79">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F79">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G79">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
@@ -5259,25 +5551,25 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>428</v>
+        <v>498</v>
       </c>
       <c r="C80" t="s">
-        <v>427</v>
+        <v>499</v>
       </c>
       <c r="D80" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F80">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G80">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.4">
@@ -5286,19 +5578,19 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="C81" t="s">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D81" t="s">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="E81">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F81">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G81">
         <v>50</v>
@@ -5313,25 +5605,25 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="D82" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="E82">
         <v>5</v>
       </c>
       <c r="F82">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G82">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H82">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.4">
@@ -5340,25 +5632,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="C83" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="D83" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="E83">
         <v>5</v>
       </c>
       <c r="F83">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G83">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H83">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5367,25 +5659,25 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>321</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F84">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G84">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="H84">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -5394,25 +5686,25 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D85" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="E85">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F85">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G85">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H85">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.4">
@@ -5421,25 +5713,25 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>172</v>
+        <v>457</v>
       </c>
       <c r="C86" t="s">
-        <v>176</v>
+        <v>458</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>459</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F86">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G86">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H86">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.4">
@@ -5448,25 +5740,25 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="D87" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F87">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>240</v>
       </c>
       <c r="H87">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.4">
@@ -5475,13 +5767,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C88" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D88" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E88">
         <v>20</v>
@@ -5502,19 +5794,19 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D89" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E89">
         <v>20</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G89">
         <v>240</v>
@@ -5529,19 +5821,19 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="C90" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="D90" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="E90">
         <v>20</v>
       </c>
       <c r="F90">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G90">
         <v>240</v>
@@ -5556,19 +5848,19 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s">
-        <v>258</v>
+        <v>178</v>
       </c>
       <c r="D91" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="E91">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F91">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G91">
         <v>240</v>
@@ -5583,19 +5875,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C92" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D92" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E92">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F92">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G92">
         <v>240</v>
@@ -5610,25 +5902,25 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="E93">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G93">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="H93">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
@@ -5637,25 +5929,25 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="C94" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="D94" t="s">
-        <v>447</v>
+        <v>258</v>
       </c>
       <c r="E94">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G94">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="H94">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
@@ -5664,25 +5956,25 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="D95" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F95">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G95">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -5691,25 +5983,25 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="C96" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E96">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="F96">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G96">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H96">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
@@ -5718,25 +6010,25 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C97" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="D97" t="s">
-        <v>46</v>
+        <v>447</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F97">
         <v>10</v>
       </c>
       <c r="G97">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="H97">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
@@ -5745,25 +6037,25 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>47</v>
+        <v>465</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>463</v>
       </c>
       <c r="D98" t="s">
-        <v>230</v>
+        <v>464</v>
       </c>
       <c r="E98">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F98">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G98">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="H98">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -5772,25 +6064,25 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>48</v>
+        <v>466</v>
       </c>
       <c r="C99" t="s">
-        <v>237</v>
+        <v>467</v>
       </c>
       <c r="D99" t="s">
-        <v>253</v>
+        <v>468</v>
       </c>
       <c r="E99">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F99">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G99">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="H99">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -5799,25 +6091,25 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
+        <v>469</v>
       </c>
       <c r="C100" t="s">
-        <v>236</v>
+        <v>470</v>
       </c>
       <c r="D100" t="s">
-        <v>235</v>
+        <v>471</v>
       </c>
       <c r="E100">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F100">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G100">
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="H100">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -5826,25 +6118,25 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>50</v>
+        <v>472</v>
       </c>
       <c r="C101" t="s">
-        <v>234</v>
+        <v>473</v>
       </c>
       <c r="D101" t="s">
-        <v>231</v>
+        <v>474</v>
       </c>
       <c r="E101">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G101">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
@@ -5853,25 +6145,25 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>475</v>
       </c>
       <c r="C102" t="s">
-        <v>143</v>
+        <v>476</v>
       </c>
       <c r="D102" t="s">
-        <v>215</v>
+        <v>476</v>
       </c>
       <c r="E102">
         <v>5</v>
       </c>
       <c r="F102">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G102">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
@@ -5880,25 +6172,25 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>504</v>
       </c>
       <c r="C103" t="s">
-        <v>151</v>
+        <v>505</v>
       </c>
       <c r="D103" t="s">
-        <v>216</v>
+        <v>505</v>
       </c>
       <c r="E103">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F103">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G103">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H103">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
@@ -5907,22 +6199,22 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>507</v>
       </c>
       <c r="C104" t="s">
-        <v>152</v>
+        <v>508</v>
       </c>
       <c r="D104" t="s">
-        <v>226</v>
+        <v>506</v>
       </c>
       <c r="E104">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F104">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G104">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H104">
         <v>12</v>
@@ -5934,25 +6226,25 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>198</v>
+        <v>477</v>
       </c>
       <c r="C105" t="s">
-        <v>199</v>
+        <v>478</v>
       </c>
       <c r="D105" t="s">
-        <v>227</v>
+        <v>479</v>
       </c>
       <c r="E105">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F105">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G105">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="H105">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
@@ -5961,25 +6253,25 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>42</v>
       </c>
       <c r="C106" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="D106" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E106">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F106">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G106">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="H106">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
@@ -5988,25 +6280,25 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>393</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>394</v>
+        <v>89</v>
       </c>
       <c r="D107" t="s">
-        <v>395</v>
+        <v>89</v>
       </c>
       <c r="E107">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="F107">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G107">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H107">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -6015,25 +6307,25 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C108" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D108" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E108">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="F108">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="G108">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H108">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.4">
@@ -6042,25 +6334,25 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>387</v>
+        <v>47</v>
       </c>
       <c r="C109" t="s">
-        <v>388</v>
+        <v>144</v>
       </c>
       <c r="D109" t="s">
-        <v>389</v>
+        <v>230</v>
       </c>
       <c r="E109">
-        <v>-30</v>
+        <v>8</v>
       </c>
       <c r="F109">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="G109">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H109">
-        <v>-10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -6069,25 +6361,25 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>448</v>
+        <v>48</v>
       </c>
       <c r="C110" t="s">
-        <v>450</v>
+        <v>237</v>
       </c>
       <c r="D110" t="s">
-        <v>449</v>
+        <v>253</v>
       </c>
       <c r="E110">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F110">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G110">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H110">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
@@ -6096,25 +6388,25 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>49</v>
       </c>
       <c r="C111" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="D111" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="E111">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="F111">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="G111">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H111">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
@@ -6123,25 +6415,25 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>391</v>
+        <v>234</v>
       </c>
       <c r="D112" t="s">
-        <v>392</v>
+        <v>231</v>
       </c>
       <c r="E112">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="F112">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="G112">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H112">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
@@ -6150,25 +6442,25 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C113" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="E113">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F113">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G113">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H113">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
@@ -6177,25 +6469,25 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>339</v>
+        <v>150</v>
       </c>
       <c r="C114" t="s">
-        <v>340</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>341</v>
+        <v>216</v>
       </c>
       <c r="E114">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F114">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G114">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H114">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
@@ -6204,25 +6496,25 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>342</v>
+        <v>153</v>
       </c>
       <c r="C115" t="s">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="D115" t="s">
-        <v>442</v>
+        <v>226</v>
       </c>
       <c r="E115">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F115">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G115">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H115">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
@@ -6231,25 +6523,25 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>344</v>
+        <v>198</v>
       </c>
       <c r="C116" t="s">
-        <v>345</v>
+        <v>199</v>
       </c>
       <c r="D116" t="s">
-        <v>346</v>
+        <v>227</v>
       </c>
       <c r="E116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F116">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G116">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H116">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
@@ -6258,25 +6550,25 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>347</v>
+        <v>155</v>
       </c>
       <c r="C117" t="s">
-        <v>348</v>
+        <v>154</v>
       </c>
       <c r="D117" t="s">
-        <v>443</v>
+        <v>217</v>
       </c>
       <c r="E117">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F117">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G117">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
@@ -6285,25 +6577,25 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="C118" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="D118" t="s">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="E118">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F118">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G118">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H118">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
@@ -6312,25 +6604,25 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>351</v>
+        <v>74</v>
       </c>
       <c r="C119" t="s">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="D119" t="s">
-        <v>444</v>
+        <v>121</v>
       </c>
       <c r="E119">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="F119">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="G119">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
@@ -6339,25 +6631,25 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="C120" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="D120" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="E120">
-        <v>10</v>
+        <v>-30</v>
       </c>
       <c r="F120">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="G120">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="H120">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
@@ -6366,25 +6658,25 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C121" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D121" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E121">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F121">
         <v>10</v>
       </c>
       <c r="G121">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H121">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -6393,25 +6685,25 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>454</v>
+        <v>264</v>
       </c>
       <c r="C122" t="s">
-        <v>455</v>
+        <v>263</v>
       </c>
       <c r="D122" t="s">
-        <v>456</v>
+        <v>265</v>
       </c>
       <c r="E122">
+        <v>-20</v>
+      </c>
+      <c r="F122">
         <v>-10</v>
       </c>
-      <c r="F122">
-        <v>10</v>
-      </c>
       <c r="G122">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H122">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -6420,25 +6712,25 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C123" t="s">
-        <v>439</v>
+        <v>391</v>
       </c>
       <c r="D123" t="s">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="E123">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G123">
         <v>100</v>
       </c>
       <c r="H123">
-        <v>2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -6447,25 +6739,25 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D124" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G124">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H124">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
@@ -6474,25 +6766,25 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>339</v>
       </c>
       <c r="C125" t="s">
-        <v>141</v>
+        <v>340</v>
       </c>
       <c r="D125" t="s">
-        <v>228</v>
+        <v>341</v>
       </c>
       <c r="E125">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F125">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G125">
         <v>300</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -6501,25 +6793,25 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="C126" t="s">
-        <v>218</v>
+        <v>343</v>
       </c>
       <c r="D126" t="s">
-        <v>219</v>
+        <v>442</v>
       </c>
       <c r="E126">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="F126">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G126">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6528,25 +6820,25 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>183</v>
+        <v>344</v>
       </c>
       <c r="C127" t="s">
-        <v>184</v>
+        <v>345</v>
       </c>
       <c r="D127" t="s">
-        <v>185</v>
+        <v>346</v>
       </c>
       <c r="E127">
+        <v>10</v>
+      </c>
+      <c r="F127">
+        <v>10</v>
+      </c>
+      <c r="G127">
+        <v>300</v>
+      </c>
+      <c r="H127">
         <v>3</v>
-      </c>
-      <c r="F127">
-        <v>20</v>
-      </c>
-      <c r="G127">
-        <v>150</v>
-      </c>
-      <c r="H127">
-        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -6555,25 +6847,25 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>186</v>
+        <v>347</v>
       </c>
       <c r="C128" t="s">
-        <v>187</v>
+        <v>348</v>
       </c>
       <c r="D128" t="s">
-        <v>188</v>
+        <v>443</v>
       </c>
       <c r="E128">
+        <v>10</v>
+      </c>
+      <c r="F128">
+        <v>10</v>
+      </c>
+      <c r="G128">
+        <v>300</v>
+      </c>
+      <c r="H128">
         <v>3</v>
-      </c>
-      <c r="F128">
-        <v>20</v>
-      </c>
-      <c r="G128">
-        <v>150</v>
-      </c>
-      <c r="H128">
-        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -6582,25 +6874,25 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>349</v>
       </c>
       <c r="C129" t="s">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="D129" t="s">
-        <v>91</v>
+        <v>445</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F129">
         <v>10</v>
       </c>
       <c r="G129">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="H129">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -6609,25 +6901,25 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="C130" t="s">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="D130" t="s">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="E130">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F130">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G130">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6636,25 +6928,25 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="C131" t="s">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="D131" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="E131">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F131">
         <v>10</v>
       </c>
       <c r="G131">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H131">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -6663,25 +6955,25 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>307</v>
+        <v>451</v>
       </c>
       <c r="C132" t="s">
-        <v>310</v>
+        <v>452</v>
       </c>
       <c r="D132" t="s">
-        <v>334</v>
+        <v>453</v>
       </c>
       <c r="E132">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F132">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G132">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -6690,25 +6982,25 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C133" t="s">
-        <v>309</v>
+        <v>455</v>
       </c>
       <c r="D133" t="s">
-        <v>311</v>
+        <v>456</v>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="F133">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G133">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="H133">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -6717,25 +7009,25 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>312</v>
+        <v>396</v>
       </c>
       <c r="C134" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
       <c r="D134" t="s">
-        <v>324</v>
+        <v>446</v>
       </c>
       <c r="E134">
-        <v>5</v>
+        <v>-30</v>
       </c>
       <c r="F134">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G134">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="H134">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -6744,25 +7036,25 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>323</v>
+        <v>76</v>
       </c>
       <c r="C135" t="s">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="D135" t="s">
-        <v>314</v>
+        <v>78</v>
       </c>
       <c r="E135">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F135">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G135">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="H135">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -6771,25 +7063,25 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>326</v>
+        <v>106</v>
       </c>
       <c r="C136" t="s">
-        <v>327</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
-        <v>328</v>
+        <v>228</v>
       </c>
       <c r="E136">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F136">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G136">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H136">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -6798,25 +7090,25 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="C137" t="s">
-        <v>331</v>
+        <v>218</v>
       </c>
       <c r="D137" t="s">
-        <v>330</v>
+        <v>219</v>
       </c>
       <c r="E137">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="F137">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="G137">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H137">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -6825,25 +7117,25 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>332</v>
+        <v>183</v>
       </c>
       <c r="C138" t="s">
-        <v>333</v>
+        <v>184</v>
       </c>
       <c r="D138" t="s">
-        <v>335</v>
+        <v>185</v>
       </c>
       <c r="E138">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F138">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G138">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H138">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -6852,25 +7144,25 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>336</v>
+        <v>186</v>
       </c>
       <c r="C139" t="s">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="D139" t="s">
-        <v>338</v>
+        <v>188</v>
       </c>
       <c r="E139">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F139">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G139">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H139">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -6879,25 +7171,25 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>315</v>
+        <v>90</v>
       </c>
       <c r="C140" t="s">
-        <v>316</v>
+        <v>99</v>
       </c>
       <c r="D140" t="s">
-        <v>317</v>
+        <v>91</v>
       </c>
       <c r="E140">
         <v>5</v>
       </c>
       <c r="F140">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G140">
-        <v>750</v>
+        <v>30</v>
       </c>
       <c r="H140">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
@@ -6906,25 +7198,25 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="C141" t="s">
-        <v>319</v>
+        <v>84</v>
       </c>
       <c r="D141" t="s">
-        <v>320</v>
+        <v>84</v>
       </c>
       <c r="E141">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F141">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G141">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="H141">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
@@ -6933,13 +7225,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>430</v>
+        <v>303</v>
       </c>
       <c r="C142" t="s">
-        <v>431</v>
+        <v>302</v>
       </c>
       <c r="D142" t="s">
-        <v>432</v>
+        <v>301</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -6948,10 +7240,10 @@
         <v>10</v>
       </c>
       <c r="G142">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H142">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -6960,25 +7252,25 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="C143" t="s">
-        <v>437</v>
+        <v>310</v>
       </c>
       <c r="D143" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="E143">
         <v>5</v>
       </c>
       <c r="F143">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G143">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="H143">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -6987,25 +7279,25 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>398</v>
+        <v>308</v>
       </c>
       <c r="C144" t="s">
-        <v>400</v>
+        <v>309</v>
       </c>
       <c r="D144" t="s">
-        <v>399</v>
+        <v>311</v>
       </c>
       <c r="E144">
         <v>5</v>
       </c>
       <c r="F144">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G144">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H144">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7014,25 +7306,25 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>312</v>
       </c>
       <c r="C145" t="s">
-        <v>401</v>
+        <v>325</v>
       </c>
       <c r="D145" t="s">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="E145">
         <v>5</v>
       </c>
       <c r="F145">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G145">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H145">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.4">
@@ -7041,25 +7333,25 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>403</v>
+        <v>313</v>
       </c>
       <c r="D146" t="s">
-        <v>404</v>
+        <v>314</v>
       </c>
       <c r="E146">
         <v>5</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G146">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H146">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.4">
@@ -7068,25 +7360,25 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>405</v>
+        <v>326</v>
       </c>
       <c r="C147" t="s">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="D147" t="s">
-        <v>407</v>
+        <v>328</v>
       </c>
       <c r="E147">
         <v>5</v>
       </c>
       <c r="F147">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G147">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H147">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.4">
@@ -7095,25 +7387,25 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>408</v>
+        <v>329</v>
       </c>
       <c r="C148" t="s">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="E148">
         <v>5</v>
       </c>
       <c r="F148">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G148">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H148">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -7122,25 +7414,25 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>412</v>
+        <v>332</v>
       </c>
       <c r="C149" t="s">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>335</v>
       </c>
       <c r="E149">
         <v>5</v>
       </c>
       <c r="F149">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G149">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H149">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7149,25 +7441,25 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="C150" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>338</v>
       </c>
       <c r="E150">
         <v>5</v>
       </c>
       <c r="F150">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G150">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H150">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7176,25 +7468,25 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>418</v>
+        <v>501</v>
       </c>
       <c r="C151" t="s">
-        <v>419</v>
+        <v>502</v>
       </c>
       <c r="D151" t="s">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="E151">
         <v>5</v>
       </c>
       <c r="F151">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G151">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H151">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7203,22 +7495,22 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>421</v>
+        <v>315</v>
       </c>
       <c r="C152" t="s">
-        <v>422</v>
+        <v>316</v>
       </c>
       <c r="D152" t="s">
-        <v>423</v>
+        <v>317</v>
       </c>
       <c r="E152">
         <v>5</v>
       </c>
       <c r="F152">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G152">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="H152">
         <v>20</v>
@@ -7230,25 +7522,25 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>424</v>
+        <v>318</v>
       </c>
       <c r="C153" t="s">
-        <v>425</v>
+        <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>426</v>
+        <v>320</v>
       </c>
       <c r="E153">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F153">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="G153">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H153">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7257,25 +7549,25 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C154" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D154" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E154">
         <v>5</v>
       </c>
       <c r="F154">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G154">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H154">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7284,24 +7576,483 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
+        <v>436</v>
+      </c>
+      <c r="C155" t="s">
+        <v>437</v>
+      </c>
+      <c r="D155" t="s">
+        <v>438</v>
+      </c>
+      <c r="E155">
+        <v>5</v>
+      </c>
+      <c r="F155">
+        <v>10</v>
+      </c>
+      <c r="G155">
+        <v>1000</v>
+      </c>
+      <c r="H155">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A156">
+        <f t="shared" si="0"/>
+        <v>154</v>
+      </c>
+      <c r="B156" t="s">
+        <v>398</v>
+      </c>
+      <c r="C156" t="s">
+        <v>400</v>
+      </c>
+      <c r="D156" t="s">
+        <v>399</v>
+      </c>
+      <c r="E156">
+        <v>5</v>
+      </c>
+      <c r="F156">
+        <v>10</v>
+      </c>
+      <c r="G156">
+        <v>300</v>
+      </c>
+      <c r="H156">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A157">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="B157" t="s">
+        <v>397</v>
+      </c>
+      <c r="C157" t="s">
+        <v>401</v>
+      </c>
+      <c r="D157" t="s">
+        <v>411</v>
+      </c>
+      <c r="E157">
+        <v>5</v>
+      </c>
+      <c r="F157">
+        <v>10</v>
+      </c>
+      <c r="G157">
+        <v>300</v>
+      </c>
+      <c r="H157">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A158">
+        <f t="shared" si="0"/>
+        <v>156</v>
+      </c>
+      <c r="B158" t="s">
+        <v>402</v>
+      </c>
+      <c r="C158" t="s">
+        <v>403</v>
+      </c>
+      <c r="D158" t="s">
+        <v>404</v>
+      </c>
+      <c r="E158">
+        <v>5</v>
+      </c>
+      <c r="F158">
+        <v>10</v>
+      </c>
+      <c r="G158">
+        <v>300</v>
+      </c>
+      <c r="H158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A159">
+        <f t="shared" si="0"/>
+        <v>157</v>
+      </c>
+      <c r="B159" t="s">
+        <v>405</v>
+      </c>
+      <c r="C159" t="s">
+        <v>406</v>
+      </c>
+      <c r="D159" t="s">
+        <v>407</v>
+      </c>
+      <c r="E159">
+        <v>5</v>
+      </c>
+      <c r="F159">
+        <v>10</v>
+      </c>
+      <c r="G159">
+        <v>300</v>
+      </c>
+      <c r="H159">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A160">
+        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+      <c r="B160" t="s">
+        <v>408</v>
+      </c>
+      <c r="C160" t="s">
+        <v>409</v>
+      </c>
+      <c r="D160" t="s">
+        <v>410</v>
+      </c>
+      <c r="E160">
+        <v>5</v>
+      </c>
+      <c r="F160">
+        <v>10</v>
+      </c>
+      <c r="G160">
+        <v>300</v>
+      </c>
+      <c r="H160">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A161">
+        <f t="shared" si="0"/>
+        <v>159</v>
+      </c>
+      <c r="B161" t="s">
+        <v>412</v>
+      </c>
+      <c r="C161" t="s">
+        <v>416</v>
+      </c>
+      <c r="D161" t="s">
+        <v>413</v>
+      </c>
+      <c r="E161">
+        <v>5</v>
+      </c>
+      <c r="F161">
+        <v>10</v>
+      </c>
+      <c r="G161">
+        <v>300</v>
+      </c>
+      <c r="H161">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A162">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="B162" t="s">
+        <v>414</v>
+      </c>
+      <c r="C162" t="s">
+        <v>415</v>
+      </c>
+      <c r="D162" t="s">
+        <v>417</v>
+      </c>
+      <c r="E162">
+        <v>5</v>
+      </c>
+      <c r="F162">
+        <v>10</v>
+      </c>
+      <c r="G162">
+        <v>300</v>
+      </c>
+      <c r="H162">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A163">
+        <f t="shared" si="0"/>
+        <v>161</v>
+      </c>
+      <c r="B163" t="s">
+        <v>418</v>
+      </c>
+      <c r="C163" t="s">
+        <v>419</v>
+      </c>
+      <c r="D163" t="s">
+        <v>420</v>
+      </c>
+      <c r="E163">
+        <v>5</v>
+      </c>
+      <c r="F163">
+        <v>10</v>
+      </c>
+      <c r="G163">
+        <v>300</v>
+      </c>
+      <c r="H163">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A164">
+        <f t="shared" si="0"/>
+        <v>162</v>
+      </c>
+      <c r="B164" t="s">
+        <v>421</v>
+      </c>
+      <c r="C164" t="s">
+        <v>422</v>
+      </c>
+      <c r="D164" t="s">
+        <v>423</v>
+      </c>
+      <c r="E164">
+        <v>5</v>
+      </c>
+      <c r="F164">
+        <v>20</v>
+      </c>
+      <c r="G164">
+        <v>500</v>
+      </c>
+      <c r="H164">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A165">
+        <f t="shared" si="0"/>
+        <v>163</v>
+      </c>
+      <c r="B165" t="s">
+        <v>424</v>
+      </c>
+      <c r="C165" t="s">
+        <v>425</v>
+      </c>
+      <c r="D165" t="s">
+        <v>426</v>
+      </c>
+      <c r="E165">
+        <v>-5</v>
+      </c>
+      <c r="F165">
+        <v>-10</v>
+      </c>
+      <c r="G165">
+        <v>300</v>
+      </c>
+      <c r="H165">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A166">
+        <f t="shared" si="0"/>
+        <v>164</v>
+      </c>
+      <c r="B166" t="s">
+        <v>433</v>
+      </c>
+      <c r="C166" t="s">
+        <v>434</v>
+      </c>
+      <c r="D166" t="s">
+        <v>435</v>
+      </c>
+      <c r="E166">
+        <v>5</v>
+      </c>
+      <c r="F166">
+        <v>15</v>
+      </c>
+      <c r="G166">
+        <v>300</v>
+      </c>
+      <c r="H166">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A167">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="B167" t="s">
+        <v>480</v>
+      </c>
+      <c r="C167" t="s">
+        <v>481</v>
+      </c>
+      <c r="D167" t="s">
+        <v>482</v>
+      </c>
+      <c r="E167">
+        <v>5</v>
+      </c>
+      <c r="F167">
+        <v>10</v>
+      </c>
+      <c r="G167">
+        <v>80</v>
+      </c>
+      <c r="H167">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A168">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+      <c r="B168" t="s">
+        <v>483</v>
+      </c>
+      <c r="C168" t="s">
+        <v>484</v>
+      </c>
+      <c r="D168" t="s">
+        <v>485</v>
+      </c>
+      <c r="E168">
+        <v>5</v>
+      </c>
+      <c r="F168">
+        <v>10</v>
+      </c>
+      <c r="G168">
+        <v>80</v>
+      </c>
+      <c r="H168">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A169">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="B169" t="s">
+        <v>486</v>
+      </c>
+      <c r="C169" t="s">
+        <v>487</v>
+      </c>
+      <c r="D169" t="s">
+        <v>488</v>
+      </c>
+      <c r="E169">
+        <v>5</v>
+      </c>
+      <c r="F169">
+        <v>10</v>
+      </c>
+      <c r="G169">
+        <v>80</v>
+      </c>
+      <c r="H169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A170">
+        <f t="shared" si="0"/>
+        <v>168</v>
+      </c>
+      <c r="B170" t="s">
+        <v>489</v>
+      </c>
+      <c r="C170" t="s">
+        <v>490</v>
+      </c>
+      <c r="D170" t="s">
+        <v>491</v>
+      </c>
+      <c r="E170">
+        <v>5</v>
+      </c>
+      <c r="F170">
+        <v>10</v>
+      </c>
+      <c r="G170">
+        <v>80</v>
+      </c>
+      <c r="H170">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A171">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="B171" t="s">
+        <v>492</v>
+      </c>
+      <c r="C171" t="s">
+        <v>493</v>
+      </c>
+      <c r="D171" t="s">
+        <v>494</v>
+      </c>
+      <c r="E171">
+        <v>5</v>
+      </c>
+      <c r="F171">
+        <v>10</v>
+      </c>
+      <c r="G171">
+        <v>80</v>
+      </c>
+      <c r="H171">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A172">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="B172" t="s">
         <v>85</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C172" t="s">
         <v>86</v>
       </c>
-      <c r="D155" t="s">
+      <c r="D172" t="s">
         <v>87</v>
       </c>
-      <c r="E155">
+      <c r="E172">
         <v>150</v>
       </c>
-      <c r="F155">
+      <c r="F172">
         <v>100</v>
       </c>
-      <c r="G155">
+      <c r="G172">
         <v>300</v>
       </c>
-      <c r="H155">
+      <c r="H172">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5143D677-CB97-4C47-92BC-3F03F1C7CD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD079C0-07C5-42EF-899F-1BDA796CB855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="1620" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1710" yWindow="930" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="515">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -2734,10 +2734,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>シュワシュワ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>シュワシュワソーダ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3018,6 +3014,55 @@
     <t>白くまチョコ</t>
     <rPh sb="0" eb="1">
       <t>シロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュワシュワUP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IceCubeHigh</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IceCubeEx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>上質氷</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウシツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コオリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>最上の氷</t>
+    <rPh sb="0" eb="2">
+      <t>サイジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コオリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キンキン豊かな</t>
+    <rPh sb="4" eb="5">
+      <t>ユタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>万年氷の</t>
+    <rPh sb="0" eb="2">
+      <t>マンネン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コオリ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3402,7 +3447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3441,7 +3486,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A172" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A174" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -3508,7 +3553,7 @@
         <v>117</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -3517,7 +3562,7 @@
         <v>50</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -3535,16 +3580,16 @@
         <v>290</v>
       </c>
       <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
         <v>20</v>
-      </c>
-      <c r="F5">
-        <v>50</v>
       </c>
       <c r="G5">
         <v>250</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -3724,10 +3769,10 @@
         <v>285</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>200</v>
@@ -3751,13 +3796,13 @@
         <v>233</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G13">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H13">
         <v>13</v>
@@ -3805,7 +3850,7 @@
         <v>129</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -4210,7 +4255,7 @@
         <v>293</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>50</v>
@@ -4237,7 +4282,7 @@
         <v>376</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>50</v>
@@ -4264,7 +4309,7 @@
         <v>379</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32">
         <v>50</v>
@@ -4525,13 +4570,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>494</v>
+      </c>
+      <c r="C42" t="s">
         <v>495</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>496</v>
-      </c>
-      <c r="D42" t="s">
-        <v>497</v>
       </c>
       <c r="E42">
         <v>-30</v>
@@ -4588,7 +4633,7 @@
         <v>43</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -4615,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F45">
         <v>8</v>
@@ -4696,7 +4741,7 @@
         <v>306</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48">
         <v>20</v>
@@ -4723,7 +4768,7 @@
         <v>270</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F49">
         <v>30</v>
@@ -4750,7 +4795,7 @@
         <v>272</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F50">
         <v>30</v>
@@ -4879,10 +4924,10 @@
         <v>460</v>
       </c>
       <c r="C55" t="s">
+        <v>508</v>
+      </c>
+      <c r="D55" t="s">
         <v>461</v>
-      </c>
-      <c r="D55" t="s">
-        <v>462</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -4894,7 +4939,7 @@
         <v>150</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
@@ -5182,7 +5227,7 @@
         <v>168</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66">
         <v>30</v>
@@ -5506,7 +5551,7 @@
         <v>295</v>
       </c>
       <c r="E78">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="F78">
         <v>5</v>
@@ -5551,13 +5596,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>497</v>
+      </c>
+      <c r="C80" t="s">
         <v>498</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>499</v>
-      </c>
-      <c r="D80" t="s">
-        <v>500</v>
       </c>
       <c r="E80">
         <v>15</v>
@@ -5776,7 +5821,7 @@
         <v>179</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F88">
         <v>10</v>
@@ -5785,7 +5830,7 @@
         <v>240</v>
       </c>
       <c r="H88">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -5803,7 +5848,7 @@
         <v>180</v>
       </c>
       <c r="E89">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F89">
         <v>20</v>
@@ -5812,7 +5857,7 @@
         <v>240</v>
       </c>
       <c r="H89">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.4">
@@ -5830,7 +5875,7 @@
         <v>181</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F90">
         <v>20</v>
@@ -5839,7 +5884,7 @@
         <v>240</v>
       </c>
       <c r="H90">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.4">
@@ -5857,7 +5902,7 @@
         <v>182</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F91">
         <v>10</v>
@@ -5866,7 +5911,7 @@
         <v>240</v>
       </c>
       <c r="H91">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.4">
@@ -5884,7 +5929,7 @@
         <v>213</v>
       </c>
       <c r="E92">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F92">
         <v>10</v>
@@ -5893,7 +5938,7 @@
         <v>240</v>
       </c>
       <c r="H92">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.4">
@@ -5911,7 +5956,7 @@
         <v>212</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F93">
         <v>10</v>
@@ -5920,7 +5965,7 @@
         <v>240</v>
       </c>
       <c r="H93">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
@@ -5938,7 +5983,7 @@
         <v>258</v>
       </c>
       <c r="E94">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F94">
         <v>12</v>
@@ -5947,7 +5992,7 @@
         <v>240</v>
       </c>
       <c r="H94">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
@@ -5965,7 +6010,7 @@
         <v>211</v>
       </c>
       <c r="E95">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F95">
         <v>30</v>
@@ -5974,7 +6019,7 @@
         <v>240</v>
       </c>
       <c r="H95">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -6037,13 +6082,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C98" t="s">
+        <v>462</v>
+      </c>
+      <c r="D98" t="s">
         <v>463</v>
-      </c>
-      <c r="D98" t="s">
-        <v>464</v>
       </c>
       <c r="E98">
         <v>10</v>
@@ -6064,13 +6109,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
+        <v>465</v>
+      </c>
+      <c r="C99" t="s">
         <v>466</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>467</v>
-      </c>
-      <c r="D99" t="s">
-        <v>468</v>
       </c>
       <c r="E99">
         <v>10</v>
@@ -6091,13 +6136,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
+        <v>468</v>
+      </c>
+      <c r="C100" t="s">
         <v>469</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>470</v>
-      </c>
-      <c r="D100" t="s">
-        <v>471</v>
       </c>
       <c r="E100">
         <v>10</v>
@@ -6118,13 +6163,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
+        <v>471</v>
+      </c>
+      <c r="C101" t="s">
         <v>472</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>473</v>
-      </c>
-      <c r="D101" t="s">
-        <v>474</v>
       </c>
       <c r="E101">
         <v>10</v>
@@ -6145,13 +6190,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
+        <v>474</v>
+      </c>
+      <c r="C102" t="s">
         <v>475</v>
       </c>
-      <c r="C102" t="s">
-        <v>476</v>
-      </c>
       <c r="D102" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -6172,13 +6217,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
+        <v>503</v>
+      </c>
+      <c r="C103" t="s">
         <v>504</v>
       </c>
-      <c r="C103" t="s">
-        <v>505</v>
-      </c>
       <c r="D103" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E103">
         <v>10</v>
@@ -6199,13 +6244,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
+        <v>506</v>
+      </c>
+      <c r="C104" t="s">
         <v>507</v>
       </c>
-      <c r="C104" t="s">
-        <v>508</v>
-      </c>
       <c r="D104" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E104">
         <v>10</v>
@@ -6226,13 +6271,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
+        <v>476</v>
+      </c>
+      <c r="C105" t="s">
         <v>477</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>478</v>
-      </c>
-      <c r="D105" t="s">
-        <v>479</v>
       </c>
       <c r="E105">
         <v>5</v>
@@ -6937,7 +6982,7 @@
         <v>355</v>
       </c>
       <c r="E131">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>10</v>
@@ -6964,7 +7009,7 @@
         <v>453</v>
       </c>
       <c r="E132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>10</v>
@@ -7036,22 +7081,22 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>509</v>
       </c>
       <c r="C135" t="s">
-        <v>77</v>
+        <v>511</v>
       </c>
       <c r="D135" t="s">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>-30</v>
       </c>
       <c r="F135">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H135">
         <v>2</v>
@@ -7063,25 +7108,25 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>106</v>
+        <v>510</v>
       </c>
       <c r="C136" t="s">
-        <v>141</v>
+        <v>512</v>
       </c>
       <c r="D136" t="s">
-        <v>228</v>
+        <v>514</v>
       </c>
       <c r="E136">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="F136">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7090,25 +7135,25 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C137" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="D137" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="E137">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="F137">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="G137">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7117,25 +7162,25 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="C138" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="D138" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F138">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G138">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H138">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7144,25 +7189,25 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="C139" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D139" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E139">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="F139">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G139">
         <v>150</v>
       </c>
       <c r="H139">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -7171,22 +7216,22 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="C140" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="D140" t="s">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="E140">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F140">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G140">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H140">
         <v>10</v>
@@ -7198,25 +7243,25 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="C141" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="D141" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="E141">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F141">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G141">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
@@ -7225,13 +7270,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>303</v>
+        <v>90</v>
       </c>
       <c r="C142" t="s">
-        <v>302</v>
+        <v>99</v>
       </c>
       <c r="D142" t="s">
-        <v>301</v>
+        <v>91</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -7240,10 +7285,10 @@
         <v>10</v>
       </c>
       <c r="G142">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H142">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -7252,25 +7297,25 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="C143" t="s">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="D143" t="s">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="E143">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G143">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H143">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7279,25 +7324,25 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C144" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D144" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E144">
         <v>5</v>
       </c>
       <c r="F144">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G144">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H144">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7306,13 +7351,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D145" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E145">
         <v>5</v>
@@ -7321,10 +7366,10 @@
         <v>15</v>
       </c>
       <c r="G145">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H145">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.4">
@@ -7333,13 +7378,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C146" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D146" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E146">
         <v>5</v>
@@ -7348,10 +7393,10 @@
         <v>15</v>
       </c>
       <c r="G146">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H146">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.4">
@@ -7360,13 +7405,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C147" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D147" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E147">
         <v>5</v>
@@ -7387,13 +7432,13 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C148" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D148" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="E148">
         <v>5</v>
@@ -7414,13 +7459,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C149" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D149" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="E149">
         <v>5</v>
@@ -7429,7 +7474,7 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H149">
         <v>15</v>
@@ -7441,13 +7486,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C150" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D150" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E150">
         <v>5</v>
@@ -7456,7 +7501,7 @@
         <v>15</v>
       </c>
       <c r="G150">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H150">
         <v>15</v>
@@ -7468,13 +7513,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>501</v>
+        <v>332</v>
       </c>
       <c r="C151" t="s">
-        <v>502</v>
+        <v>333</v>
       </c>
       <c r="D151" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="E151">
         <v>5</v>
@@ -7495,13 +7540,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C152" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D152" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E152">
         <v>5</v>
@@ -7510,10 +7555,10 @@
         <v>15</v>
       </c>
       <c r="G152">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H152">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7522,13 +7567,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="C153" t="s">
-        <v>319</v>
+        <v>501</v>
       </c>
       <c r="D153" t="s">
-        <v>320</v>
+        <v>502</v>
       </c>
       <c r="E153">
         <v>5</v>
@@ -7537,10 +7582,10 @@
         <v>15</v>
       </c>
       <c r="G153">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H153">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7549,25 +7594,25 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>430</v>
+        <v>315</v>
       </c>
       <c r="C154" t="s">
-        <v>431</v>
+        <v>316</v>
       </c>
       <c r="D154" t="s">
-        <v>432</v>
+        <v>317</v>
       </c>
       <c r="E154">
         <v>5</v>
       </c>
       <c r="F154">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G154">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H154">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7576,22 +7621,22 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>436</v>
+        <v>318</v>
       </c>
       <c r="C155" t="s">
-        <v>437</v>
+        <v>319</v>
       </c>
       <c r="D155" t="s">
-        <v>438</v>
+        <v>320</v>
       </c>
       <c r="E155">
         <v>5</v>
       </c>
       <c r="F155">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G155">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="H155">
         <v>20</v>
@@ -7603,13 +7648,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="E156">
         <v>5</v>
@@ -7618,10 +7663,10 @@
         <v>10</v>
       </c>
       <c r="G156">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H156">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7630,13 +7675,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="C157" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="D157" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="E157">
         <v>5</v>
@@ -7645,10 +7690,10 @@
         <v>10</v>
       </c>
       <c r="G157">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H157">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7657,13 +7702,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C158" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E158">
         <v>5</v>
@@ -7675,7 +7720,7 @@
         <v>300</v>
       </c>
       <c r="H158">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7684,13 +7729,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C159" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E159">
         <v>5</v>
@@ -7702,7 +7747,7 @@
         <v>300</v>
       </c>
       <c r="H159">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7711,13 +7756,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C160" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E160">
         <v>5</v>
@@ -7729,7 +7774,7 @@
         <v>300</v>
       </c>
       <c r="H160">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7738,13 +7783,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C161" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D161" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E161">
         <v>5</v>
@@ -7765,13 +7810,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C162" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E162">
         <v>5</v>
@@ -7783,7 +7828,7 @@
         <v>300</v>
       </c>
       <c r="H162">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7792,13 +7837,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C163" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="E163">
         <v>5</v>
@@ -7819,25 +7864,25 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C164" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="D164" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E164">
         <v>5</v>
       </c>
       <c r="F164">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G164">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H164">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -7846,19 +7891,19 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C165" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E165">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="F165">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G165">
         <v>300</v>
@@ -7873,25 +7918,25 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C166" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D166" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E166">
         <v>5</v>
       </c>
       <c r="F166">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G166">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H166">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -7900,25 +7945,25 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>480</v>
+        <v>424</v>
       </c>
       <c r="C167" t="s">
-        <v>481</v>
+        <v>425</v>
       </c>
       <c r="D167" t="s">
-        <v>482</v>
+        <v>426</v>
       </c>
       <c r="E167">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G167">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H167">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -7927,25 +7972,25 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>483</v>
+        <v>433</v>
       </c>
       <c r="C168" t="s">
-        <v>484</v>
+        <v>434</v>
       </c>
       <c r="D168" t="s">
-        <v>485</v>
+        <v>435</v>
       </c>
       <c r="E168">
         <v>5</v>
       </c>
       <c r="F168">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G168">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H168">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -7954,16 +7999,16 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C169" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="D169" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E169">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F169">
         <v>10</v>
@@ -7972,7 +8017,7 @@
         <v>80</v>
       </c>
       <c r="H169">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -7981,13 +8026,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C170" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D170" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="E170">
         <v>5</v>
@@ -8008,13 +8053,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C171" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="D171" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="E171">
         <v>5</v>
@@ -8035,24 +8080,78 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
+        <v>488</v>
+      </c>
+      <c r="C172" t="s">
+        <v>489</v>
+      </c>
+      <c r="D172" t="s">
+        <v>490</v>
+      </c>
+      <c r="E172">
+        <v>5</v>
+      </c>
+      <c r="F172">
+        <v>10</v>
+      </c>
+      <c r="G172">
+        <v>80</v>
+      </c>
+      <c r="H172">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A173">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="B173" t="s">
+        <v>491</v>
+      </c>
+      <c r="C173" t="s">
+        <v>492</v>
+      </c>
+      <c r="D173" t="s">
+        <v>493</v>
+      </c>
+      <c r="E173">
+        <v>5</v>
+      </c>
+      <c r="F173">
+        <v>10</v>
+      </c>
+      <c r="G173">
+        <v>80</v>
+      </c>
+      <c r="H173">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A174">
+        <f t="shared" si="0"/>
+        <v>172</v>
+      </c>
+      <c r="B174" t="s">
         <v>85</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C174" t="s">
         <v>86</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D174" t="s">
         <v>87</v>
       </c>
-      <c r="E172">
+      <c r="E174">
         <v>150</v>
       </c>
-      <c r="F172">
+      <c r="F174">
         <v>100</v>
       </c>
-      <c r="G172">
+      <c r="G174">
         <v>300</v>
       </c>
-      <c r="H172">
+      <c r="H174">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD079C0-07C5-42EF-899F-1BDA796CB855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FF3AD1-66D3-4963-98FB-7895D655A4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="930" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3526,7 +3526,7 @@
         <v>220</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3553,7 +3553,7 @@
         <v>117</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -3580,7 +3580,7 @@
         <v>290</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -3607,7 +3607,7 @@
         <v>201</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3634,7 +3634,7 @@
         <v>358</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -3661,7 +3661,7 @@
         <v>240</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -3688,7 +3688,7 @@
         <v>361</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>15</v>
@@ -3715,7 +3715,7 @@
         <v>239</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -3742,7 +3742,7 @@
         <v>245</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>12</v>
@@ -3769,7 +3769,7 @@
         <v>285</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>20</v>
@@ -3796,7 +3796,7 @@
         <v>233</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>20</v>
@@ -3823,7 +3823,7 @@
         <v>242</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>12</v>
@@ -3850,7 +3850,7 @@
         <v>129</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -3877,7 +3877,7 @@
         <v>149</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -3904,7 +3904,7 @@
         <v>246</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>10</v>
@@ -3931,7 +3931,7 @@
         <v>364</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -3958,7 +3958,7 @@
         <v>367</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -3985,7 +3985,7 @@
         <v>200</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>14</v>
@@ -4012,7 +4012,7 @@
         <v>208</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>10</v>
@@ -4039,7 +4039,7 @@
         <v>244</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -4066,7 +4066,7 @@
         <v>370</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -4093,7 +4093,7 @@
         <v>202</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>12</v>
@@ -4120,7 +4120,7 @@
         <v>241</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>20</v>
@@ -4174,7 +4174,7 @@
         <v>243</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>20</v>
@@ -4228,7 +4228,7 @@
         <v>248</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>20</v>
@@ -4255,7 +4255,7 @@
         <v>293</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>50</v>
@@ -4282,7 +4282,7 @@
         <v>376</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>50</v>
@@ -4309,7 +4309,7 @@
         <v>379</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>50</v>
@@ -4336,7 +4336,7 @@
         <v>440</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>50</v>
@@ -4363,7 +4363,7 @@
         <v>441</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>50</v>
@@ -4390,7 +4390,7 @@
         <v>247</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -4417,7 +4417,7 @@
         <v>386</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>288</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>30</v>
@@ -4471,7 +4471,7 @@
         <v>204</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>8</v>
@@ -4498,7 +4498,7 @@
         <v>205</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>30</v>
@@ -4606,7 +4606,7 @@
         <v>20</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F43">
         <v>15</v>
@@ -4633,7 +4633,7 @@
         <v>43</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F44">
         <v>8</v>
@@ -4660,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="E45">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>8</v>
@@ -4687,7 +4687,7 @@
         <v>18</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>20</v>
@@ -4714,7 +4714,7 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F47">
         <v>15</v>
@@ -4741,7 +4741,7 @@
         <v>306</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>20</v>
@@ -4768,7 +4768,7 @@
         <v>270</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>30</v>
@@ -4795,7 +4795,7 @@
         <v>272</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>30</v>
@@ -4822,7 +4822,7 @@
         <v>23</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>5</v>
@@ -4849,7 +4849,7 @@
         <v>233</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>100</v>
@@ -4876,7 +4876,7 @@
         <v>238</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <v>15</v>
@@ -4903,7 +4903,7 @@
         <v>232</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>10</v>
@@ -4957,7 +4957,7 @@
         <v>221</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>5</v>
@@ -4984,7 +4984,7 @@
         <v>252</v>
       </c>
       <c r="E57">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>30</v>
@@ -5011,7 +5011,7 @@
         <v>256</v>
       </c>
       <c r="E58">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>50</v>
@@ -5038,7 +5038,7 @@
         <v>266</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -5065,7 +5065,7 @@
         <v>280</v>
       </c>
       <c r="E60">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>50</v>
@@ -5092,7 +5092,7 @@
         <v>222</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -5119,7 +5119,7 @@
         <v>223</v>
       </c>
       <c r="E62">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>7</v>
@@ -5146,7 +5146,7 @@
         <v>283</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>5</v>
@@ -5173,7 +5173,7 @@
         <v>34</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>92</v>
       </c>
       <c r="E65">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>5</v>
@@ -5227,7 +5227,7 @@
         <v>168</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>30</v>
@@ -5254,7 +5254,7 @@
         <v>62</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -5263,7 +5263,7 @@
         <v>120</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.4">
@@ -5281,7 +5281,7 @@
         <v>70</v>
       </c>
       <c r="E68">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>5</v>
@@ -5290,7 +5290,7 @@
         <v>120</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
@@ -5308,7 +5308,7 @@
         <v>65</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>5</v>
@@ -5317,7 +5317,7 @@
         <v>120</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.4">
@@ -5335,7 +5335,7 @@
         <v>147</v>
       </c>
       <c r="E70">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>5</v>
@@ -5344,7 +5344,7 @@
         <v>120</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">
@@ -5362,7 +5362,7 @@
         <v>160</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>5</v>
@@ -5371,7 +5371,7 @@
         <v>120</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.4">
@@ -5389,7 +5389,7 @@
         <v>164</v>
       </c>
       <c r="E72">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F72">
         <v>5</v>
@@ -5398,7 +5398,7 @@
         <v>120</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.4">
@@ -5416,7 +5416,7 @@
         <v>166</v>
       </c>
       <c r="E73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>5</v>
@@ -5425,7 +5425,7 @@
         <v>120</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.4">
@@ -5443,7 +5443,7 @@
         <v>68</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F74">
         <v>5</v>
@@ -5452,7 +5452,7 @@
         <v>120</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.4">
@@ -5470,7 +5470,7 @@
         <v>190</v>
       </c>
       <c r="E75">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <v>5</v>
@@ -5479,7 +5479,7 @@
         <v>120</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.4">
@@ -5497,7 +5497,7 @@
         <v>148</v>
       </c>
       <c r="E76">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F76">
         <v>5</v>
@@ -5506,7 +5506,7 @@
         <v>120</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.4">
@@ -5524,7 +5524,7 @@
         <v>262</v>
       </c>
       <c r="E77">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <v>5</v>
@@ -5533,7 +5533,7 @@
         <v>120</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.4">
@@ -5578,7 +5578,7 @@
         <v>277</v>
       </c>
       <c r="E79">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>20</v>
@@ -5587,7 +5587,7 @@
         <v>120</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
@@ -5605,7 +5605,7 @@
         <v>499</v>
       </c>
       <c r="E80">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F80">
         <v>20</v>
@@ -5614,7 +5614,7 @@
         <v>120</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.4">
@@ -5632,7 +5632,7 @@
         <v>79</v>
       </c>
       <c r="E81">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F81">
         <v>4</v>
@@ -5641,7 +5641,7 @@
         <v>50</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.4">
@@ -5659,7 +5659,7 @@
         <v>224</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>7</v>
@@ -5668,7 +5668,7 @@
         <v>50</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.4">
@@ -5686,7 +5686,7 @@
         <v>429</v>
       </c>
       <c r="E83">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>7</v>
@@ -5695,7 +5695,7 @@
         <v>50</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5713,7 +5713,7 @@
         <v>280</v>
       </c>
       <c r="E84">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>7</v>
@@ -5722,7 +5722,7 @@
         <v>50</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -5740,7 +5740,7 @@
         <v>209</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>30</v>
@@ -5767,7 +5767,7 @@
         <v>459</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>30</v>
@@ -5794,7 +5794,7 @@
         <v>80</v>
       </c>
       <c r="E87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>10</v>
@@ -5821,7 +5821,7 @@
         <v>179</v>
       </c>
       <c r="E88">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>10</v>
@@ -5848,7 +5848,7 @@
         <v>180</v>
       </c>
       <c r="E89">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>20</v>
@@ -5875,7 +5875,7 @@
         <v>181</v>
       </c>
       <c r="E90">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F90">
         <v>20</v>
@@ -5902,7 +5902,7 @@
         <v>182</v>
       </c>
       <c r="E91">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F91">
         <v>10</v>
@@ -5929,7 +5929,7 @@
         <v>213</v>
       </c>
       <c r="E92">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F92">
         <v>10</v>
@@ -5956,7 +5956,7 @@
         <v>212</v>
       </c>
       <c r="E93">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>10</v>
@@ -5983,7 +5983,7 @@
         <v>258</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>12</v>
@@ -6010,7 +6010,7 @@
         <v>211</v>
       </c>
       <c r="E95">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>30</v>
@@ -6037,7 +6037,7 @@
         <v>44</v>
       </c>
       <c r="E96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>5</v>
@@ -6064,7 +6064,7 @@
         <v>447</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>10</v>
@@ -6091,7 +6091,7 @@
         <v>463</v>
       </c>
       <c r="E98">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>10</v>
@@ -6118,7 +6118,7 @@
         <v>467</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F99">
         <v>10</v>
@@ -6145,7 +6145,7 @@
         <v>470</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>10</v>
@@ -6172,7 +6172,7 @@
         <v>473</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F101">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>475</v>
       </c>
       <c r="E102">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>10</v>
@@ -6226,7 +6226,7 @@
         <v>504</v>
       </c>
       <c r="E103">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>10</v>
@@ -6253,7 +6253,7 @@
         <v>505</v>
       </c>
       <c r="E104">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F104">
         <v>10</v>
@@ -6280,7 +6280,7 @@
         <v>478</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F105">
         <v>10</v>
@@ -6307,7 +6307,7 @@
         <v>225</v>
       </c>
       <c r="E106">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>10</v>
@@ -6361,7 +6361,7 @@
         <v>46</v>
       </c>
       <c r="E108">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>10</v>
@@ -6388,7 +6388,7 @@
         <v>230</v>
       </c>
       <c r="E109">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>12</v>
@@ -6415,7 +6415,7 @@
         <v>253</v>
       </c>
       <c r="E110">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>14</v>
@@ -6442,7 +6442,7 @@
         <v>235</v>
       </c>
       <c r="E111">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>15</v>
@@ -6469,7 +6469,7 @@
         <v>231</v>
       </c>
       <c r="E112">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>6</v>
@@ -6496,7 +6496,7 @@
         <v>215</v>
       </c>
       <c r="E113">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>5</v>
@@ -6523,7 +6523,7 @@
         <v>216</v>
       </c>
       <c r="E114">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>20</v>
@@ -6550,7 +6550,7 @@
         <v>226</v>
       </c>
       <c r="E115">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F115">
         <v>25</v>
@@ -6577,7 +6577,7 @@
         <v>227</v>
       </c>
       <c r="E116">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F116">
         <v>25</v>
@@ -6604,7 +6604,7 @@
         <v>217</v>
       </c>
       <c r="E117">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F117">
         <v>35</v>
@@ -6631,7 +6631,7 @@
         <v>395</v>
       </c>
       <c r="E118">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>35</v>
@@ -6712,7 +6712,7 @@
         <v>449</v>
       </c>
       <c r="E121">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F121">
         <v>10</v>
@@ -6793,7 +6793,7 @@
         <v>142</v>
       </c>
       <c r="E124">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F124">
         <v>30</v>
@@ -6820,7 +6820,7 @@
         <v>341</v>
       </c>
       <c r="E125">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F125">
         <v>10</v>
@@ -6829,7 +6829,7 @@
         <v>300</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -6847,7 +6847,7 @@
         <v>442</v>
       </c>
       <c r="E126">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>300</v>
       </c>
       <c r="H126">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6874,7 +6874,7 @@
         <v>346</v>
       </c>
       <c r="E127">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>10</v>
@@ -6883,7 +6883,7 @@
         <v>300</v>
       </c>
       <c r="H127">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -6901,7 +6901,7 @@
         <v>443</v>
       </c>
       <c r="E128">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F128">
         <v>10</v>
@@ -6910,7 +6910,7 @@
         <v>300</v>
       </c>
       <c r="H128">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -6928,7 +6928,7 @@
         <v>445</v>
       </c>
       <c r="E129">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F129">
         <v>10</v>
@@ -6937,7 +6937,7 @@
         <v>600</v>
       </c>
       <c r="H129">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -6955,7 +6955,7 @@
         <v>444</v>
       </c>
       <c r="E130">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>10</v>
@@ -6964,7 +6964,7 @@
         <v>700</v>
       </c>
       <c r="H130">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -6991,7 +6991,7 @@
         <v>700</v>
       </c>
       <c r="H131">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -7018,7 +7018,7 @@
         <v>300</v>
       </c>
       <c r="H132">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7045,7 +7045,7 @@
         <v>500</v>
       </c>
       <c r="H133">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7144,7 +7144,7 @@
         <v>78</v>
       </c>
       <c r="E137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>5</v>
@@ -7171,7 +7171,7 @@
         <v>228</v>
       </c>
       <c r="E138">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>30</v>
@@ -7180,7 +7180,7 @@
         <v>300</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7225,7 +7225,7 @@
         <v>185</v>
       </c>
       <c r="E140">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>20</v>
@@ -7252,7 +7252,7 @@
         <v>188</v>
       </c>
       <c r="E141">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>20</v>
@@ -7279,7 +7279,7 @@
         <v>91</v>
       </c>
       <c r="E142">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>10</v>
@@ -7306,7 +7306,7 @@
         <v>84</v>
       </c>
       <c r="E143">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>30</v>
@@ -7315,7 +7315,7 @@
         <v>300</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7333,7 +7333,7 @@
         <v>301</v>
       </c>
       <c r="E144">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>10</v>
@@ -7360,7 +7360,7 @@
         <v>334</v>
       </c>
       <c r="E145">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <v>15</v>
@@ -7387,7 +7387,7 @@
         <v>311</v>
       </c>
       <c r="E146">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F146">
         <v>15</v>
@@ -7414,7 +7414,7 @@
         <v>324</v>
       </c>
       <c r="E147">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>15</v>
@@ -7441,7 +7441,7 @@
         <v>314</v>
       </c>
       <c r="E148">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>15</v>
@@ -7468,7 +7468,7 @@
         <v>328</v>
       </c>
       <c r="E149">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>15</v>
@@ -7495,7 +7495,7 @@
         <v>330</v>
       </c>
       <c r="E150">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>15</v>
@@ -7522,7 +7522,7 @@
         <v>335</v>
       </c>
       <c r="E151">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>15</v>
@@ -7549,7 +7549,7 @@
         <v>338</v>
       </c>
       <c r="E152">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>15</v>
@@ -7576,7 +7576,7 @@
         <v>502</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>15</v>
@@ -7603,7 +7603,7 @@
         <v>317</v>
       </c>
       <c r="E154">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>15</v>
@@ -7630,7 +7630,7 @@
         <v>320</v>
       </c>
       <c r="E155">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>15</v>
@@ -7657,7 +7657,7 @@
         <v>432</v>
       </c>
       <c r="E156">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>10</v>
@@ -7684,7 +7684,7 @@
         <v>438</v>
       </c>
       <c r="E157">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>10</v>
@@ -7711,7 +7711,7 @@
         <v>399</v>
       </c>
       <c r="E158">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>10</v>
@@ -7738,7 +7738,7 @@
         <v>411</v>
       </c>
       <c r="E159">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>10</v>
@@ -7765,7 +7765,7 @@
         <v>404</v>
       </c>
       <c r="E160">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>10</v>
@@ -7792,7 +7792,7 @@
         <v>407</v>
       </c>
       <c r="E161">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>10</v>
@@ -7819,7 +7819,7 @@
         <v>410</v>
       </c>
       <c r="E162">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>10</v>
@@ -7846,7 +7846,7 @@
         <v>413</v>
       </c>
       <c r="E163">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>10</v>
@@ -7873,7 +7873,7 @@
         <v>417</v>
       </c>
       <c r="E164">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>10</v>
@@ -7900,7 +7900,7 @@
         <v>420</v>
       </c>
       <c r="E165">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>10</v>
@@ -7927,7 +7927,7 @@
         <v>423</v>
       </c>
       <c r="E166">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>20</v>
@@ -7981,7 +7981,7 @@
         <v>435</v>
       </c>
       <c r="E168">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F168">
         <v>15</v>
@@ -8035,7 +8035,7 @@
         <v>484</v>
       </c>
       <c r="E170">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>10</v>
@@ -8062,7 +8062,7 @@
         <v>487</v>
       </c>
       <c r="E171">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>10</v>
@@ -8089,7 +8089,7 @@
         <v>490</v>
       </c>
       <c r="E172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>10</v>
@@ -8116,7 +8116,7 @@
         <v>493</v>
       </c>
       <c r="E173">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>10</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FF3AD1-66D3-4963-98FB-7895D655A4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA21384-B571-4952-994B-3236CD7BD684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7339,7 +7339,7 @@
         <v>10</v>
       </c>
       <c r="G144">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H144">
         <v>5</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA21384-B571-4952-994B-3236CD7BD684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1778789-217F-415C-A2E3-51E667CF4D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1920" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6559,7 +6559,7 @@
         <v>350</v>
       </c>
       <c r="H115">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
@@ -6586,7 +6586,7 @@
         <v>350</v>
       </c>
       <c r="H116">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
@@ -6613,7 +6613,7 @@
         <v>400</v>
       </c>
       <c r="H117">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
@@ -6802,7 +6802,7 @@
         <v>150</v>
       </c>
       <c r="H124">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1778789-217F-415C-A2E3-51E667CF4D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0B5FB8-981E-4332-9925-CA2CD4310060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="1140" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0B5FB8-981E-4332-9925-CA2CD4310060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FC588A-6FE8-46DB-925D-7DE5851A94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1140" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1845" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2638,10 +2638,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>キンキンの</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ショコラ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3050,20 +3046,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>キンキン豊かな</t>
-    <rPh sb="4" eb="5">
-      <t>ユタ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>万年氷の</t>
-    <rPh sb="0" eb="2">
-      <t>マンネン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>コオリ</t>
-    </rPh>
+    <t>ひえひえ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キンキン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブリザード</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4570,13 +4561,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>493</v>
+      </c>
+      <c r="C42" t="s">
         <v>494</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>495</v>
-      </c>
-      <c r="D42" t="s">
-        <v>496</v>
       </c>
       <c r="E42">
         <v>-30</v>
@@ -4921,13 +4912,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>459</v>
+      </c>
+      <c r="C55" t="s">
+        <v>507</v>
+      </c>
+      <c r="D55" t="s">
         <v>460</v>
-      </c>
-      <c r="C55" t="s">
-        <v>508</v>
-      </c>
-      <c r="D55" t="s">
-        <v>461</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -5596,13 +5587,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>496</v>
+      </c>
+      <c r="C80" t="s">
         <v>497</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>498</v>
-      </c>
-      <c r="D80" t="s">
-        <v>499</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5758,13 +5749,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
+        <v>456</v>
+      </c>
+      <c r="C86" t="s">
         <v>457</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>458</v>
-      </c>
-      <c r="D86" t="s">
-        <v>459</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -6061,7 +6052,7 @@
         <v>41</v>
       </c>
       <c r="D97" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6082,13 +6073,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C98" t="s">
+        <v>461</v>
+      </c>
+      <c r="D98" t="s">
         <v>462</v>
-      </c>
-      <c r="D98" t="s">
-        <v>463</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6109,13 +6100,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
+        <v>464</v>
+      </c>
+      <c r="C99" t="s">
         <v>465</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>466</v>
-      </c>
-      <c r="D99" t="s">
-        <v>467</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6136,13 +6127,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
+        <v>467</v>
+      </c>
+      <c r="C100" t="s">
         <v>468</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>469</v>
-      </c>
-      <c r="D100" t="s">
-        <v>470</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6163,13 +6154,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
+        <v>470</v>
+      </c>
+      <c r="C101" t="s">
         <v>471</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>472</v>
-      </c>
-      <c r="D101" t="s">
-        <v>473</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6190,13 +6181,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
+        <v>473</v>
+      </c>
+      <c r="C102" t="s">
         <v>474</v>
       </c>
-      <c r="C102" t="s">
-        <v>475</v>
-      </c>
       <c r="D102" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6217,13 +6208,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
+        <v>502</v>
+      </c>
+      <c r="C103" t="s">
         <v>503</v>
       </c>
-      <c r="C103" t="s">
-        <v>504</v>
-      </c>
       <c r="D103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6244,13 +6235,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
+        <v>505</v>
+      </c>
+      <c r="C104" t="s">
         <v>506</v>
       </c>
-      <c r="C104" t="s">
-        <v>507</v>
-      </c>
       <c r="D104" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6271,13 +6262,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
+        <v>475</v>
+      </c>
+      <c r="C105" t="s">
         <v>476</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>477</v>
-      </c>
-      <c r="D105" t="s">
-        <v>478</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6703,13 +6694,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
+        <v>447</v>
+      </c>
+      <c r="C121" t="s">
+        <v>449</v>
+      </c>
+      <c r="D121" t="s">
         <v>448</v>
-      </c>
-      <c r="C121" t="s">
-        <v>450</v>
-      </c>
-      <c r="D121" t="s">
-        <v>449</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7000,13 +6991,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
+        <v>450</v>
+      </c>
+      <c r="C132" t="s">
         <v>451</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>452</v>
-      </c>
-      <c r="D132" t="s">
-        <v>453</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7027,13 +7018,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
+        <v>453</v>
+      </c>
+      <c r="C133" t="s">
         <v>454</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>455</v>
-      </c>
-      <c r="D133" t="s">
-        <v>456</v>
       </c>
       <c r="E133">
         <v>-10</v>
@@ -7060,10 +7051,10 @@
         <v>439</v>
       </c>
       <c r="D134" t="s">
-        <v>446</v>
+        <v>512</v>
       </c>
       <c r="E134">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -7081,16 +7072,16 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C135" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D135" t="s">
         <v>513</v>
       </c>
       <c r="E135">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -7108,16 +7099,16 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C136" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D136" t="s">
         <v>514</v>
       </c>
       <c r="E136">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -7567,13 +7558,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
+        <v>499</v>
+      </c>
+      <c r="C153" t="s">
         <v>500</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
         <v>501</v>
-      </c>
-      <c r="D153" t="s">
-        <v>502</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -7999,13 +7990,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
+        <v>478</v>
+      </c>
+      <c r="C169" t="s">
         <v>479</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>480</v>
-      </c>
-      <c r="D169" t="s">
-        <v>481</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8026,13 +8017,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
+        <v>481</v>
+      </c>
+      <c r="C170" t="s">
         <v>482</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>483</v>
-      </c>
-      <c r="D170" t="s">
-        <v>484</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8053,13 +8044,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
+        <v>484</v>
+      </c>
+      <c r="C171" t="s">
         <v>485</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>486</v>
-      </c>
-      <c r="D171" t="s">
-        <v>487</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8080,13 +8071,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
+        <v>487</v>
+      </c>
+      <c r="C172" t="s">
         <v>488</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>489</v>
-      </c>
-      <c r="D172" t="s">
-        <v>490</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -8107,13 +8098,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
+        <v>490</v>
+      </c>
+      <c r="C173" t="s">
         <v>491</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>492</v>
-      </c>
-      <c r="D173" t="s">
-        <v>493</v>
       </c>
       <c r="E173">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FC588A-6FE8-46DB-925D-7DE5851A94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C042F73C-DF47-4357-82E8-B25A0624BDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1845" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="533">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -3055,6 +3055,120 @@
   </si>
   <si>
     <t>ブリザード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LittleHydrangeaGlow</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>橙紫の光</t>
+    <rPh sb="0" eb="1">
+      <t>ダイダイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>深い橙紫色に光る</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ムラサキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヒカリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LittleViolatteGlow</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>青紫の光</t>
+    <rPh sb="0" eb="2">
+      <t>アオムラサキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>深いすみれ色に光る</t>
+    <rPh sb="0" eb="1">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒカリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ピーチアイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マスカットアイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひんやりピーチ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ひんやりマスカット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PeachIceCream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MuscutIceCream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateIceCream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコアイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>濃厚チョコアイス</t>
+    <rPh sb="0" eb="2">
+      <t>ノウコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Gelato</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジェラートのせ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジェラートッピング</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3438,7 +3552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3477,7 +3591,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A174" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A180" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -5680,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G83">
         <v>50</v>
       </c>
       <c r="H83">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5803,25 +5917,25 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>530</v>
       </c>
       <c r="C88" t="s">
-        <v>175</v>
+        <v>531</v>
       </c>
       <c r="D88" t="s">
-        <v>179</v>
+        <v>532</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G88">
         <v>240</v>
       </c>
       <c r="H88">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -5830,19 +5944,19 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D89" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G89">
         <v>240</v>
@@ -5857,13 +5971,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5884,19 +5998,19 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C91" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G91">
         <v>240</v>
@@ -5911,13 +6025,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C92" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D92" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5938,13 +6052,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C93" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D93" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5965,19 +6079,19 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="C94" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="D94" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G94">
         <v>240</v>
@@ -5992,25 +6106,25 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>525</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>521</v>
       </c>
       <c r="D95" t="s">
-        <v>211</v>
+        <v>523</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G95">
         <v>240</v>
       </c>
       <c r="H95">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -6019,25 +6133,25 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>38</v>
+        <v>526</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>522</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>524</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G96">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="H96">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
@@ -6046,25 +6160,25 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
+        <v>258</v>
       </c>
       <c r="D97" t="s">
-        <v>446</v>
+        <v>258</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G97">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="H97">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
@@ -6073,22 +6187,22 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>463</v>
+        <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>461</v>
+        <v>196</v>
       </c>
       <c r="D98" t="s">
-        <v>462</v>
+        <v>211</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G98">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="H98">
         <v>20</v>
@@ -6100,25 +6214,25 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="C99" t="s">
-        <v>465</v>
+        <v>528</v>
       </c>
       <c r="D99" t="s">
-        <v>466</v>
+        <v>529</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G99">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="H99">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -6127,25 +6241,25 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>467</v>
+        <v>38</v>
       </c>
       <c r="C100" t="s">
-        <v>468</v>
+        <v>146</v>
       </c>
       <c r="D100" t="s">
-        <v>469</v>
+        <v>44</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G100">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="H100">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -6154,13 +6268,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>470</v>
+        <v>40</v>
       </c>
       <c r="C101" t="s">
-        <v>471</v>
+        <v>41</v>
       </c>
       <c r="D101" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6169,10 +6283,10 @@
         <v>10</v>
       </c>
       <c r="G101">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H101">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
@@ -6181,13 +6295,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C102" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D102" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6196,10 +6310,10 @@
         <v>10</v>
       </c>
       <c r="G102">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="H102">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
@@ -6208,13 +6322,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="C103" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="D103" t="s">
-        <v>503</v>
+        <v>466</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6223,10 +6337,10 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H103">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
@@ -6235,13 +6349,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="C104" t="s">
-        <v>506</v>
+        <v>468</v>
       </c>
       <c r="D104" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6250,10 +6364,10 @@
         <v>10</v>
       </c>
       <c r="G104">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H104">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.4">
@@ -6262,13 +6376,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C105" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D105" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6277,10 +6391,10 @@
         <v>10</v>
       </c>
       <c r="G105">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="H105">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
@@ -6289,13 +6403,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>42</v>
+        <v>473</v>
       </c>
       <c r="C106" t="s">
-        <v>214</v>
+        <v>474</v>
       </c>
       <c r="D106" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6304,10 +6418,10 @@
         <v>10</v>
       </c>
       <c r="G106">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="H106">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
@@ -6316,25 +6430,25 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>88</v>
+        <v>502</v>
       </c>
       <c r="C107" t="s">
-        <v>89</v>
+        <v>503</v>
       </c>
       <c r="D107" t="s">
-        <v>89</v>
+        <v>503</v>
       </c>
       <c r="E107">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>10</v>
       </c>
       <c r="G107">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H107">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -6343,13 +6457,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>505</v>
       </c>
       <c r="C108" t="s">
-        <v>98</v>
+        <v>506</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>504</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6358,10 +6472,10 @@
         <v>10</v>
       </c>
       <c r="G108">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="H108">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.4">
@@ -6370,25 +6484,25 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>475</v>
       </c>
       <c r="C109" t="s">
-        <v>144</v>
+        <v>476</v>
       </c>
       <c r="D109" t="s">
-        <v>230</v>
+        <v>477</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G109">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H109">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -6397,25 +6511,25 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C110" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="D110" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G110">
         <v>80</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
@@ -6424,22 +6538,22 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C111" t="s">
-        <v>236</v>
+        <v>89</v>
       </c>
       <c r="D111" t="s">
-        <v>235</v>
+        <v>89</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F111">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G111">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="H111">
         <v>5</v>
@@ -6451,19 +6565,19 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C112" t="s">
-        <v>234</v>
+        <v>98</v>
       </c>
       <c r="D112" t="s">
-        <v>231</v>
+        <v>46</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G112">
         <v>70</v>
@@ -6478,25 +6592,25 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C113" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G113">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
@@ -6505,25 +6619,25 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="C114" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="D114" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G114">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="H114">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
@@ -6532,25 +6646,25 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="C115" t="s">
-        <v>152</v>
+        <v>236</v>
       </c>
       <c r="D115" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G115">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H115">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
@@ -6559,25 +6673,25 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="D116" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G116">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H116">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
@@ -6586,25 +6700,25 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="C117" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G117">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="H117">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
@@ -6613,25 +6727,25 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>393</v>
+        <v>150</v>
       </c>
       <c r="C118" t="s">
-        <v>394</v>
+        <v>151</v>
       </c>
       <c r="D118" t="s">
-        <v>395</v>
+        <v>216</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G118">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="H118">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
@@ -6640,25 +6754,25 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="D119" t="s">
-        <v>121</v>
+        <v>226</v>
       </c>
       <c r="E119">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>-5</v>
+        <v>25</v>
       </c>
       <c r="G119">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H119">
-        <v>-10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
@@ -6667,25 +6781,25 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>387</v>
+        <v>198</v>
       </c>
       <c r="C120" t="s">
-        <v>388</v>
+        <v>199</v>
       </c>
       <c r="D120" t="s">
-        <v>389</v>
+        <v>227</v>
       </c>
       <c r="E120">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>-5</v>
+        <v>25</v>
       </c>
       <c r="G120">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H120">
-        <v>-10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
@@ -6694,25 +6808,25 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>447</v>
+        <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>449</v>
+        <v>154</v>
       </c>
       <c r="D121" t="s">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G121">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="H121">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -6721,25 +6835,25 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="C122" t="s">
-        <v>263</v>
+        <v>394</v>
       </c>
       <c r="D122" t="s">
-        <v>265</v>
+        <v>395</v>
       </c>
       <c r="E122">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>-10</v>
+        <v>35</v>
       </c>
       <c r="G122">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H122">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -6748,22 +6862,22 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>390</v>
+        <v>74</v>
       </c>
       <c r="C123" t="s">
-        <v>391</v>
+        <v>75</v>
       </c>
       <c r="D123" t="s">
-        <v>392</v>
+        <v>121</v>
       </c>
       <c r="E123">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F123">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="G123">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H123">
         <v>-10</v>
@@ -6775,25 +6889,25 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>104</v>
+        <v>387</v>
       </c>
       <c r="C124" t="s">
-        <v>105</v>
+        <v>388</v>
       </c>
       <c r="D124" t="s">
-        <v>142</v>
+        <v>389</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F124">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="G124">
         <v>150</v>
       </c>
       <c r="H124">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
@@ -6802,13 +6916,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>339</v>
+        <v>447</v>
       </c>
       <c r="C125" t="s">
-        <v>340</v>
+        <v>449</v>
       </c>
       <c r="D125" t="s">
-        <v>341</v>
+        <v>448</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6817,10 +6931,10 @@
         <v>10</v>
       </c>
       <c r="G125">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H125">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -6829,25 +6943,25 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>342</v>
+        <v>264</v>
       </c>
       <c r="C126" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
       <c r="D126" t="s">
-        <v>442</v>
+        <v>265</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G126">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H126">
-        <v>10</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6856,25 +6970,25 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="C127" t="s">
-        <v>345</v>
+        <v>391</v>
       </c>
       <c r="D127" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F127">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G127">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H127">
-        <v>10</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
@@ -6883,25 +6997,25 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>347</v>
+        <v>104</v>
       </c>
       <c r="C128" t="s">
-        <v>348</v>
+        <v>105</v>
       </c>
       <c r="D128" t="s">
-        <v>443</v>
+        <v>142</v>
       </c>
       <c r="E128">
         <v>0</v>
       </c>
       <c r="F128">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G128">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H128">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -6910,13 +7024,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C129" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D129" t="s">
-        <v>445</v>
+        <v>341</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6925,7 +7039,7 @@
         <v>10</v>
       </c>
       <c r="G129">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H129">
         <v>10</v>
@@ -6937,13 +7051,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C130" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D130" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6952,7 +7066,7 @@
         <v>10</v>
       </c>
       <c r="G130">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H130">
         <v>10</v>
@@ -6964,13 +7078,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C131" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D131" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6979,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H131">
         <v>10</v>
@@ -6991,13 +7105,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>450</v>
+        <v>347</v>
       </c>
       <c r="C132" t="s">
-        <v>451</v>
+        <v>348</v>
       </c>
       <c r="D132" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7018,22 +7132,22 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>453</v>
+        <v>349</v>
       </c>
       <c r="C133" t="s">
-        <v>454</v>
+        <v>350</v>
       </c>
       <c r="D133" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="E133">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>10</v>
       </c>
       <c r="G133">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H133">
         <v>10</v>
@@ -7045,25 +7159,25 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="C134" t="s">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="D134" t="s">
-        <v>512</v>
+        <v>444</v>
       </c>
       <c r="E134">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G134">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H134">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7072,25 +7186,25 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>508</v>
+        <v>353</v>
       </c>
       <c r="C135" t="s">
-        <v>510</v>
+        <v>354</v>
       </c>
       <c r="D135" t="s">
-        <v>513</v>
+        <v>355</v>
       </c>
       <c r="E135">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G135">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7099,25 +7213,25 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>509</v>
+        <v>450</v>
       </c>
       <c r="C136" t="s">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="D136" t="s">
-        <v>514</v>
+        <v>452</v>
       </c>
       <c r="E136">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G136">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H136">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7126,25 +7240,25 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>76</v>
+        <v>453</v>
       </c>
       <c r="C137" t="s">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="D137" t="s">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F137">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G137">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7153,25 +7267,25 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>106</v>
+        <v>396</v>
       </c>
       <c r="C138" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="D138" t="s">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F138">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G138">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H138">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7180,25 +7294,25 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>107</v>
+        <v>508</v>
       </c>
       <c r="C139" t="s">
-        <v>218</v>
+        <v>510</v>
       </c>
       <c r="D139" t="s">
-        <v>219</v>
+        <v>513</v>
       </c>
       <c r="E139">
         <v>-10</v>
       </c>
       <c r="F139">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -7207,25 +7321,25 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>183</v>
+        <v>509</v>
       </c>
       <c r="C140" t="s">
-        <v>184</v>
+        <v>511</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>514</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F140">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G140">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H140">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.4">
@@ -7234,25 +7348,25 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="C141" t="s">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="D141" t="s">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="E141">
         <v>0</v>
       </c>
       <c r="F141">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G141">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H141">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.4">
@@ -7261,25 +7375,25 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C142" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="D142" t="s">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G142">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="H142">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -7288,25 +7402,25 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C143" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="D143" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F143">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G143">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H143">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7315,25 +7429,25 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>303</v>
+        <v>183</v>
       </c>
       <c r="C144" t="s">
-        <v>302</v>
+        <v>184</v>
       </c>
       <c r="D144" t="s">
-        <v>301</v>
+        <v>185</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G144">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H144">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7342,22 +7456,22 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>307</v>
+        <v>186</v>
       </c>
       <c r="C145" t="s">
-        <v>310</v>
+        <v>187</v>
       </c>
       <c r="D145" t="s">
-        <v>334</v>
+        <v>188</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G145">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H145">
         <v>10</v>
@@ -7369,22 +7483,22 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>308</v>
+        <v>90</v>
       </c>
       <c r="C146" t="s">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="D146" t="s">
-        <v>311</v>
+        <v>91</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G146">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="H146">
         <v>10</v>
@@ -7396,22 +7510,22 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="C147" t="s">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="D147" t="s">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G147">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H147">
         <v>15</v>
@@ -7423,25 +7537,25 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="C148" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D148" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G148">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H148">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -7450,13 +7564,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="C149" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="D149" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -7465,10 +7579,10 @@
         <v>15</v>
       </c>
       <c r="G149">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H149">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7477,13 +7591,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="C150" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="D150" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -7492,10 +7606,10 @@
         <v>15</v>
       </c>
       <c r="G150">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7504,13 +7618,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="C151" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D151" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -7519,7 +7633,7 @@
         <v>15</v>
       </c>
       <c r="G151">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H151">
         <v>15</v>
@@ -7531,13 +7645,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C152" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="D152" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -7546,7 +7660,7 @@
         <v>15</v>
       </c>
       <c r="G152">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H152">
         <v>15</v>
@@ -7558,13 +7672,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>499</v>
+        <v>326</v>
       </c>
       <c r="C153" t="s">
-        <v>500</v>
+        <v>327</v>
       </c>
       <c r="D153" t="s">
-        <v>501</v>
+        <v>328</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -7573,7 +7687,7 @@
         <v>15</v>
       </c>
       <c r="G153">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H153">
         <v>15</v>
@@ -7585,13 +7699,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C154" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="D154" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -7600,10 +7714,10 @@
         <v>15</v>
       </c>
       <c r="G154">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="H154">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7612,13 +7726,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>318</v>
+        <v>515</v>
       </c>
       <c r="C155" t="s">
-        <v>319</v>
+        <v>516</v>
       </c>
       <c r="D155" t="s">
-        <v>320</v>
+        <v>517</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -7627,10 +7741,10 @@
         <v>15</v>
       </c>
       <c r="G155">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="H155">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7639,25 +7753,25 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>430</v>
+        <v>518</v>
       </c>
       <c r="C156" t="s">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="D156" t="s">
-        <v>432</v>
+        <v>520</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G156">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H156">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7666,25 +7780,25 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>436</v>
+        <v>332</v>
       </c>
       <c r="C157" t="s">
-        <v>437</v>
+        <v>333</v>
       </c>
       <c r="D157" t="s">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G157">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H157">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7693,25 +7807,25 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>398</v>
+        <v>336</v>
       </c>
       <c r="C158" t="s">
+        <v>337</v>
+      </c>
+      <c r="D158" t="s">
+        <v>338</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>15</v>
+      </c>
+      <c r="G158">
         <v>400</v>
       </c>
-      <c r="D158" t="s">
-        <v>399</v>
-      </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-      <c r="F158">
-        <v>10</v>
-      </c>
-      <c r="G158">
-        <v>300</v>
-      </c>
       <c r="H158">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7720,25 +7834,25 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>397</v>
+        <v>499</v>
       </c>
       <c r="C159" t="s">
-        <v>401</v>
+        <v>500</v>
       </c>
       <c r="D159" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
       <c r="E159">
         <v>0</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G159">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H159">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7747,25 +7861,25 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="C160" t="s">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>317</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G160">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H160">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7774,25 +7888,25 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>405</v>
+        <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>320</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G161">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="H161">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7801,13 +7915,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C162" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -7816,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="G162">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H162">
         <v>10</v>
@@ -7828,13 +7942,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C163" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D163" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -7843,10 +7957,10 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H163">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -7855,13 +7969,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C164" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -7873,7 +7987,7 @@
         <v>300</v>
       </c>
       <c r="H164">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -7882,13 +7996,13 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="C165" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="D165" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -7900,7 +8014,7 @@
         <v>300</v>
       </c>
       <c r="H165">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -7909,25 +8023,25 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="C166" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="D166" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G166">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H166">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -7936,19 +8050,19 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C167" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="D167" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="E167">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F167">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G167">
         <v>300</v>
@@ -7963,25 +8077,25 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C168" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="E168">
         <v>0</v>
       </c>
       <c r="F168">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G168">
         <v>300</v>
       </c>
       <c r="H168">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -7990,13 +8104,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="C169" t="s">
-        <v>479</v>
+        <v>416</v>
       </c>
       <c r="D169" t="s">
-        <v>480</v>
+        <v>413</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8005,10 +8119,10 @@
         <v>10</v>
       </c>
       <c r="G169">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H169">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8017,13 +8131,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>481</v>
+        <v>414</v>
       </c>
       <c r="C170" t="s">
-        <v>482</v>
+        <v>415</v>
       </c>
       <c r="D170" t="s">
-        <v>483</v>
+        <v>417</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8032,10 +8146,10 @@
         <v>10</v>
       </c>
       <c r="G170">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H170">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8044,13 +8158,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>484</v>
+        <v>418</v>
       </c>
       <c r="C171" t="s">
-        <v>485</v>
+        <v>419</v>
       </c>
       <c r="D171" t="s">
-        <v>486</v>
+        <v>420</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8059,10 +8173,10 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H171">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8071,25 +8185,25 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>487</v>
+        <v>421</v>
       </c>
       <c r="C172" t="s">
-        <v>488</v>
+        <v>422</v>
       </c>
       <c r="D172" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
       <c r="F172">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G172">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="H172">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8098,25 +8212,25 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>490</v>
+        <v>424</v>
       </c>
       <c r="C173" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="D173" t="s">
-        <v>492</v>
+        <v>426</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F173">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G173">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H173">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8125,24 +8239,186 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="C174" t="s">
-        <v>86</v>
+        <v>434</v>
       </c>
       <c r="D174" t="s">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="E174">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F174">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G174">
         <v>300</v>
       </c>
       <c r="H174">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A175">
+        <f t="shared" si="0"/>
+        <v>173</v>
+      </c>
+      <c r="B175" t="s">
+        <v>478</v>
+      </c>
+      <c r="C175" t="s">
+        <v>479</v>
+      </c>
+      <c r="D175" t="s">
+        <v>480</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>10</v>
+      </c>
+      <c r="G175">
+        <v>80</v>
+      </c>
+      <c r="H175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A176">
+        <f t="shared" si="0"/>
+        <v>174</v>
+      </c>
+      <c r="B176" t="s">
+        <v>481</v>
+      </c>
+      <c r="C176" t="s">
+        <v>482</v>
+      </c>
+      <c r="D176" t="s">
+        <v>483</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>10</v>
+      </c>
+      <c r="G176">
+        <v>80</v>
+      </c>
+      <c r="H176">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A177">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="B177" t="s">
+        <v>484</v>
+      </c>
+      <c r="C177" t="s">
+        <v>485</v>
+      </c>
+      <c r="D177" t="s">
+        <v>486</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>10</v>
+      </c>
+      <c r="G177">
+        <v>80</v>
+      </c>
+      <c r="H177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A178">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+      <c r="B178" t="s">
+        <v>487</v>
+      </c>
+      <c r="C178" t="s">
+        <v>488</v>
+      </c>
+      <c r="D178" t="s">
+        <v>489</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>10</v>
+      </c>
+      <c r="G178">
+        <v>80</v>
+      </c>
+      <c r="H178">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A179">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="B179" t="s">
+        <v>490</v>
+      </c>
+      <c r="C179" t="s">
+        <v>491</v>
+      </c>
+      <c r="D179" t="s">
+        <v>492</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>10</v>
+      </c>
+      <c r="G179">
+        <v>80</v>
+      </c>
+      <c r="H179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A180">
+        <f t="shared" si="0"/>
+        <v>178</v>
+      </c>
+      <c r="B180" t="s">
+        <v>85</v>
+      </c>
+      <c r="C180" t="s">
+        <v>86</v>
+      </c>
+      <c r="D180" t="s">
+        <v>87</v>
+      </c>
+      <c r="E180">
+        <v>150</v>
+      </c>
+      <c r="F180">
+        <v>100</v>
+      </c>
+      <c r="G180">
+        <v>300</v>
+      </c>
+      <c r="H180">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C042F73C-DF47-4357-82E8-B25A0624BDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BA5CD3-0E06-4E48-8E47-D683E8CF026F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3030" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="536">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -3169,6 +3169,27 @@
   </si>
   <si>
     <t>ジェラートッピング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KohakuCandyGlow</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>琥珀糖</t>
+    <rPh sb="0" eb="3">
+      <t>コハクトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光る宝石の</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウセキ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3552,7 +3573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3591,7 +3612,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A180" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A181" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -4879,7 +4900,7 @@
         <v>30</v>
       </c>
       <c r="G49">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -4906,7 +4927,7 @@
         <v>30</v>
       </c>
       <c r="G50">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -5095,7 +5116,7 @@
         <v>30</v>
       </c>
       <c r="G57">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H57">
         <v>20</v>
@@ -5107,25 +5128,25 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>254</v>
+        <v>533</v>
       </c>
       <c r="C58" t="s">
-        <v>255</v>
+        <v>534</v>
       </c>
       <c r="D58" t="s">
-        <v>256</v>
+        <v>535</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G58">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="H58">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -5134,25 +5155,25 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C59" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G59">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -5161,22 +5182,22 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
+        <v>3</v>
+      </c>
+      <c r="G60">
         <v>50</v>
-      </c>
-      <c r="G60">
-        <v>300</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -5188,22 +5209,22 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="C61" t="s">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G61">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -5215,25 +5236,25 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>222</v>
       </c>
       <c r="D62" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H62">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
@@ -5242,25 +5263,25 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>283</v>
+        <v>223</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G63">
         <v>120</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
@@ -5269,25 +5290,25 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>282</v>
       </c>
       <c r="D64" t="s">
-        <v>34</v>
+        <v>283</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G64">
         <v>120</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
@@ -5296,25 +5317,25 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G65">
         <v>120</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.4">
@@ -5323,25 +5344,25 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>169</v>
+        <v>94</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G66">
         <v>120</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
@@ -5350,19 +5371,19 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="G67">
         <v>120</v>
@@ -5377,13 +5398,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -5404,13 +5425,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -5431,13 +5452,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C70" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -5458,13 +5479,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -5485,13 +5506,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D72" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -5512,13 +5533,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D73" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5539,13 +5560,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5566,13 +5587,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="C75" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="D75" t="s">
-        <v>190</v>
+        <v>68</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5593,13 +5614,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5620,13 +5641,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>260</v>
+        <v>69</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>97</v>
       </c>
       <c r="D77" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5647,16 +5668,16 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="D78" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="E78">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>5</v>
@@ -5665,7 +5686,7 @@
         <v>120</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.4">
@@ -5674,25 +5695,25 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C79" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D79" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F79">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G79">
         <v>120</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
@@ -5701,13 +5722,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>496</v>
+        <v>275</v>
       </c>
       <c r="C80" t="s">
-        <v>497</v>
+        <v>276</v>
       </c>
       <c r="D80" t="s">
-        <v>498</v>
+        <v>277</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5728,22 +5749,22 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>59</v>
+        <v>496</v>
       </c>
       <c r="C81" t="s">
-        <v>58</v>
+        <v>497</v>
       </c>
       <c r="D81" t="s">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G81">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5755,19 +5776,19 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="D82" t="s">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G82">
         <v>50</v>
@@ -5782,25 +5803,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="C83" t="s">
-        <v>427</v>
+        <v>140</v>
       </c>
       <c r="D83" t="s">
-        <v>429</v>
+        <v>224</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G83">
         <v>50</v>
       </c>
       <c r="H83">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5809,25 +5830,25 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>321</v>
+        <v>428</v>
       </c>
       <c r="C84" t="s">
-        <v>322</v>
+        <v>427</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>429</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G84">
         <v>50</v>
       </c>
       <c r="H84">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -5836,25 +5857,25 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>33</v>
+        <v>321</v>
       </c>
       <c r="C85" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="D85" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G85">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H85">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.4">
@@ -5863,13 +5884,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>456</v>
+        <v>33</v>
       </c>
       <c r="C86" t="s">
-        <v>457</v>
+        <v>210</v>
       </c>
       <c r="D86" t="s">
-        <v>458</v>
+        <v>209</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5881,7 +5902,7 @@
         <v>120</v>
       </c>
       <c r="H86">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.4">
@@ -5890,25 +5911,25 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>456</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>457</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G87">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H87">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.4">
@@ -5917,25 +5938,25 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>530</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>531</v>
+        <v>100</v>
       </c>
       <c r="D88" t="s">
-        <v>532</v>
+        <v>80</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G88">
         <v>240</v>
       </c>
       <c r="H88">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -5944,25 +5965,25 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>530</v>
       </c>
       <c r="C89" t="s">
-        <v>175</v>
+        <v>531</v>
       </c>
       <c r="D89" t="s">
-        <v>179</v>
+        <v>532</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G89">
         <v>240</v>
       </c>
       <c r="H89">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.4">
@@ -5971,19 +5992,19 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G90">
         <v>240</v>
@@ -5998,13 +6019,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -6025,19 +6046,19 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C92" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D92" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G92">
         <v>240</v>
@@ -6052,13 +6073,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D93" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -6079,13 +6100,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -6106,13 +6127,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>525</v>
+        <v>195</v>
       </c>
       <c r="C95" t="s">
-        <v>521</v>
+        <v>194</v>
       </c>
       <c r="D95" t="s">
-        <v>523</v>
+        <v>212</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6133,13 +6154,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C96" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D96" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6160,19 +6181,19 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>257</v>
+        <v>526</v>
       </c>
       <c r="C97" t="s">
-        <v>258</v>
+        <v>522</v>
       </c>
       <c r="D97" t="s">
-        <v>258</v>
+        <v>524</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G97">
         <v>240</v>
@@ -6187,25 +6208,25 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="D98" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G98">
         <v>240</v>
       </c>
       <c r="H98">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -6214,25 +6235,25 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>527</v>
+        <v>197</v>
       </c>
       <c r="C99" t="s">
-        <v>528</v>
+        <v>196</v>
       </c>
       <c r="D99" t="s">
-        <v>529</v>
+        <v>211</v>
       </c>
       <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G99">
         <v>240</v>
       </c>
       <c r="H99">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -6241,25 +6262,25 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>38</v>
+        <v>527</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>528</v>
       </c>
       <c r="D100" t="s">
-        <v>44</v>
+        <v>529</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G100">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -6268,25 +6289,25 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="D101" t="s">
-        <v>446</v>
+        <v>44</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G101">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="H101">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
@@ -6295,13 +6316,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>463</v>
+        <v>40</v>
       </c>
       <c r="C102" t="s">
-        <v>461</v>
+        <v>41</v>
       </c>
       <c r="D102" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6310,10 +6331,10 @@
         <v>10</v>
       </c>
       <c r="G102">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H102">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
@@ -6322,13 +6343,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C103" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D103" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6349,13 +6370,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C104" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D104" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6376,13 +6397,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C105" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D105" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6403,13 +6424,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C106" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D106" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6418,10 +6439,10 @@
         <v>10</v>
       </c>
       <c r="G106">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="H106">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
@@ -6430,13 +6451,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="C107" t="s">
-        <v>503</v>
+        <v>474</v>
       </c>
       <c r="D107" t="s">
-        <v>503</v>
+        <v>474</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6445,10 +6466,10 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H107">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -6457,13 +6478,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C108" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D108" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6484,13 +6505,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="C109" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="D109" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6499,10 +6520,10 @@
         <v>10</v>
       </c>
       <c r="G109">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H109">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -6511,13 +6532,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="C110" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="D110" t="s">
-        <v>225</v>
+        <v>477</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6526,10 +6547,10 @@
         <v>10</v>
       </c>
       <c r="G110">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="H110">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
@@ -6538,25 +6559,25 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C111" t="s">
-        <v>89</v>
+        <v>214</v>
       </c>
       <c r="D111" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="E111">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>10</v>
       </c>
       <c r="G111">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H111">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
@@ -6565,22 +6586,22 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C112" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F112">
         <v>10</v>
       </c>
       <c r="G112">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="H112">
         <v>5</v>
@@ -6592,25 +6613,25 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C113" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D113" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G113">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H113">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
@@ -6619,25 +6640,25 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C114" t="s">
-        <v>237</v>
+        <v>144</v>
       </c>
       <c r="D114" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G114">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H114">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
@@ -6646,25 +6667,25 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C115" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D115" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G115">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H115">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
@@ -6673,22 +6694,22 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D116" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G116">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -6700,25 +6721,25 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C117" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="D117" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
+        <v>6</v>
+      </c>
+      <c r="G117">
+        <v>70</v>
+      </c>
+      <c r="H117">
         <v>5</v>
-      </c>
-      <c r="G117">
-        <v>120</v>
-      </c>
-      <c r="H117">
-        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
@@ -6727,25 +6748,25 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="C118" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D118" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G118">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H118">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
@@ -6754,25 +6775,25 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C119" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D119" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G119">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H119">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
@@ -6781,13 +6802,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="D120" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6799,7 +6820,7 @@
         <v>350</v>
       </c>
       <c r="H120">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
@@ -6808,25 +6829,25 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="C121" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="D121" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G121">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H121">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
@@ -6835,13 +6856,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>393</v>
+        <v>155</v>
       </c>
       <c r="C122" t="s">
-        <v>394</v>
+        <v>154</v>
       </c>
       <c r="D122" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6850,10 +6871,10 @@
         <v>35</v>
       </c>
       <c r="G122">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H122">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
@@ -6862,25 +6883,25 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>74</v>
+        <v>393</v>
       </c>
       <c r="C123" t="s">
-        <v>75</v>
+        <v>394</v>
       </c>
       <c r="D123" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="E123">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F123">
-        <v>-5</v>
+        <v>35</v>
       </c>
       <c r="G123">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="H123">
-        <v>-10</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -6889,13 +6910,13 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>387</v>
+        <v>74</v>
       </c>
       <c r="C124" t="s">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="D124" t="s">
-        <v>389</v>
+        <v>121</v>
       </c>
       <c r="E124">
         <v>-30</v>
@@ -6916,25 +6937,25 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C125" t="s">
-        <v>449</v>
+        <v>388</v>
       </c>
       <c r="D125" t="s">
-        <v>448</v>
+        <v>389</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F125">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="G125">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H125">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
@@ -6943,25 +6964,25 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>264</v>
+        <v>447</v>
       </c>
       <c r="C126" t="s">
-        <v>263</v>
+        <v>449</v>
       </c>
       <c r="D126" t="s">
-        <v>265</v>
+        <v>448</v>
       </c>
       <c r="E126">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G126">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H126">
-        <v>-10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
@@ -6970,13 +6991,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="C127" t="s">
-        <v>391</v>
+        <v>263</v>
       </c>
       <c r="D127" t="s">
-        <v>392</v>
+        <v>265</v>
       </c>
       <c r="E127">
         <v>-20</v>
@@ -6997,25 +7018,25 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="C128" t="s">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>392</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F128">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="G128">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H128">
-        <v>3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
@@ -7024,25 +7045,25 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="C129" t="s">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="D129" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G129">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H129">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -7051,13 +7072,13 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C130" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D130" t="s">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7069,7 +7090,7 @@
         <v>300</v>
       </c>
       <c r="H130">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -7078,13 +7099,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C131" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D131" t="s">
-        <v>346</v>
+        <v>442</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7096,7 +7117,7 @@
         <v>300</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -7105,13 +7126,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C132" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D132" t="s">
-        <v>443</v>
+        <v>346</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7123,7 +7144,7 @@
         <v>300</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7132,13 +7153,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C133" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D133" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7147,10 +7168,10 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H133">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7159,13 +7180,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C134" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D134" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7174,10 +7195,10 @@
         <v>10</v>
       </c>
       <c r="G134">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H134">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7186,13 +7207,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C135" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D135" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -7204,7 +7225,7 @@
         <v>700</v>
       </c>
       <c r="H135">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7213,13 +7234,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>450</v>
+        <v>353</v>
       </c>
       <c r="C136" t="s">
-        <v>451</v>
+        <v>354</v>
       </c>
       <c r="D136" t="s">
-        <v>452</v>
+        <v>355</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -7228,10 +7249,10 @@
         <v>10</v>
       </c>
       <c r="G136">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="H136">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7240,25 +7261,25 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C137" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D137" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E137">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>10</v>
       </c>
       <c r="G137">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H137">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7267,25 +7288,25 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="C138" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="D138" t="s">
-        <v>512</v>
+        <v>455</v>
       </c>
       <c r="E138">
         <v>-10</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G138">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H138">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7294,13 +7315,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>508</v>
+        <v>396</v>
       </c>
       <c r="C139" t="s">
-        <v>510</v>
+        <v>439</v>
       </c>
       <c r="D139" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E139">
         <v>-10</v>
@@ -7321,13 +7342,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C140" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D140" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E140">
         <v>-10</v>
@@ -7348,22 +7369,22 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>76</v>
+        <v>509</v>
       </c>
       <c r="C141" t="s">
-        <v>77</v>
+        <v>511</v>
       </c>
       <c r="D141" t="s">
-        <v>78</v>
+        <v>514</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F141">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H141">
         <v>2</v>
@@ -7375,25 +7396,25 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C142" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="D142" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G142">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H142">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.4">
@@ -7402,25 +7423,25 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C143" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="D143" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E143">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F143">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G143">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7429,25 +7450,25 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="C144" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D144" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F144">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G144">
         <v>150</v>
       </c>
       <c r="H144">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7456,13 +7477,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C145" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D145" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -7483,22 +7504,22 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="C146" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="D146" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G146">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H146">
         <v>10</v>
@@ -7510,25 +7531,25 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C147" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D147" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
+        <v>10</v>
+      </c>
+      <c r="G147">
         <v>30</v>
       </c>
-      <c r="G147">
-        <v>300</v>
-      </c>
       <c r="H147">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.4">
@@ -7537,25 +7558,25 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="C148" t="s">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="D148" t="s">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G148">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="H148">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -7564,25 +7585,25 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C149" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D149" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G149">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="H149">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7591,13 +7612,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C150" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D150" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -7618,13 +7639,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C151" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D151" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -7633,10 +7654,10 @@
         <v>15</v>
       </c>
       <c r="G151">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="H151">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7645,13 +7666,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C152" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D152" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -7672,13 +7693,13 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C153" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D153" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -7699,13 +7720,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C154" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D154" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -7726,13 +7747,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>515</v>
+        <v>329</v>
       </c>
       <c r="C155" t="s">
-        <v>516</v>
+        <v>331</v>
       </c>
       <c r="D155" t="s">
-        <v>517</v>
+        <v>330</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -7753,13 +7774,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C156" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D156" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -7780,13 +7801,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>332</v>
+        <v>518</v>
       </c>
       <c r="C157" t="s">
-        <v>333</v>
+        <v>519</v>
       </c>
       <c r="D157" t="s">
-        <v>335</v>
+        <v>520</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -7795,7 +7816,7 @@
         <v>15</v>
       </c>
       <c r="G157">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H157">
         <v>15</v>
@@ -7807,13 +7828,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C158" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D158" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -7834,13 +7855,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>499</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>500</v>
+        <v>337</v>
       </c>
       <c r="D159" t="s">
-        <v>501</v>
+        <v>338</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -7861,13 +7882,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>315</v>
+        <v>499</v>
       </c>
       <c r="C160" t="s">
-        <v>316</v>
+        <v>500</v>
       </c>
       <c r="D160" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -7876,10 +7897,10 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="H160">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7888,13 +7909,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C161" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D161" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -7915,25 +7936,25 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>430</v>
+        <v>318</v>
       </c>
       <c r="C162" t="s">
-        <v>431</v>
+        <v>319</v>
       </c>
       <c r="D162" t="s">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G162">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="H162">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7942,13 +7963,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C163" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D163" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -7957,10 +7978,10 @@
         <v>10</v>
       </c>
       <c r="G163">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H163">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -7969,13 +7990,13 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C164" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="D164" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -7984,10 +8005,10 @@
         <v>10</v>
       </c>
       <c r="G164">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H164">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -7996,13 +8017,13 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C165" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -8014,7 +8035,7 @@
         <v>300</v>
       </c>
       <c r="H165">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8023,13 +8044,13 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C166" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D166" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -8050,13 +8071,13 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C167" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -8068,7 +8089,7 @@
         <v>300</v>
       </c>
       <c r="H167">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8077,13 +8098,13 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C168" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D168" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -8104,13 +8125,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C169" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8131,13 +8152,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C170" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D170" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8149,7 +8170,7 @@
         <v>300</v>
       </c>
       <c r="H170">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8158,13 +8179,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C171" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D171" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8176,7 +8197,7 @@
         <v>300</v>
       </c>
       <c r="H171">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8185,25 +8206,25 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C172" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D172" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
       <c r="F172">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G172">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H172">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8212,25 +8233,25 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C173" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D173" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E173">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F173">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="G173">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H173">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8239,25 +8260,25 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C174" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F174">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="G174">
         <v>300</v>
       </c>
       <c r="H174">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8266,25 +8287,25 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="C175" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="D175" t="s">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="F175">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G175">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H175">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8293,13 +8314,13 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C176" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D176" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -8311,7 +8332,7 @@
         <v>80</v>
       </c>
       <c r="H176">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8320,13 +8341,13 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C177" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D177" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -8338,7 +8359,7 @@
         <v>80</v>
       </c>
       <c r="H177">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8347,13 +8368,13 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C178" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D178" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -8365,7 +8386,7 @@
         <v>80</v>
       </c>
       <c r="H178">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8374,13 +8395,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C179" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D179" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -8392,7 +8413,7 @@
         <v>80</v>
       </c>
       <c r="H179">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8401,24 +8422,51 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
+        <v>490</v>
+      </c>
+      <c r="C180" t="s">
+        <v>491</v>
+      </c>
+      <c r="D180" t="s">
+        <v>492</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>10</v>
+      </c>
+      <c r="G180">
+        <v>80</v>
+      </c>
+      <c r="H180">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A181">
+        <f t="shared" si="0"/>
+        <v>179</v>
+      </c>
+      <c r="B181" t="s">
         <v>85</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>86</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D181" t="s">
         <v>87</v>
       </c>
-      <c r="E180">
+      <c r="E181">
         <v>150</v>
       </c>
-      <c r="F180">
+      <c r="F181">
         <v>100</v>
       </c>
-      <c r="G180">
+      <c r="G181">
         <v>300</v>
       </c>
-      <c r="H180">
+      <c r="H181">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BA5CD3-0E06-4E48-8E47-D683E8CF026F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D43D12-56FC-410E-9EF4-DF6A5991E832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7435,13 +7435,13 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G143">
         <v>300</v>
       </c>
       <c r="H143">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7462,7 +7462,7 @@
         <v>-10</v>
       </c>
       <c r="F144">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G144">
         <v>150</v>
@@ -7603,7 +7603,7 @@
         <v>70</v>
       </c>
       <c r="H149">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7657,7 +7657,7 @@
         <v>250</v>
       </c>
       <c r="H151">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D43D12-56FC-410E-9EF4-DF6A5991E832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A4C11-30C3-4C23-BC03-26E5FA9B8AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3060" yWindow="945" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A4C11-30C3-4C23-BC03-26E5FA9B8AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89874F6-8875-4263-91D9-7D175EE3B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="945" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2865" yWindow="1005" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6460,7 +6460,7 @@
         <v>474</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -6487,7 +6487,7 @@
         <v>503</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F108">
         <v>10</v>
@@ -6514,7 +6514,7 @@
         <v>504</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F109">
         <v>10</v>
@@ -7081,7 +7081,7 @@
         <v>341</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F130">
         <v>10</v>
@@ -7108,7 +7108,7 @@
         <v>442</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F131">
         <v>10</v>
@@ -7135,7 +7135,7 @@
         <v>346</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F132">
         <v>10</v>
@@ -7162,7 +7162,7 @@
         <v>443</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F133">
         <v>10</v>
@@ -7189,7 +7189,7 @@
         <v>445</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F134">
         <v>10</v>
@@ -7216,7 +7216,7 @@
         <v>444</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F135">
         <v>10</v>
@@ -7243,7 +7243,7 @@
         <v>355</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -7270,7 +7270,7 @@
         <v>452</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F137">
         <v>10</v>
@@ -7594,7 +7594,7 @@
         <v>301</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F149">
         <v>10</v>
@@ -7621,7 +7621,7 @@
         <v>334</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F150">
         <v>15</v>
@@ -7648,7 +7648,7 @@
         <v>311</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F151">
         <v>15</v>
@@ -7675,7 +7675,7 @@
         <v>324</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F152">
         <v>15</v>
@@ -7702,7 +7702,7 @@
         <v>314</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F153">
         <v>15</v>
@@ -7729,7 +7729,7 @@
         <v>328</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F154">
         <v>15</v>
@@ -7756,7 +7756,7 @@
         <v>330</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F155">
         <v>15</v>
@@ -7783,7 +7783,7 @@
         <v>517</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F156">
         <v>15</v>
@@ -7810,7 +7810,7 @@
         <v>520</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F157">
         <v>15</v>
@@ -7837,7 +7837,7 @@
         <v>335</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F158">
         <v>15</v>
@@ -7864,7 +7864,7 @@
         <v>338</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F159">
         <v>15</v>
@@ -7891,7 +7891,7 @@
         <v>501</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F160">
         <v>15</v>
@@ -7918,7 +7918,7 @@
         <v>317</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F161">
         <v>15</v>
@@ -7945,7 +7945,7 @@
         <v>320</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F162">
         <v>15</v>
@@ -7972,7 +7972,7 @@
         <v>432</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F163">
         <v>10</v>
@@ -7999,7 +7999,7 @@
         <v>438</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F164">
         <v>10</v>
@@ -8026,7 +8026,7 @@
         <v>399</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F165">
         <v>10</v>
@@ -8053,7 +8053,7 @@
         <v>411</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F166">
         <v>10</v>
@@ -8080,7 +8080,7 @@
         <v>404</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F167">
         <v>10</v>
@@ -8107,7 +8107,7 @@
         <v>407</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F168">
         <v>10</v>
@@ -8134,7 +8134,7 @@
         <v>410</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F169">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>413</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F170">
         <v>10</v>
@@ -8188,7 +8188,7 @@
         <v>417</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F171">
         <v>10</v>
@@ -8215,7 +8215,7 @@
         <v>420</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F172">
         <v>10</v>
@@ -8242,7 +8242,7 @@
         <v>423</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F173">
         <v>20</v>
@@ -8296,7 +8296,7 @@
         <v>435</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F175">
         <v>15</v>
@@ -8323,7 +8323,7 @@
         <v>480</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F176">
         <v>10</v>
@@ -8350,7 +8350,7 @@
         <v>483</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F177">
         <v>10</v>
@@ -8377,7 +8377,7 @@
         <v>486</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F178">
         <v>10</v>
@@ -8404,7 +8404,7 @@
         <v>489</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F179">
         <v>10</v>
@@ -8431,7 +8431,7 @@
         <v>492</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F180">
         <v>10</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89874F6-8875-4263-91D9-7D175EE3B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A867CAF8-E1F3-46BE-AFD0-0D5F8AB0D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="1005" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3712,7 +3712,7 @@
         <v>20</v>
       </c>
       <c r="G5">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -3901,7 +3901,7 @@
         <v>20</v>
       </c>
       <c r="G12">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -3928,7 +3928,7 @@
         <v>20</v>
       </c>
       <c r="G13">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>13</v>
@@ -4036,7 +4036,7 @@
         <v>10</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17">
         <v>8</v>
@@ -4063,7 +4063,7 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>12</v>
@@ -4090,7 +4090,7 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H19">
         <v>15</v>
@@ -4144,7 +4144,7 @@
         <v>10</v>
       </c>
       <c r="G21">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -4171,7 +4171,7 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H22">
         <v>6</v>
@@ -4198,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -4306,7 +4306,7 @@
         <v>20</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -4333,7 +4333,7 @@
         <v>20</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -4360,7 +4360,7 @@
         <v>20</v>
       </c>
       <c r="G29">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -4387,7 +4387,7 @@
         <v>50</v>
       </c>
       <c r="G30">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H30">
         <v>9</v>
@@ -4468,7 +4468,7 @@
         <v>50</v>
       </c>
       <c r="G33">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -4495,7 +4495,7 @@
         <v>50</v>
       </c>
       <c r="G34">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -4549,7 +4549,7 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -4576,7 +4576,7 @@
         <v>30</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H37">
         <v>9</v>
@@ -4603,7 +4603,7 @@
         <v>8</v>
       </c>
       <c r="G38">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>3</v>
@@ -4846,7 +4846,7 @@
         <v>15</v>
       </c>
       <c r="G47">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -4873,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="G48">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -4900,7 +4900,7 @@
         <v>30</v>
       </c>
       <c r="G49">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -4927,7 +4927,7 @@
         <v>30</v>
       </c>
       <c r="G50">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -5008,7 +5008,7 @@
         <v>15</v>
       </c>
       <c r="G53">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H53">
         <v>8</v>
@@ -5035,7 +5035,7 @@
         <v>10</v>
       </c>
       <c r="G54">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="H54">
         <v>7</v>
@@ -5062,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="G55">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -5170,7 +5170,7 @@
         <v>50</v>
       </c>
       <c r="G59">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="H59">
         <v>15</v>
@@ -5332,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -5359,7 +5359,7 @@
         <v>5</v>
       </c>
       <c r="G66">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -5386,7 +5386,7 @@
         <v>30</v>
       </c>
       <c r="G67">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -5413,7 +5413,7 @@
         <v>5</v>
       </c>
       <c r="G68">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -5440,7 +5440,7 @@
         <v>5</v>
       </c>
       <c r="G69">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -5467,7 +5467,7 @@
         <v>5</v>
       </c>
       <c r="G70">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5494,7 +5494,7 @@
         <v>5</v>
       </c>
       <c r="G71">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -5521,7 +5521,7 @@
         <v>5</v>
       </c>
       <c r="G72">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -5548,7 +5548,7 @@
         <v>5</v>
       </c>
       <c r="G73">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -5575,7 +5575,7 @@
         <v>5</v>
       </c>
       <c r="G74">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -5602,7 +5602,7 @@
         <v>5</v>
       </c>
       <c r="G75">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -5629,7 +5629,7 @@
         <v>5</v>
       </c>
       <c r="G76">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -5656,7 +5656,7 @@
         <v>5</v>
       </c>
       <c r="G77">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -5683,7 +5683,7 @@
         <v>5</v>
       </c>
       <c r="G78">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -5710,7 +5710,7 @@
         <v>5</v>
       </c>
       <c r="G79">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -5737,7 +5737,7 @@
         <v>20</v>
       </c>
       <c r="G80">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -5764,7 +5764,7 @@
         <v>20</v>
       </c>
       <c r="G81">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -5980,7 +5980,7 @@
         <v>20</v>
       </c>
       <c r="G89">
-        <v>240</v>
+        <v>480</v>
       </c>
       <c r="H89">
         <v>20</v>
@@ -6331,7 +6331,7 @@
         <v>10</v>
       </c>
       <c r="G102">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H102">
         <v>12</v>
@@ -6358,7 +6358,7 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="H103">
         <v>20</v>
@@ -6385,7 +6385,7 @@
         <v>10</v>
       </c>
       <c r="G104">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="H104">
         <v>20</v>
@@ -6412,7 +6412,7 @@
         <v>10</v>
       </c>
       <c r="G105">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="H105">
         <v>20</v>
@@ -6439,7 +6439,7 @@
         <v>10</v>
       </c>
       <c r="G106">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="H106">
         <v>20</v>
@@ -6493,7 +6493,7 @@
         <v>10</v>
       </c>
       <c r="G108">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H108">
         <v>12</v>
@@ -6520,7 +6520,7 @@
         <v>10</v>
       </c>
       <c r="G109">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H109">
         <v>12</v>
@@ -6547,7 +6547,7 @@
         <v>10</v>
       </c>
       <c r="G110">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H110">
         <v>10</v>
@@ -6628,7 +6628,7 @@
         <v>10</v>
       </c>
       <c r="G113">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -6655,7 +6655,7 @@
         <v>12</v>
       </c>
       <c r="G114">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H114">
         <v>7</v>
@@ -6682,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="G115">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H115">
         <v>6</v>
@@ -6709,7 +6709,7 @@
         <v>15</v>
       </c>
       <c r="G116">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -6736,7 +6736,7 @@
         <v>6</v>
       </c>
       <c r="G117">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H117">
         <v>5</v>
@@ -6763,7 +6763,7 @@
         <v>5</v>
       </c>
       <c r="G118">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H118">
         <v>3</v>
@@ -6790,7 +6790,7 @@
         <v>20</v>
       </c>
       <c r="G119">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="H119">
         <v>7</v>
@@ -6817,7 +6817,7 @@
         <v>25</v>
       </c>
       <c r="G120">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="H120">
         <v>6</v>
@@ -6844,7 +6844,7 @@
         <v>25</v>
       </c>
       <c r="G121">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="H121">
         <v>7</v>
@@ -6871,7 +6871,7 @@
         <v>35</v>
       </c>
       <c r="G122">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H122">
         <v>6</v>
@@ -6898,7 +6898,7 @@
         <v>35</v>
       </c>
       <c r="G123">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H123">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>-5</v>
       </c>
       <c r="G124">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H124">
         <v>-10</v>
@@ -6952,7 +6952,7 @@
         <v>-5</v>
       </c>
       <c r="G125">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H125">
         <v>-10</v>
@@ -6979,7 +6979,7 @@
         <v>10</v>
       </c>
       <c r="G126">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H126">
         <v>5</v>
@@ -7006,7 +7006,7 @@
         <v>-10</v>
       </c>
       <c r="G127">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H127">
         <v>-10</v>
@@ -7033,7 +7033,7 @@
         <v>-10</v>
       </c>
       <c r="G128">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H128">
         <v>-10</v>
@@ -7087,7 +7087,7 @@
         <v>10</v>
       </c>
       <c r="G130">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H130">
         <v>20</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H131">
         <v>20</v>
@@ -7141,7 +7141,7 @@
         <v>10</v>
       </c>
       <c r="G132">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H132">
         <v>20</v>
@@ -7168,7 +7168,7 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H133">
         <v>20</v>
@@ -7195,7 +7195,7 @@
         <v>10</v>
       </c>
       <c r="G134">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H134">
         <v>20</v>
@@ -7222,7 +7222,7 @@
         <v>10</v>
       </c>
       <c r="G135">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H135">
         <v>20</v>
@@ -7249,7 +7249,7 @@
         <v>10</v>
       </c>
       <c r="G136">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H136">
         <v>20</v>
@@ -7303,7 +7303,7 @@
         <v>10</v>
       </c>
       <c r="G138">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H138">
         <v>20</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="G139">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H139">
         <v>2</v>
@@ -7357,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="G140">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H140">
         <v>2</v>
@@ -7384,7 +7384,7 @@
         <v>0</v>
       </c>
       <c r="G141">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H141">
         <v>2</v>
@@ -7465,7 +7465,7 @@
         <v>30</v>
       </c>
       <c r="G144">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H144">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>20</v>
       </c>
       <c r="G145">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H145">
         <v>10</v>
@@ -7519,7 +7519,7 @@
         <v>20</v>
       </c>
       <c r="G146">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H146">
         <v>10</v>
@@ -7627,7 +7627,7 @@
         <v>15</v>
       </c>
       <c r="G150">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H150">
         <v>10</v>
@@ -7654,7 +7654,7 @@
         <v>15</v>
       </c>
       <c r="G151">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="H151">
         <v>12</v>
@@ -7681,7 +7681,7 @@
         <v>15</v>
       </c>
       <c r="G152">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H152">
         <v>15</v>
@@ -7708,7 +7708,7 @@
         <v>15</v>
       </c>
       <c r="G153">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="H153">
         <v>15</v>
@@ -7735,7 +7735,7 @@
         <v>15</v>
       </c>
       <c r="G154">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="H154">
         <v>15</v>
@@ -7762,7 +7762,7 @@
         <v>15</v>
       </c>
       <c r="G155">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="H155">
         <v>15</v>
@@ -7789,7 +7789,7 @@
         <v>15</v>
       </c>
       <c r="G156">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="H156">
         <v>15</v>
@@ -7816,7 +7816,7 @@
         <v>15</v>
       </c>
       <c r="G157">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="H157">
         <v>15</v>
@@ -7843,7 +7843,7 @@
         <v>15</v>
       </c>
       <c r="G158">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H158">
         <v>15</v>
@@ -7870,7 +7870,7 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H159">
         <v>15</v>
@@ -7897,7 +7897,7 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H160">
         <v>15</v>
@@ -7924,7 +7924,7 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="H161">
         <v>20</v>
@@ -7951,7 +7951,7 @@
         <v>15</v>
       </c>
       <c r="G162">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="H162">
         <v>20</v>
@@ -8005,7 +8005,7 @@
         <v>10</v>
       </c>
       <c r="G164">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H164">
         <v>20</v>
@@ -8032,7 +8032,7 @@
         <v>10</v>
       </c>
       <c r="G165">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H165">
         <v>12</v>
@@ -8059,7 +8059,7 @@
         <v>10</v>
       </c>
       <c r="G166">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H166">
         <v>9</v>
@@ -8086,7 +8086,7 @@
         <v>10</v>
       </c>
       <c r="G167">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H167">
         <v>9</v>
@@ -8113,7 +8113,7 @@
         <v>10</v>
       </c>
       <c r="G168">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H168">
         <v>10</v>
@@ -8140,7 +8140,7 @@
         <v>10</v>
       </c>
       <c r="G169">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H169">
         <v>10</v>
@@ -8167,7 +8167,7 @@
         <v>10</v>
       </c>
       <c r="G170">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H170">
         <v>10</v>
@@ -8194,7 +8194,7 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H171">
         <v>11</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G172">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H172">
         <v>10</v>
@@ -8248,7 +8248,7 @@
         <v>20</v>
       </c>
       <c r="G173">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H173">
         <v>20</v>
@@ -8275,7 +8275,7 @@
         <v>-10</v>
       </c>
       <c r="G174">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H174">
         <v>10</v>
@@ -8302,7 +8302,7 @@
         <v>15</v>
       </c>
       <c r="G175">
-        <v>300</v>
+        <v>170</v>
       </c>
       <c r="H175">
         <v>20</v>
@@ -8329,7 +8329,7 @@
         <v>10</v>
       </c>
       <c r="G176">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H176">
         <v>15</v>
@@ -8356,7 +8356,7 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H177">
         <v>15</v>
@@ -8383,7 +8383,7 @@
         <v>10</v>
       </c>
       <c r="G178">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H178">
         <v>15</v>
@@ -8410,7 +8410,7 @@
         <v>10</v>
       </c>
       <c r="G179">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H179">
         <v>15</v>
@@ -8437,7 +8437,7 @@
         <v>10</v>
       </c>
       <c r="G180">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H180">
         <v>25</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A867CAF8-E1F3-46BE-AFD0-0D5F8AB0D527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D2EE1-24B4-4DA5-B280-EFD114405800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6550,7 +6550,7 @@
         <v>200</v>
       </c>
       <c r="H110">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
@@ -6946,7 +6946,7 @@
         <v>389</v>
       </c>
       <c r="E125">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="F125">
         <v>-5</v>
@@ -6973,7 +6973,7 @@
         <v>448</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F126">
         <v>10</v>
@@ -7081,7 +7081,7 @@
         <v>341</v>
       </c>
       <c r="E130">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F130">
         <v>10</v>
@@ -7108,7 +7108,7 @@
         <v>442</v>
       </c>
       <c r="E131">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F131">
         <v>10</v>
@@ -7135,7 +7135,7 @@
         <v>346</v>
       </c>
       <c r="E132">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F132">
         <v>10</v>
@@ -7162,7 +7162,7 @@
         <v>443</v>
       </c>
       <c r="E133">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F133">
         <v>10</v>
@@ -7189,7 +7189,7 @@
         <v>445</v>
       </c>
       <c r="E134">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F134">
         <v>10</v>
@@ -7216,7 +7216,7 @@
         <v>444</v>
       </c>
       <c r="E135">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F135">
         <v>10</v>
@@ -7243,7 +7243,7 @@
         <v>355</v>
       </c>
       <c r="E136">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -7270,7 +7270,7 @@
         <v>452</v>
       </c>
       <c r="E137">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F137">
         <v>10</v>
@@ -7594,7 +7594,7 @@
         <v>301</v>
       </c>
       <c r="E149">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>10</v>
@@ -7603,7 +7603,7 @@
         <v>70</v>
       </c>
       <c r="H149">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7621,7 +7621,7 @@
         <v>334</v>
       </c>
       <c r="E150">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F150">
         <v>15</v>
@@ -7630,7 +7630,7 @@
         <v>100</v>
       </c>
       <c r="H150">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7648,7 +7648,7 @@
         <v>311</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F151">
         <v>15</v>
@@ -7657,7 +7657,7 @@
         <v>120</v>
       </c>
       <c r="H151">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7675,7 +7675,7 @@
         <v>324</v>
       </c>
       <c r="E152">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F152">
         <v>15</v>
@@ -7684,7 +7684,7 @@
         <v>150</v>
       </c>
       <c r="H152">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7702,7 +7702,7 @@
         <v>314</v>
       </c>
       <c r="E153">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F153">
         <v>15</v>
@@ -7711,7 +7711,7 @@
         <v>180</v>
       </c>
       <c r="H153">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7729,7 +7729,7 @@
         <v>328</v>
       </c>
       <c r="E154">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F154">
         <v>15</v>
@@ -7738,7 +7738,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7756,7 +7756,7 @@
         <v>330</v>
       </c>
       <c r="E155">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F155">
         <v>15</v>
@@ -7765,7 +7765,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7783,7 +7783,7 @@
         <v>517</v>
       </c>
       <c r="E156">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F156">
         <v>15</v>
@@ -7792,7 +7792,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7810,7 +7810,7 @@
         <v>520</v>
       </c>
       <c r="E157">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F157">
         <v>15</v>
@@ -7819,7 +7819,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7837,7 +7837,7 @@
         <v>335</v>
       </c>
       <c r="E158">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F158">
         <v>15</v>
@@ -7846,7 +7846,7 @@
         <v>200</v>
       </c>
       <c r="H158">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7864,7 +7864,7 @@
         <v>338</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F159">
         <v>15</v>
@@ -7873,7 +7873,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7891,7 +7891,7 @@
         <v>501</v>
       </c>
       <c r="E160">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F160">
         <v>15</v>
@@ -7900,7 +7900,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7918,7 +7918,7 @@
         <v>317</v>
       </c>
       <c r="E161">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F161">
         <v>15</v>
@@ -7927,7 +7927,7 @@
         <v>250</v>
       </c>
       <c r="H161">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7945,7 +7945,7 @@
         <v>320</v>
       </c>
       <c r="E162">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F162">
         <v>15</v>
@@ -7954,7 +7954,7 @@
         <v>250</v>
       </c>
       <c r="H162">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -8026,7 +8026,7 @@
         <v>399</v>
       </c>
       <c r="E165">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>10</v>
@@ -8035,7 +8035,7 @@
         <v>100</v>
       </c>
       <c r="H165">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8053,7 +8053,7 @@
         <v>411</v>
       </c>
       <c r="E166">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>10</v>
@@ -8080,7 +8080,7 @@
         <v>404</v>
       </c>
       <c r="E167">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>10</v>
@@ -8107,7 +8107,7 @@
         <v>407</v>
       </c>
       <c r="E168">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F168">
         <v>10</v>
@@ -8116,7 +8116,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8134,7 +8134,7 @@
         <v>410</v>
       </c>
       <c r="E169">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F169">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>413</v>
       </c>
       <c r="E170">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>10</v>
@@ -8188,7 +8188,7 @@
         <v>417</v>
       </c>
       <c r="E171">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>10</v>
@@ -8215,7 +8215,7 @@
         <v>420</v>
       </c>
       <c r="E172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F172">
         <v>10</v>
@@ -8242,7 +8242,7 @@
         <v>423</v>
       </c>
       <c r="E173">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F173">
         <v>20</v>
@@ -8251,7 +8251,7 @@
         <v>200</v>
       </c>
       <c r="H173">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8296,7 +8296,7 @@
         <v>435</v>
       </c>
       <c r="E175">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>15</v>
@@ -8305,7 +8305,7 @@
         <v>170</v>
       </c>
       <c r="H175">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8323,7 +8323,7 @@
         <v>480</v>
       </c>
       <c r="E176">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F176">
         <v>10</v>
@@ -8332,7 +8332,7 @@
         <v>200</v>
       </c>
       <c r="H176">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8350,7 +8350,7 @@
         <v>483</v>
       </c>
       <c r="E177">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F177">
         <v>10</v>
@@ -8359,7 +8359,7 @@
         <v>150</v>
       </c>
       <c r="H177">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8377,7 +8377,7 @@
         <v>486</v>
       </c>
       <c r="E178">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F178">
         <v>10</v>
@@ -8386,7 +8386,7 @@
         <v>150</v>
       </c>
       <c r="H178">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8404,7 +8404,7 @@
         <v>489</v>
       </c>
       <c r="E179">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F179">
         <v>10</v>
@@ -8413,7 +8413,7 @@
         <v>150</v>
       </c>
       <c r="H179">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8431,7 +8431,7 @@
         <v>492</v>
       </c>
       <c r="E180">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F180">
         <v>10</v>
@@ -8440,7 +8440,7 @@
         <v>200</v>
       </c>
       <c r="H180">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D2EE1-24B4-4DA5-B280-EFD114405800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE05BE0-F1ED-4457-A496-7FE6895EB331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1455" yWindow="1050" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5113,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="F57">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G57">
         <v>300</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="F58">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G58">
         <v>500</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="F59">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G59">
         <v>200</v>
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G61">
         <v>300</v>
@@ -6460,7 +6460,7 @@
         <v>474</v>
       </c>
       <c r="E107">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -6469,7 +6469,7 @@
         <v>500</v>
       </c>
       <c r="H107">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -6487,7 +6487,7 @@
         <v>503</v>
       </c>
       <c r="E108">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F108">
         <v>10</v>
@@ -6496,7 +6496,7 @@
         <v>400</v>
       </c>
       <c r="H108">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.4">
@@ -6514,7 +6514,7 @@
         <v>504</v>
       </c>
       <c r="E109">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F109">
         <v>10</v>
@@ -6523,7 +6523,7 @@
         <v>400</v>
       </c>
       <c r="H109">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
@@ -7630,7 +7630,7 @@
         <v>100</v>
       </c>
       <c r="H150">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7657,7 +7657,7 @@
         <v>120</v>
       </c>
       <c r="H151">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7684,7 +7684,7 @@
         <v>150</v>
       </c>
       <c r="H152">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7711,7 +7711,7 @@
         <v>180</v>
       </c>
       <c r="H153">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7738,7 +7738,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7765,7 +7765,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>12</v>
+        <v>322</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7792,7 +7792,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7819,7 +7819,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7846,7 +7846,7 @@
         <v>200</v>
       </c>
       <c r="H158">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7873,7 +7873,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7900,7 +7900,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7927,7 +7927,7 @@
         <v>250</v>
       </c>
       <c r="H161">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7954,7 +7954,7 @@
         <v>250</v>
       </c>
       <c r="H162">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7981,7 +7981,7 @@
         <v>150</v>
       </c>
       <c r="H163">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8008,7 +8008,7 @@
         <v>500</v>
       </c>
       <c r="H164">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8035,7 +8035,7 @@
         <v>100</v>
       </c>
       <c r="H165">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8062,7 +8062,7 @@
         <v>100</v>
       </c>
       <c r="H166">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8089,7 +8089,7 @@
         <v>100</v>
       </c>
       <c r="H167">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8116,7 +8116,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8143,7 +8143,7 @@
         <v>100</v>
       </c>
       <c r="H169">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8170,7 +8170,7 @@
         <v>100</v>
       </c>
       <c r="H170">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8197,7 +8197,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8224,7 +8224,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8251,7 +8251,7 @@
         <v>200</v>
       </c>
       <c r="H173">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8278,7 +8278,7 @@
         <v>100</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8305,7 +8305,7 @@
         <v>170</v>
       </c>
       <c r="H175">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8359,7 +8359,7 @@
         <v>150</v>
       </c>
       <c r="H177">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8386,7 +8386,7 @@
         <v>150</v>
       </c>
       <c r="H178">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8413,7 +8413,7 @@
         <v>150</v>
       </c>
       <c r="H179">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8440,7 +8440,7 @@
         <v>200</v>
       </c>
       <c r="H180">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE05BE0-F1ED-4457-A496-7FE6895EB331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6585D78-D79B-4F88-86EF-1C9857D9548C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="1050" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1875" yWindow="765" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7711,7 +7711,7 @@
         <v>180</v>
       </c>
       <c r="H153">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7738,7 +7738,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7765,7 +7765,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>322</v>
+        <v>42</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7792,7 +7792,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7819,7 +7819,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7846,7 +7846,7 @@
         <v>200</v>
       </c>
       <c r="H158">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7873,7 +7873,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7900,7 +7900,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7927,7 +7927,7 @@
         <v>250</v>
       </c>
       <c r="H161">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7954,7 +7954,7 @@
         <v>250</v>
       </c>
       <c r="H162">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7981,7 +7981,7 @@
         <v>150</v>
       </c>
       <c r="H163">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8008,7 +8008,7 @@
         <v>500</v>
       </c>
       <c r="H164">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8035,7 +8035,7 @@
         <v>100</v>
       </c>
       <c r="H165">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8062,7 +8062,7 @@
         <v>100</v>
       </c>
       <c r="H166">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8089,7 +8089,7 @@
         <v>100</v>
       </c>
       <c r="H167">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8116,7 +8116,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8143,7 +8143,7 @@
         <v>100</v>
       </c>
       <c r="H169">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8170,7 +8170,7 @@
         <v>100</v>
       </c>
       <c r="H170">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8197,7 +8197,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8224,7 +8224,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8251,7 +8251,7 @@
         <v>200</v>
       </c>
       <c r="H173">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8278,7 +8278,7 @@
         <v>100</v>
       </c>
       <c r="H174">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8305,7 +8305,7 @@
         <v>170</v>
       </c>
       <c r="H175">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8332,7 +8332,7 @@
         <v>200</v>
       </c>
       <c r="H176">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8359,7 +8359,7 @@
         <v>150</v>
       </c>
       <c r="H177">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8386,7 +8386,7 @@
         <v>150</v>
       </c>
       <c r="H178">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8413,7 +8413,7 @@
         <v>150</v>
       </c>
       <c r="H179">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8440,7 +8440,7 @@
         <v>200</v>
       </c>
       <c r="H180">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6585D78-D79B-4F88-86EF-1C9857D9548C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D5B48C-9951-4448-AF9F-09D23D1F770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="765" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1680" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7090,7 +7090,7 @@
         <v>200</v>
       </c>
       <c r="H130">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -7117,7 +7117,7 @@
         <v>200</v>
       </c>
       <c r="H131">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -7144,7 +7144,7 @@
         <v>200</v>
       </c>
       <c r="H132">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7171,7 +7171,7 @@
         <v>200</v>
       </c>
       <c r="H133">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7198,7 +7198,7 @@
         <v>300</v>
       </c>
       <c r="H134">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7225,7 +7225,7 @@
         <v>300</v>
       </c>
       <c r="H135">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7252,7 +7252,7 @@
         <v>300</v>
       </c>
       <c r="H136">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7279,7 +7279,7 @@
         <v>300</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7306,7 +7306,7 @@
         <v>300</v>
       </c>
       <c r="H138">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D5B48C-9951-4448-AF9F-09D23D1F770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B15DC95-4712-41DF-A1EB-28D7035B18F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="539">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -3189,6 +3189,24 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ホウセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SaltTopping</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しおっ気</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お塩</t>
+    <rPh sb="1" eb="2">
+      <t>シオ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3573,7 +3591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3612,7 +3630,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A181" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A182" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -7315,13 +7333,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>396</v>
+        <v>536</v>
       </c>
       <c r="C139" t="s">
-        <v>439</v>
+        <v>537</v>
       </c>
       <c r="D139" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="E139">
         <v>-10</v>
@@ -7330,10 +7348,10 @@
         <v>0</v>
       </c>
       <c r="G139">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H139">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.4">
@@ -7342,13 +7360,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>508</v>
+        <v>396</v>
       </c>
       <c r="C140" t="s">
-        <v>510</v>
+        <v>439</v>
       </c>
       <c r="D140" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E140">
         <v>-10</v>
@@ -7357,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="G140">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H140">
         <v>2</v>
@@ -7369,13 +7387,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C141" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D141" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E141">
         <v>-10</v>
@@ -7384,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="G141">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H141">
         <v>2</v>
@@ -7396,22 +7414,22 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>509</v>
       </c>
       <c r="C142" t="s">
-        <v>77</v>
+        <v>511</v>
       </c>
       <c r="D142" t="s">
-        <v>78</v>
+        <v>514</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F142">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G142">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H142">
         <v>2</v>
@@ -7423,25 +7441,25 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C143" t="s">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="D143" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G143">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H143">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.4">
@@ -7450,25 +7468,25 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C144" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="D144" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E144">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G144">
         <v>300</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7477,25 +7495,25 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="C145" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="D145" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F145">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G145">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H145">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.4">
@@ -7504,13 +7522,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C146" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D146" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -7531,22 +7549,22 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="C147" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="D147" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G147">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H147">
         <v>10</v>
@@ -7558,25 +7576,25 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C148" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D148" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
+        <v>10</v>
+      </c>
+      <c r="G148">
         <v>30</v>
       </c>
-      <c r="G148">
-        <v>300</v>
-      </c>
       <c r="H148">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.4">
@@ -7585,25 +7603,25 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="C149" t="s">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="D149" t="s">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G149">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="H149">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.4">
@@ -7612,25 +7630,25 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C150" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D150" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G150">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7639,25 +7657,25 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D151" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="E151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F151">
         <v>15</v>
       </c>
       <c r="G151">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H151">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7666,13 +7684,13 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C152" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D152" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E152">
         <v>3</v>
@@ -7681,10 +7699,10 @@
         <v>15</v>
       </c>
       <c r="G152">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H152">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7693,25 +7711,25 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C153" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="D153" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F153">
         <v>15</v>
       </c>
       <c r="G153">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H153">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7720,13 +7738,13 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C154" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D154" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E154">
         <v>5</v>
@@ -7747,13 +7765,13 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C155" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D155" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E155">
         <v>5</v>
@@ -7765,7 +7783,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7774,13 +7792,13 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>515</v>
+        <v>329</v>
       </c>
       <c r="C156" t="s">
-        <v>516</v>
+        <v>331</v>
       </c>
       <c r="D156" t="s">
-        <v>517</v>
+        <v>330</v>
       </c>
       <c r="E156">
         <v>5</v>
@@ -7792,7 +7810,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7801,13 +7819,13 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C157" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D157" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E157">
         <v>5</v>
@@ -7819,7 +7837,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7828,13 +7846,13 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>332</v>
+        <v>518</v>
       </c>
       <c r="C158" t="s">
-        <v>333</v>
+        <v>519</v>
       </c>
       <c r="D158" t="s">
-        <v>335</v>
+        <v>520</v>
       </c>
       <c r="E158">
         <v>5</v>
@@ -7843,7 +7861,7 @@
         <v>15</v>
       </c>
       <c r="G158">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H158">
         <v>42</v>
@@ -7855,13 +7873,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C159" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D159" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E159">
         <v>5</v>
@@ -7882,13 +7900,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>499</v>
+        <v>336</v>
       </c>
       <c r="C160" t="s">
-        <v>500</v>
+        <v>337</v>
       </c>
       <c r="D160" t="s">
-        <v>501</v>
+        <v>338</v>
       </c>
       <c r="E160">
         <v>5</v>
@@ -7909,13 +7927,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>315</v>
+        <v>499</v>
       </c>
       <c r="C161" t="s">
-        <v>316</v>
+        <v>500</v>
       </c>
       <c r="D161" t="s">
-        <v>317</v>
+        <v>501</v>
       </c>
       <c r="E161">
         <v>5</v>
@@ -7924,10 +7942,10 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H161">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7936,13 +7954,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C162" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D162" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E162">
         <v>5</v>
@@ -7963,25 +7981,25 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>430</v>
+        <v>318</v>
       </c>
       <c r="C163" t="s">
-        <v>431</v>
+        <v>319</v>
       </c>
       <c r="D163" t="s">
-        <v>432</v>
+        <v>320</v>
       </c>
       <c r="E163">
         <v>5</v>
       </c>
       <c r="F163">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G163">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H163">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -7990,25 +8008,25 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D164" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E164">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F164">
         <v>10</v>
       </c>
       <c r="G164">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H164">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8017,25 +8035,25 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="C165" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="D165" t="s">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F165">
         <v>10</v>
       </c>
       <c r="G165">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H165">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8044,13 +8062,13 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C166" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D166" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -8062,7 +8080,7 @@
         <v>100</v>
       </c>
       <c r="H166">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8071,13 +8089,13 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C167" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -8098,13 +8116,13 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C168" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -8116,7 +8134,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8125,13 +8143,13 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C169" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D169" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -8143,7 +8161,7 @@
         <v>100</v>
       </c>
       <c r="H169">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8152,13 +8170,13 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C170" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -8179,13 +8197,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C171" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8197,7 +8215,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8206,13 +8224,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C172" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D172" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -8224,7 +8242,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8233,25 +8251,25 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C173" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D173" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G173">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H173">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8260,25 +8278,25 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C174" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D174" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E174">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F174">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="G174">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H174">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8287,25 +8305,25 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C175" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D175" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F175">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="G175">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H175">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8314,25 +8332,25 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="C176" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="D176" t="s">
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
       <c r="F176">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G176">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="H176">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8341,25 +8359,25 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C177" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D177" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E177">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>10</v>
       </c>
       <c r="G177">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H177">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8368,13 +8386,13 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C178" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D178" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E178">
         <v>5</v>
@@ -8395,13 +8413,13 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C179" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D179" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E179">
         <v>5</v>
@@ -8422,13 +8440,13 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C180" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D180" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E180">
         <v>5</v>
@@ -8437,10 +8455,10 @@
         <v>10</v>
       </c>
       <c r="G180">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H180">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -8449,24 +8467,51 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
+        <v>490</v>
+      </c>
+      <c r="C181" t="s">
+        <v>491</v>
+      </c>
+      <c r="D181" t="s">
+        <v>492</v>
+      </c>
+      <c r="E181">
+        <v>5</v>
+      </c>
+      <c r="F181">
+        <v>10</v>
+      </c>
+      <c r="G181">
+        <v>200</v>
+      </c>
+      <c r="H181">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A182">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="B182" t="s">
         <v>85</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C182" t="s">
         <v>86</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D182" t="s">
         <v>87</v>
       </c>
-      <c r="E181">
+      <c r="E182">
         <v>150</v>
       </c>
-      <c r="F181">
+      <c r="F182">
         <v>100</v>
       </c>
-      <c r="G181">
+      <c r="G182">
         <v>300</v>
       </c>
-      <c r="H181">
+      <c r="H182">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B15DC95-4712-41DF-A1EB-28D7035B18F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4652B5-D455-4CC4-BC9F-EE7B5A58F875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4669,7 +4669,7 @@
         <v>39</v>
       </c>
       <c r="E40">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F40">
         <v>-10</v>
@@ -4678,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>-10</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4652B5-D455-4CC4-BC9F-EE7B5A58F875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045EF88-CBB7-4AD3-B1AA-7F0A5ADCF7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2700" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045EF88-CBB7-4AD3-B1AA-7F0A5ADCF7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC5E9D1-6ADC-42B3-9F9C-74D212038E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1035" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1260" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6919,7 +6919,7 @@
         <v>150</v>
       </c>
       <c r="H123">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
@@ -7081,7 +7081,7 @@
         <v>150</v>
       </c>
       <c r="H129">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
@@ -7108,7 +7108,7 @@
         <v>200</v>
       </c>
       <c r="H130">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -7135,7 +7135,7 @@
         <v>200</v>
       </c>
       <c r="H131">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -7162,7 +7162,7 @@
         <v>200</v>
       </c>
       <c r="H132">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7189,7 +7189,7 @@
         <v>200</v>
       </c>
       <c r="H133">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7216,7 +7216,7 @@
         <v>300</v>
       </c>
       <c r="H134">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7243,7 +7243,7 @@
         <v>300</v>
       </c>
       <c r="H135">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7270,7 +7270,7 @@
         <v>300</v>
       </c>
       <c r="H136">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7288,7 +7288,7 @@
         <v>452</v>
       </c>
       <c r="E137">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="F137">
         <v>10</v>
@@ -7297,7 +7297,7 @@
         <v>300</v>
       </c>
       <c r="H137">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7756,7 +7756,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7783,7 +7783,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7810,7 +7810,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7837,7 +7837,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7864,7 +7864,7 @@
         <v>180</v>
       </c>
       <c r="H158">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7891,7 +7891,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7918,7 +7918,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7945,7 +7945,7 @@
         <v>200</v>
       </c>
       <c r="H161">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7972,7 +7972,7 @@
         <v>250</v>
       </c>
       <c r="H162">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7999,7 +7999,7 @@
         <v>250</v>
       </c>
       <c r="H163">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8026,7 +8026,7 @@
         <v>150</v>
       </c>
       <c r="H164">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8053,7 +8053,7 @@
         <v>500</v>
       </c>
       <c r="H165">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8080,7 +8080,7 @@
         <v>100</v>
       </c>
       <c r="H166">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8107,7 +8107,7 @@
         <v>100</v>
       </c>
       <c r="H167">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8134,7 +8134,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8161,7 +8161,7 @@
         <v>100</v>
       </c>
       <c r="H169">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8188,7 +8188,7 @@
         <v>100</v>
       </c>
       <c r="H170">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8215,7 +8215,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8242,7 +8242,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8269,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="H173">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8296,7 +8296,7 @@
         <v>200</v>
       </c>
       <c r="H174">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8323,7 +8323,7 @@
         <v>100</v>
       </c>
       <c r="H175">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8350,7 +8350,7 @@
         <v>170</v>
       </c>
       <c r="H176">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8377,7 +8377,7 @@
         <v>200</v>
       </c>
       <c r="H177">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC5E9D1-6ADC-42B3-9F9C-74D212038E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77CA0E1-9F12-45FF-B852-BCADBDB1410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2055" yWindow="1185" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7162,7 +7162,7 @@
         <v>200</v>
       </c>
       <c r="H132">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7189,7 +7189,7 @@
         <v>200</v>
       </c>
       <c r="H133">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7216,7 +7216,7 @@
         <v>300</v>
       </c>
       <c r="H134">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7243,7 +7243,7 @@
         <v>300</v>
       </c>
       <c r="H135">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7270,7 +7270,7 @@
         <v>300</v>
       </c>
       <c r="H136">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7324,7 +7324,7 @@
         <v>300</v>
       </c>
       <c r="H138">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7702,7 +7702,7 @@
         <v>120</v>
       </c>
       <c r="H152">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7756,7 +7756,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7783,7 +7783,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7810,7 +7810,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7837,7 +7837,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7864,7 +7864,7 @@
         <v>180</v>
       </c>
       <c r="H158">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7891,7 +7891,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7918,7 +7918,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7945,7 +7945,7 @@
         <v>200</v>
       </c>
       <c r="H161">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77CA0E1-9F12-45FF-B852-BCADBDB1410F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52B17F3-5D1D-44AF-AE60-35D44A6C2FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1185" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3120" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4084,7 +4084,7 @@
         <v>50</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>200</v>
       </c>
       <c r="H19">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
@@ -4516,7 +4516,7 @@
         <v>150</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -4570,7 +4570,7 @@
         <v>50</v>
       </c>
       <c r="H36">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -4597,7 +4597,7 @@
         <v>90</v>
       </c>
       <c r="H37">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -4813,7 +4813,7 @@
         <v>80</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
@@ -4840,7 +4840,7 @@
         <v>120</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
@@ -4894,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -4921,7 +4921,7 @@
         <v>150</v>
       </c>
       <c r="H49">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
@@ -4948,7 +4948,7 @@
         <v>300</v>
       </c>
       <c r="H50">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -5137,7 +5137,7 @@
         <v>300</v>
       </c>
       <c r="H57">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
@@ -5164,7 +5164,7 @@
         <v>500</v>
       </c>
       <c r="H58">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -5191,7 +5191,7 @@
         <v>200</v>
       </c>
       <c r="H59">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -5974,7 +5974,7 @@
         <v>240</v>
       </c>
       <c r="H88">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -6001,7 +6001,7 @@
         <v>480</v>
       </c>
       <c r="H89">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.4">
@@ -6028,7 +6028,7 @@
         <v>240</v>
       </c>
       <c r="H90">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.4">
@@ -6055,7 +6055,7 @@
         <v>240</v>
       </c>
       <c r="H91">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.4">
@@ -6082,7 +6082,7 @@
         <v>240</v>
       </c>
       <c r="H92">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.4">
@@ -6109,7 +6109,7 @@
         <v>240</v>
       </c>
       <c r="H93">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
@@ -6136,7 +6136,7 @@
         <v>240</v>
       </c>
       <c r="H94">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
@@ -6163,7 +6163,7 @@
         <v>240</v>
       </c>
       <c r="H95">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
@@ -6190,7 +6190,7 @@
         <v>240</v>
       </c>
       <c r="H96">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
@@ -6217,7 +6217,7 @@
         <v>240</v>
       </c>
       <c r="H97">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
@@ -6244,7 +6244,7 @@
         <v>240</v>
       </c>
       <c r="H98">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
@@ -6271,7 +6271,7 @@
         <v>240</v>
       </c>
       <c r="H99">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -6298,7 +6298,7 @@
         <v>240</v>
       </c>
       <c r="H100">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -6487,7 +6487,7 @@
         <v>500</v>
       </c>
       <c r="H107">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -7108,7 +7108,7 @@
         <v>200</v>
       </c>
       <c r="H130">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.4">
@@ -7135,7 +7135,7 @@
         <v>200</v>
       </c>
       <c r="H131">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.4">
@@ -7162,7 +7162,7 @@
         <v>200</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.4">
@@ -7189,7 +7189,7 @@
         <v>200</v>
       </c>
       <c r="H133">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.4">
@@ -7216,7 +7216,7 @@
         <v>300</v>
       </c>
       <c r="H134">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.4">
@@ -7243,7 +7243,7 @@
         <v>300</v>
       </c>
       <c r="H135">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.4">
@@ -7270,7 +7270,7 @@
         <v>300</v>
       </c>
       <c r="H136">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7297,7 +7297,7 @@
         <v>300</v>
       </c>
       <c r="H137">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.4">
@@ -7324,7 +7324,7 @@
         <v>300</v>
       </c>
       <c r="H138">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.4">
@@ -7342,7 +7342,7 @@
         <v>538</v>
       </c>
       <c r="E139">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7486,7 +7486,7 @@
         <v>300</v>
       </c>
       <c r="H144">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.4">
@@ -7540,7 +7540,7 @@
         <v>200</v>
       </c>
       <c r="H146">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.4">
@@ -7567,7 +7567,7 @@
         <v>200</v>
       </c>
       <c r="H147">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.4">
@@ -7675,7 +7675,7 @@
         <v>100</v>
       </c>
       <c r="H151">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7702,7 +7702,7 @@
         <v>120</v>
       </c>
       <c r="H152">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7729,7 +7729,7 @@
         <v>150</v>
       </c>
       <c r="H153">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7756,7 +7756,7 @@
         <v>180</v>
       </c>
       <c r="H154">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7783,7 +7783,7 @@
         <v>180</v>
       </c>
       <c r="H155">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7810,7 +7810,7 @@
         <v>180</v>
       </c>
       <c r="H156">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7837,7 +7837,7 @@
         <v>180</v>
       </c>
       <c r="H157">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7864,7 +7864,7 @@
         <v>180</v>
       </c>
       <c r="H158">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7891,7 +7891,7 @@
         <v>200</v>
       </c>
       <c r="H159">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7918,7 +7918,7 @@
         <v>200</v>
       </c>
       <c r="H160">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7945,7 +7945,7 @@
         <v>200</v>
       </c>
       <c r="H161">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -7972,7 +7972,7 @@
         <v>250</v>
       </c>
       <c r="H162">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7999,7 +7999,7 @@
         <v>250</v>
       </c>
       <c r="H163">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8026,7 +8026,7 @@
         <v>150</v>
       </c>
       <c r="H164">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8053,7 +8053,7 @@
         <v>500</v>
       </c>
       <c r="H165">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8080,7 +8080,7 @@
         <v>100</v>
       </c>
       <c r="H166">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8107,7 +8107,7 @@
         <v>100</v>
       </c>
       <c r="H167">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8134,7 +8134,7 @@
         <v>100</v>
       </c>
       <c r="H168">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8161,7 +8161,7 @@
         <v>100</v>
       </c>
       <c r="H169">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8188,7 +8188,7 @@
         <v>100</v>
       </c>
       <c r="H170">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8215,7 +8215,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8242,7 +8242,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8269,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="H173">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8296,7 +8296,7 @@
         <v>200</v>
       </c>
       <c r="H174">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8323,7 +8323,7 @@
         <v>100</v>
       </c>
       <c r="H175">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8350,7 +8350,7 @@
         <v>170</v>
       </c>
       <c r="H176">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8377,7 +8377,7 @@
         <v>200</v>
       </c>
       <c r="H177">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8404,7 +8404,7 @@
         <v>150</v>
       </c>
       <c r="H178">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8431,7 +8431,7 @@
         <v>150</v>
       </c>
       <c r="H179">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8458,7 +8458,7 @@
         <v>150</v>
       </c>
       <c r="H180">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -8485,7 +8485,7 @@
         <v>200</v>
       </c>
       <c r="H181">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52B17F3-5D1D-44AF-AE60-35D44A6C2FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5342ED8C-86D8-408A-9A4A-37E0557FDC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5342ED8C-86D8-408A-9A4A-37E0557FDC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F064618D-E45F-406D-85CF-238329FEE18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3030" yWindow="1110" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>500</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -8296,7 +8296,7 @@
         <v>200</v>
       </c>
       <c r="H174">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F064618D-E45F-406D-85CF-238329FEE18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C88FAC-35E7-482C-84E3-9D67D2EB08F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="1110" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2370" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="554">
   <si>
     <t>ItemID</t>
     <phoneticPr fontId="3"/>
@@ -3207,6 +3207,105 @@
     <t>お塩</t>
     <rPh sb="1" eb="2">
       <t>シオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GlowWater</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光る水</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キラキラ光る</t>
+    <rPh sb="4" eb="5">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>浮遊する砂糖</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>デコ砂糖</t>
+    <rPh sb="2" eb="4">
+      <t>サトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FloatingSuger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>空中フルーツ</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>浮遊フルーツ</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FloatingFruits</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>デコキラ砂糖</t>
+    <rPh sb="4" eb="6">
+      <t>サトウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FloatingSugerLumi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>浮遊する光</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FloatingFruitsLumi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>空中キラフルーツ</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>浮遊グローフルーツ</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3591,7 +3690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
@@ -3630,7 +3729,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
-        <f t="shared" ref="A2:A182" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A187" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -7630,13 +7729,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>303</v>
+        <v>539</v>
       </c>
       <c r="C150" t="s">
-        <v>302</v>
+        <v>540</v>
       </c>
       <c r="D150" t="s">
-        <v>301</v>
+        <v>541</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -7645,10 +7744,10 @@
         <v>10</v>
       </c>
       <c r="G150">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H150">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.4">
@@ -7657,25 +7756,25 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>307</v>
+        <v>544</v>
       </c>
       <c r="C151" t="s">
-        <v>310</v>
+        <v>543</v>
       </c>
       <c r="D151" t="s">
-        <v>334</v>
+        <v>542</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F151">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G151">
         <v>100</v>
       </c>
       <c r="H151">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7684,25 +7783,25 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>308</v>
+        <v>549</v>
       </c>
       <c r="C152" t="s">
-        <v>309</v>
+        <v>548</v>
       </c>
       <c r="D152" t="s">
-        <v>311</v>
+        <v>550</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F152">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G152">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H152">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7711,25 +7810,25 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>312</v>
+        <v>547</v>
       </c>
       <c r="C153" t="s">
-        <v>325</v>
+        <v>545</v>
       </c>
       <c r="D153" t="s">
-        <v>324</v>
+        <v>546</v>
       </c>
       <c r="E153">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G153">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H153">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7738,25 +7837,25 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>323</v>
+        <v>551</v>
       </c>
       <c r="C154" t="s">
-        <v>313</v>
+        <v>552</v>
       </c>
       <c r="D154" t="s">
-        <v>314</v>
+        <v>553</v>
       </c>
       <c r="E154">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F154">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G154">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H154">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7765,25 +7864,25 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="C155" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="D155" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="E155">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G155">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H155">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">
@@ -7792,25 +7891,25 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="C156" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="D156" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E156">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F156">
         <v>15</v>
       </c>
       <c r="G156">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="H156">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7819,22 +7918,22 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>515</v>
+        <v>308</v>
       </c>
       <c r="C157" t="s">
-        <v>516</v>
+        <v>309</v>
       </c>
       <c r="D157" t="s">
-        <v>517</v>
+        <v>311</v>
       </c>
       <c r="E157">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F157">
         <v>15</v>
       </c>
       <c r="G157">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H157">
         <v>36</v>
@@ -7846,25 +7945,25 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>518</v>
+        <v>312</v>
       </c>
       <c r="C158" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="D158" t="s">
-        <v>520</v>
+        <v>324</v>
       </c>
       <c r="E158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F158">
         <v>15</v>
       </c>
       <c r="G158">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H158">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7873,13 +7972,13 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C159" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="D159" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="E159">
         <v>5</v>
@@ -7888,10 +7987,10 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H159">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -7900,13 +7999,13 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="C160" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="D160" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E160">
         <v>5</v>
@@ -7915,10 +8014,10 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H160">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -7927,13 +8026,13 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>499</v>
+        <v>329</v>
       </c>
       <c r="C161" t="s">
-        <v>500</v>
+        <v>331</v>
       </c>
       <c r="D161" t="s">
-        <v>501</v>
+        <v>330</v>
       </c>
       <c r="E161">
         <v>5</v>
@@ -7942,7 +8041,7 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H161">
         <v>36</v>
@@ -7954,13 +8053,13 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>315</v>
+        <v>515</v>
       </c>
       <c r="C162" t="s">
-        <v>316</v>
+        <v>516</v>
       </c>
       <c r="D162" t="s">
-        <v>317</v>
+        <v>517</v>
       </c>
       <c r="E162">
         <v>5</v>
@@ -7969,10 +8068,10 @@
         <v>15</v>
       </c>
       <c r="G162">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H162">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -7981,13 +8080,13 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>318</v>
+        <v>518</v>
       </c>
       <c r="C163" t="s">
-        <v>319</v>
+        <v>519</v>
       </c>
       <c r="D163" t="s">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="E163">
         <v>5</v>
@@ -7996,10 +8095,10 @@
         <v>15</v>
       </c>
       <c r="G163">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H163">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8008,25 +8107,25 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>430</v>
+        <v>332</v>
       </c>
       <c r="C164" t="s">
-        <v>431</v>
+        <v>333</v>
       </c>
       <c r="D164" t="s">
-        <v>432</v>
+        <v>335</v>
       </c>
       <c r="E164">
         <v>5</v>
       </c>
       <c r="F164">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G164">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H164">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8035,25 +8134,25 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>436</v>
+        <v>336</v>
       </c>
       <c r="C165" t="s">
-        <v>437</v>
+        <v>337</v>
       </c>
       <c r="D165" t="s">
-        <v>438</v>
+        <v>338</v>
       </c>
       <c r="E165">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G165">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H165">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8062,25 +8161,25 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>398</v>
+        <v>499</v>
       </c>
       <c r="C166" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D166" t="s">
-        <v>399</v>
+        <v>501</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F166">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G166">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H166">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8089,25 +8188,25 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>397</v>
+        <v>315</v>
       </c>
       <c r="C167" t="s">
-        <v>401</v>
+        <v>316</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>317</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G167">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H167">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8116,25 +8215,25 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>402</v>
+        <v>318</v>
       </c>
       <c r="C168" t="s">
-        <v>403</v>
+        <v>319</v>
       </c>
       <c r="D168" t="s">
-        <v>404</v>
+        <v>320</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F168">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G168">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H168">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8143,25 +8242,25 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C169" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="D169" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F169">
         <v>10</v>
       </c>
       <c r="G169">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H169">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8170,25 +8269,25 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="C170" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F170">
         <v>10</v>
       </c>
       <c r="G170">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H170">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8197,13 +8296,13 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="C171" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -8215,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8224,13 +8323,13 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="C172" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="D172" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -8242,7 +8341,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8251,13 +8350,13 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C173" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="D173" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -8269,7 +8368,7 @@
         <v>100</v>
       </c>
       <c r="H173">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8278,25 +8377,25 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C174" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="D174" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G174">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H174">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8305,19 +8404,19 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="D175" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="E175">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F175">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G175">
         <v>100</v>
@@ -8332,25 +8431,25 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C176" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="D176" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
       <c r="F176">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G176">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H176">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8359,13 +8458,13 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>478</v>
+        <v>414</v>
       </c>
       <c r="C177" t="s">
-        <v>479</v>
+        <v>415</v>
       </c>
       <c r="D177" t="s">
-        <v>480</v>
+        <v>417</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -8374,10 +8473,10 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H177">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8386,25 +8485,25 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>481</v>
+        <v>418</v>
       </c>
       <c r="C178" t="s">
-        <v>482</v>
+        <v>419</v>
       </c>
       <c r="D178" t="s">
-        <v>483</v>
+        <v>420</v>
       </c>
       <c r="E178">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F178">
         <v>10</v>
       </c>
       <c r="G178">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H178">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8413,25 +8512,25 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>484</v>
+        <v>421</v>
       </c>
       <c r="C179" t="s">
-        <v>485</v>
+        <v>422</v>
       </c>
       <c r="D179" t="s">
-        <v>486</v>
+        <v>423</v>
       </c>
       <c r="E179">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F179">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G179">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H179">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8440,25 +8539,25 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>487</v>
+        <v>424</v>
       </c>
       <c r="C180" t="s">
-        <v>488</v>
+        <v>425</v>
       </c>
       <c r="D180" t="s">
-        <v>489</v>
+        <v>426</v>
       </c>
       <c r="E180">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="F180">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="G180">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H180">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -8467,25 +8566,25 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>490</v>
+        <v>433</v>
       </c>
       <c r="C181" t="s">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="D181" t="s">
-        <v>492</v>
+        <v>435</v>
       </c>
       <c r="E181">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G181">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="H181">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.4">
@@ -8494,24 +8593,159 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
+        <v>478</v>
+      </c>
+      <c r="C182" t="s">
+        <v>479</v>
+      </c>
+      <c r="D182" t="s">
+        <v>480</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>10</v>
+      </c>
+      <c r="G182">
+        <v>200</v>
+      </c>
+      <c r="H182">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A183">
+        <f t="shared" si="0"/>
+        <v>181</v>
+      </c>
+      <c r="B183" t="s">
+        <v>481</v>
+      </c>
+      <c r="C183" t="s">
+        <v>482</v>
+      </c>
+      <c r="D183" t="s">
+        <v>483</v>
+      </c>
+      <c r="E183">
+        <v>5</v>
+      </c>
+      <c r="F183">
+        <v>10</v>
+      </c>
+      <c r="G183">
+        <v>150</v>
+      </c>
+      <c r="H183">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A184">
+        <f t="shared" si="0"/>
+        <v>182</v>
+      </c>
+      <c r="B184" t="s">
+        <v>484</v>
+      </c>
+      <c r="C184" t="s">
+        <v>485</v>
+      </c>
+      <c r="D184" t="s">
+        <v>486</v>
+      </c>
+      <c r="E184">
+        <v>5</v>
+      </c>
+      <c r="F184">
+        <v>10</v>
+      </c>
+      <c r="G184">
+        <v>150</v>
+      </c>
+      <c r="H184">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A185">
+        <f t="shared" si="0"/>
+        <v>183</v>
+      </c>
+      <c r="B185" t="s">
+        <v>487</v>
+      </c>
+      <c r="C185" t="s">
+        <v>488</v>
+      </c>
+      <c r="D185" t="s">
+        <v>489</v>
+      </c>
+      <c r="E185">
+        <v>5</v>
+      </c>
+      <c r="F185">
+        <v>10</v>
+      </c>
+      <c r="G185">
+        <v>150</v>
+      </c>
+      <c r="H185">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A186">
+        <f t="shared" si="0"/>
+        <v>184</v>
+      </c>
+      <c r="B186" t="s">
+        <v>490</v>
+      </c>
+      <c r="C186" t="s">
+        <v>491</v>
+      </c>
+      <c r="D186" t="s">
+        <v>492</v>
+      </c>
+      <c r="E186">
+        <v>5</v>
+      </c>
+      <c r="F186">
+        <v>10</v>
+      </c>
+      <c r="G186">
+        <v>200</v>
+      </c>
+      <c r="H186">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A187">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="B187" t="s">
         <v>85</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C187" t="s">
         <v>86</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D187" t="s">
         <v>87</v>
       </c>
-      <c r="E182">
+      <c r="E187">
         <v>150</v>
       </c>
-      <c r="F182">
+      <c r="F187">
         <v>100</v>
       </c>
-      <c r="G182">
+      <c r="G187">
         <v>300</v>
       </c>
-      <c r="H182">
+      <c r="H187">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C88FAC-35E7-482C-84E3-9D67D2EB08F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0443F5-36B4-4466-80C6-815F0ED3F9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H15">
         <v>8</v>
@@ -5263,7 +5263,7 @@
         <v>500</v>
       </c>
       <c r="H58">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.4">
@@ -6070,10 +6070,10 @@
         <v>10</v>
       </c>
       <c r="G88">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H88">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -6097,7 +6097,7 @@
         <v>20</v>
       </c>
       <c r="G89">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="H89">
         <v>40</v>
@@ -6124,7 +6124,7 @@
         <v>10</v>
       </c>
       <c r="G90">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H90">
         <v>20</v>
@@ -6151,7 +6151,7 @@
         <v>20</v>
       </c>
       <c r="G91">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H91">
         <v>20</v>
@@ -6178,7 +6178,7 @@
         <v>20</v>
       </c>
       <c r="G92">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H92">
         <v>20</v>
@@ -6205,7 +6205,7 @@
         <v>10</v>
       </c>
       <c r="G93">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H93">
         <v>20</v>
@@ -6232,7 +6232,7 @@
         <v>10</v>
       </c>
       <c r="G94">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H94">
         <v>20</v>
@@ -6259,7 +6259,7 @@
         <v>10</v>
       </c>
       <c r="G95">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H95">
         <v>20</v>
@@ -6286,7 +6286,7 @@
         <v>10</v>
       </c>
       <c r="G96">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H96">
         <v>20</v>
@@ -6313,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="G97">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H97">
         <v>20</v>
@@ -6340,7 +6340,7 @@
         <v>12</v>
       </c>
       <c r="G98">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H98">
         <v>20</v>
@@ -6367,10 +6367,10 @@
         <v>30</v>
       </c>
       <c r="G99">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H99">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
@@ -6394,10 +6394,10 @@
         <v>20</v>
       </c>
       <c r="G100">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="H100">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
@@ -6448,7 +6448,7 @@
         <v>10</v>
       </c>
       <c r="G102">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="H102">
         <v>12</v>
@@ -6475,7 +6475,7 @@
         <v>10</v>
       </c>
       <c r="G103">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H103">
         <v>20</v>
@@ -6502,7 +6502,7 @@
         <v>10</v>
       </c>
       <c r="G104">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H104">
         <v>20</v>
@@ -6529,7 +6529,7 @@
         <v>10</v>
       </c>
       <c r="G105">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H105">
         <v>20</v>
@@ -6556,7 +6556,7 @@
         <v>10</v>
       </c>
       <c r="G106">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H106">
         <v>20</v>
@@ -6583,10 +6583,10 @@
         <v>10</v>
       </c>
       <c r="G107">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H107">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
@@ -6610,7 +6610,7 @@
         <v>10</v>
       </c>
       <c r="G108">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="H108">
         <v>32</v>
@@ -6637,7 +6637,7 @@
         <v>10</v>
       </c>
       <c r="G109">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="H109">
         <v>32</v>
@@ -6664,7 +6664,7 @@
         <v>10</v>
       </c>
       <c r="G110">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H110">
         <v>7</v>
@@ -7204,7 +7204,7 @@
         <v>10</v>
       </c>
       <c r="G130">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H130">
         <v>20</v>
@@ -7231,7 +7231,7 @@
         <v>10</v>
       </c>
       <c r="G131">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H131">
         <v>20</v>
@@ -7258,7 +7258,7 @@
         <v>10</v>
       </c>
       <c r="G132">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H132">
         <v>30</v>
@@ -7285,7 +7285,7 @@
         <v>10</v>
       </c>
       <c r="G133">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H133">
         <v>35</v>
@@ -7312,7 +7312,7 @@
         <v>10</v>
       </c>
       <c r="G134">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H134">
         <v>30</v>
@@ -7339,7 +7339,7 @@
         <v>10</v>
       </c>
       <c r="G135">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H135">
         <v>35</v>
@@ -7366,7 +7366,7 @@
         <v>10</v>
       </c>
       <c r="G136">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H136">
         <v>33</v>
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="G137">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H137">
         <v>25</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="G138">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H138">
         <v>50</v>
@@ -7636,7 +7636,7 @@
         <v>20</v>
       </c>
       <c r="G146">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H146">
         <v>30</v>
@@ -7663,7 +7663,7 @@
         <v>20</v>
       </c>
       <c r="G147">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H147">
         <v>30</v>
@@ -7717,7 +7717,7 @@
         <v>30</v>
       </c>
       <c r="G149">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="H149">
         <v>15</v>
@@ -7744,7 +7744,7 @@
         <v>10</v>
       </c>
       <c r="G150">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H150">
         <v>10</v>
@@ -7774,7 +7774,7 @@
         <v>100</v>
       </c>
       <c r="H151">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.4">
@@ -7801,7 +7801,7 @@
         <v>100</v>
       </c>
       <c r="H152">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.4">
@@ -7828,7 +7828,7 @@
         <v>100</v>
       </c>
       <c r="H153">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.4">
@@ -7855,7 +7855,7 @@
         <v>100</v>
       </c>
       <c r="H154">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.4">
@@ -7909,7 +7909,7 @@
         <v>100</v>
       </c>
       <c r="H156">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.4">
@@ -7936,7 +7936,7 @@
         <v>120</v>
       </c>
       <c r="H157">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.4">
@@ -7960,10 +7960,10 @@
         <v>15</v>
       </c>
       <c r="G158">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="H158">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.4">
@@ -7987,10 +7987,10 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H159">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -8014,10 +8014,10 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H160">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -8041,10 +8041,10 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H161">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -8068,10 +8068,10 @@
         <v>15</v>
       </c>
       <c r="G162">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H162">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -8095,10 +8095,10 @@
         <v>15</v>
       </c>
       <c r="G163">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H163">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8122,10 +8122,10 @@
         <v>15</v>
       </c>
       <c r="G164">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H164">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8149,10 +8149,10 @@
         <v>15</v>
       </c>
       <c r="G165">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H165">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8176,10 +8176,10 @@
         <v>15</v>
       </c>
       <c r="G166">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H166">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8203,10 +8203,10 @@
         <v>15</v>
       </c>
       <c r="G167">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="H167">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8230,10 +8230,10 @@
         <v>15</v>
       </c>
       <c r="G168">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="H168">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8257,10 +8257,10 @@
         <v>10</v>
       </c>
       <c r="G169">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H169">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8287,7 +8287,7 @@
         <v>500</v>
       </c>
       <c r="H170">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.4">
@@ -8314,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8341,7 +8341,7 @@
         <v>100</v>
       </c>
       <c r="H172">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.4">
@@ -8368,7 +8368,7 @@
         <v>100</v>
       </c>
       <c r="H173">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.4">
@@ -8395,7 +8395,7 @@
         <v>100</v>
       </c>
       <c r="H174">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.4">
@@ -8422,7 +8422,7 @@
         <v>100</v>
       </c>
       <c r="H175">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8449,7 +8449,7 @@
         <v>100</v>
       </c>
       <c r="H176">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.4">
@@ -8476,7 +8476,7 @@
         <v>100</v>
       </c>
       <c r="H177">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.4">
@@ -8503,7 +8503,7 @@
         <v>100</v>
       </c>
       <c r="H178">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.4">
@@ -8527,10 +8527,10 @@
         <v>20</v>
       </c>
       <c r="G179">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H179">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.4">
@@ -8557,7 +8557,7 @@
         <v>100</v>
       </c>
       <c r="H180">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -8584,7 +8584,7 @@
         <v>170</v>
       </c>
       <c r="H181">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.4">
@@ -8611,7 +8611,7 @@
         <v>200</v>
       </c>
       <c r="H182">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.4">
@@ -8638,7 +8638,7 @@
         <v>150</v>
       </c>
       <c r="H183">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.4">
@@ -8665,7 +8665,7 @@
         <v>150</v>
       </c>
       <c r="H184">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.4">
@@ -8692,7 +8692,7 @@
         <v>150</v>
       </c>
       <c r="H185">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.4">
@@ -8719,7 +8719,7 @@
         <v>200</v>
       </c>
       <c r="H186">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0443F5-36B4-4466-80C6-815F0ED3F9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3D631-E1C3-4EFA-A58E-2A806A9A2D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="900" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7873,7 +7873,7 @@
         <v>301</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155">
         <v>10</v>
@@ -7882,7 +7882,7 @@
         <v>70</v>
       </c>
       <c r="H155">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3D631-E1C3-4EFA-A58E-2A806A9A2D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB61085E-4295-4FC1-9582-94329216FAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="900" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8737,7 +8737,7 @@
         <v>87</v>
       </c>
       <c r="E187">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F187">
         <v>100</v>
@@ -8746,7 +8746,7 @@
         <v>300</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB61085E-4295-4FC1-9582-94329216FAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427E6F0-55FA-4106-A706-94B7F1CD3923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1230" yWindow="870" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7744,7 +7744,7 @@
         <v>10</v>
       </c>
       <c r="G150">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H150">
         <v>10</v>
@@ -7771,7 +7771,7 @@
         <v>10</v>
       </c>
       <c r="G151">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H151">
         <v>20</v>
@@ -7798,7 +7798,7 @@
         <v>10</v>
       </c>
       <c r="G152">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H152">
         <v>30</v>
@@ -7825,7 +7825,7 @@
         <v>10</v>
       </c>
       <c r="G153">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H153">
         <v>20</v>
@@ -7852,7 +7852,7 @@
         <v>10</v>
       </c>
       <c r="G154">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H154">
         <v>30</v>
@@ -7906,7 +7906,7 @@
         <v>15</v>
       </c>
       <c r="G156">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="H156">
         <v>15</v>
@@ -7933,7 +7933,7 @@
         <v>15</v>
       </c>
       <c r="G157">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H157">
         <v>18</v>
@@ -7960,7 +7960,7 @@
         <v>15</v>
       </c>
       <c r="G158">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="H158">
         <v>22</v>
@@ -7987,7 +7987,7 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H159">
         <v>20</v>
@@ -8014,7 +8014,7 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H160">
         <v>20</v>
@@ -8041,7 +8041,7 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H161">
         <v>18</v>
@@ -8068,7 +8068,7 @@
         <v>15</v>
       </c>
       <c r="G162">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H162">
         <v>18</v>
@@ -8095,7 +8095,7 @@
         <v>15</v>
       </c>
       <c r="G163">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H163">
         <v>18</v>
@@ -8122,7 +8122,7 @@
         <v>15</v>
       </c>
       <c r="G164">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="H164">
         <v>18</v>
@@ -8149,7 +8149,7 @@
         <v>15</v>
       </c>
       <c r="G165">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="H165">
         <v>18</v>
@@ -8176,7 +8176,7 @@
         <v>15</v>
       </c>
       <c r="G166">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="H166">
         <v>18</v>
@@ -8203,7 +8203,7 @@
         <v>15</v>
       </c>
       <c r="G167">
-        <v>220</v>
+        <v>370</v>
       </c>
       <c r="H167">
         <v>22</v>
@@ -8230,7 +8230,7 @@
         <v>15</v>
       </c>
       <c r="G168">
-        <v>220</v>
+        <v>370</v>
       </c>
       <c r="H168">
         <v>22</v>
@@ -8257,7 +8257,7 @@
         <v>10</v>
       </c>
       <c r="G169">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="H169">
         <v>16</v>
@@ -8311,7 +8311,7 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H171">
         <v>16</v>
@@ -8338,7 +8338,7 @@
         <v>10</v>
       </c>
       <c r="G172">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H172">
         <v>14</v>
@@ -8365,7 +8365,7 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H173">
         <v>14</v>
@@ -8392,7 +8392,7 @@
         <v>10</v>
       </c>
       <c r="G174">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H174">
         <v>30</v>
@@ -8419,7 +8419,7 @@
         <v>10</v>
       </c>
       <c r="G175">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H175">
         <v>15</v>
@@ -8446,7 +8446,7 @@
         <v>10</v>
       </c>
       <c r="G176">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H176">
         <v>15</v>
@@ -8473,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H177">
         <v>16</v>
@@ -8500,7 +8500,7 @@
         <v>10</v>
       </c>
       <c r="G178">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H178">
         <v>15</v>
@@ -8527,7 +8527,7 @@
         <v>20</v>
       </c>
       <c r="G179">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="H179">
         <v>15</v>
@@ -8554,7 +8554,7 @@
         <v>-10</v>
       </c>
       <c r="G180">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H180">
         <v>15</v>
@@ -8581,7 +8581,7 @@
         <v>15</v>
       </c>
       <c r="G181">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="H181">
         <v>19</v>
@@ -8608,7 +8608,7 @@
         <v>10</v>
       </c>
       <c r="G182">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H182">
         <v>20</v>
@@ -8635,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="H183">
         <v>22</v>
@@ -8662,7 +8662,7 @@
         <v>10</v>
       </c>
       <c r="G184">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="H184">
         <v>22</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G185">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="H185">
         <v>22</v>
@@ -8716,7 +8716,7 @@
         <v>10</v>
       </c>
       <c r="G186">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="H186">
         <v>25</v>
@@ -8743,7 +8743,7 @@
         <v>100</v>
       </c>
       <c r="G187">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="H187">
         <v>100</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427E6F0-55FA-4106-A706-94B7F1CD3923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43465E95-F700-4E74-B17C-86C346A89BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="870" windowWidth="25005" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1215" yWindow="990" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7906,7 +7906,7 @@
         <v>15</v>
       </c>
       <c r="G156">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="H156">
         <v>15</v>
@@ -7933,7 +7933,7 @@
         <v>15</v>
       </c>
       <c r="G157">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H157">
         <v>18</v>
@@ -7960,7 +7960,7 @@
         <v>15</v>
       </c>
       <c r="G158">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="H158">
         <v>22</v>
@@ -7987,7 +7987,7 @@
         <v>15</v>
       </c>
       <c r="G159">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H159">
         <v>20</v>
@@ -8014,7 +8014,7 @@
         <v>15</v>
       </c>
       <c r="G160">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H160">
         <v>20</v>
@@ -8041,7 +8041,7 @@
         <v>15</v>
       </c>
       <c r="G161">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H161">
         <v>18</v>
@@ -8068,7 +8068,7 @@
         <v>15</v>
       </c>
       <c r="G162">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H162">
         <v>18</v>
@@ -8095,7 +8095,7 @@
         <v>15</v>
       </c>
       <c r="G163">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H163">
         <v>18</v>
@@ -8122,7 +8122,7 @@
         <v>15</v>
       </c>
       <c r="G164">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H164">
         <v>18</v>
@@ -8149,7 +8149,7 @@
         <v>15</v>
       </c>
       <c r="G165">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H165">
         <v>18</v>
@@ -8176,7 +8176,7 @@
         <v>15</v>
       </c>
       <c r="G166">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H166">
         <v>18</v>
@@ -8284,7 +8284,7 @@
         <v>10</v>
       </c>
       <c r="G170">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H170">
         <v>30</v>
@@ -8311,7 +8311,7 @@
         <v>10</v>
       </c>
       <c r="G171">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H171">
         <v>16</v>
@@ -8338,7 +8338,7 @@
         <v>10</v>
       </c>
       <c r="G172">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H172">
         <v>14</v>
@@ -8365,7 +8365,7 @@
         <v>10</v>
       </c>
       <c r="G173">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H173">
         <v>14</v>
@@ -8392,7 +8392,7 @@
         <v>10</v>
       </c>
       <c r="G174">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H174">
         <v>30</v>
@@ -8419,7 +8419,7 @@
         <v>10</v>
       </c>
       <c r="G175">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H175">
         <v>15</v>
@@ -8446,7 +8446,7 @@
         <v>10</v>
       </c>
       <c r="G176">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H176">
         <v>15</v>
@@ -8473,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="G177">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H177">
         <v>16</v>
@@ -8500,7 +8500,7 @@
         <v>10</v>
       </c>
       <c r="G178">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H178">
         <v>15</v>
@@ -8527,7 +8527,7 @@
         <v>20</v>
       </c>
       <c r="G179">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="H179">
         <v>15</v>
@@ -8554,7 +8554,7 @@
         <v>-10</v>
       </c>
       <c r="G180">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H180">
         <v>15</v>
@@ -8581,7 +8581,7 @@
         <v>15</v>
       </c>
       <c r="G181">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="H181">
         <v>19</v>
@@ -8608,7 +8608,7 @@
         <v>10</v>
       </c>
       <c r="G182">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H182">
         <v>20</v>
@@ -8635,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="G183">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="H183">
         <v>22</v>
@@ -8662,7 +8662,7 @@
         <v>10</v>
       </c>
       <c r="G184">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="H184">
         <v>22</v>
@@ -8689,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G185">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="H185">
         <v>22</v>
@@ -8716,7 +8716,7 @@
         <v>10</v>
       </c>
       <c r="G186">
-        <v>350</v>
+        <v>170</v>
       </c>
       <c r="H186">
         <v>25</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43465E95-F700-4E74-B17C-86C346A89BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8813E93-8DCF-4BBF-8967-9312A483F15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="990" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2415" yWindow="1050" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G102">
         <v>150</v>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G103">
         <v>150</v>
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G104">
         <v>150</v>
@@ -6526,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="F105">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G105">
         <v>150</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="F106">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G106">
         <v>150</v>
@@ -6580,7 +6580,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G107">
         <v>300</v>
@@ -6607,7 +6607,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G108">
         <v>180</v>
@@ -6634,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G109">
         <v>180</v>
@@ -6661,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G110">
         <v>150</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8813E93-8DCF-4BBF-8967-9312A483F15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4D6626-7525-43EA-A293-17728B2A5B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2415" yWindow="1050" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3045" yWindow="1020" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8611,7 +8611,7 @@
         <v>300</v>
       </c>
       <c r="H182">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4D6626-7525-43EA-A293-17728B2A5B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7349C-8768-4642-8450-9BF3DA6BA4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1020" windowWidth="25005" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7873,7 +7873,7 @@
         <v>301</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155">
         <v>10</v>
@@ -7900,7 +7900,7 @@
         <v>334</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156">
         <v>15</v>

--- a/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_slotNameDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC7349C-8768-4642-8450-9BF3DA6BA4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46BB6563-BF03-4311-90BC-461595C69F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3675" yWindow="1875" windowWidth="21915" windowHeight="13455" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5983,7 +5983,7 @@
         <v>280</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F85">
         <v>7</v>
@@ -7198,7 +7198,7 @@
         <v>341</v>
       </c>
       <c r="E130">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F130">
         <v>10</v>
@@ -7225,7 +7225,7 @@
         <v>442</v>
       </c>
       <c r="E131">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F131">
         <v>10</v>
@@ -7252,7 +7252,7 @@
         <v>346</v>
       </c>
       <c r="E132">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F132">
         <v>10</v>
@@ -7279,7 +7279,7 @@
         <v>443</v>
       </c>
       <c r="E133">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F133">
         <v>10</v>
@@ -7306,7 +7306,7 @@
         <v>445</v>
       </c>
       <c r="E134">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F134">
         <v>10</v>
@@ -7333,7 +7333,7 @@
         <v>444</v>
       </c>
       <c r="E135">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F135">
         <v>10</v>
@@ -7360,7 +7360,7 @@
         <v>355</v>
       </c>
       <c r="E136">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F136">
         <v>10</v>
@@ -7369,7 +7369,7 @@
         <v>150</v>
       </c>
       <c r="H136">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
@@ -7981,7 +7981,7 @@
         <v>314</v>
       </c>
       <c r="E159">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F159">
         <v>15</v>
@@ -7990,7 +7990,7 @@
         <v>180</v>
       </c>
       <c r="H159">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.4">
@@ -8008,7 +8008,7 @@
         <v>328</v>
       </c>
       <c r="E160">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F160">
         <v>15</v>
@@ -8017,7 +8017,7 @@
         <v>180</v>
       </c>
       <c r="H160">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.4">
@@ -8035,7 +8035,7 @@
         <v>330</v>
       </c>
       <c r="E161">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F161">
         <v>15</v>
@@ -8044,7 +8044,7 @@
         <v>180</v>
       </c>
       <c r="H161">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.4">
@@ -8062,7 +8062,7 @@
         <v>517</v>
       </c>
       <c r="E162">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F162">
         <v>15</v>
@@ -8071,7 +8071,7 @@
         <v>180</v>
       </c>
       <c r="H162">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.4">
@@ -8089,7 +8089,7 @@
         <v>520</v>
       </c>
       <c r="E163">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F163">
         <v>15</v>
@@ -8098,7 +8098,7 @@
         <v>180</v>
       </c>
       <c r="H163">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.4">
@@ -8116,7 +8116,7 @@
         <v>335</v>
       </c>
       <c r="E164">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F164">
         <v>15</v>
@@ -8125,7 +8125,7 @@
         <v>200</v>
       </c>
       <c r="H164">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.4">
@@ -8143,7 +8143,7 @@
         <v>338</v>
       </c>
       <c r="E165">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F165">
         <v>15</v>
@@ -8152,7 +8152,7 @@
         <v>200</v>
       </c>
       <c r="H165">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.4">
@@ -8170,7 +8170,7 @@
         <v>501</v>
       </c>
       <c r="E166">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F166">
         <v>15</v>
@@ -8179,7 +8179,7 @@
         <v>200</v>
       </c>
       <c r="H166">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.4">
@@ -8206,7 +8206,7 @@
         <v>370</v>
       </c>
       <c r="H167">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.4">
@@ -8233,7 +8233,7 @@
         <v>370</v>
       </c>
       <c r="H168">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.4">
@@ -8260,7 +8260,7 @@
         <v>170</v>
       </c>
       <c r="H169">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.4">
@@ -8278,7 +8278,7 @@
         <v>438</v>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F170">
         <v>10</v>
@@ -8305,7 +8305,7 @@
         <v>399</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F171">
         <v>10</v>
@@ -8314,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="H171">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.4">
@@ -8332,7 +8332,7 @@
         <v>411</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F172">
         <v>10</v>
@@ -8359,7 +8359,7 @@
         <v>404</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F173">
         <v>10</v>
@@ -8386,7 +8386,7 @@
         <v>407</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F174">
         <v>10</v>
@@ -8413,7 +8413,7 @@
         <v>410</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F175">
         <v>10</v>
@@ -8422,7 +8422,7 @@
         <v>100</v>
       </c>
       <c r="H175">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.4">
@@ -8440,7 +8440,7 @@
         <v>413</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F176">
         <v>10</v>
@@ -8467,7 +8467,7 @@
         <v>417</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F177">
         <v>10</v>
@@ -8494,7 +8494,7 @@
         <v>420</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F178">
         <v>10</v>
@@ -8521,7 +8521,7 @@
         <v>423</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F179">
         <v>20</v>
@@ -8548,7 +8548,7 @@
         <v>426</v>
       </c>
       <c r="E180">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="F180">
         <v>-10</v>
@@ -8557,7 +8557,7 @@
         <v>110</v>
       </c>
       <c r="H180">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.4">
@@ -8575,7 +8575,7 @@
         <v>435</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F181">
         <v>15</v>
@@ -8629,13 +8629,13 @@
         <v>483</v>
       </c>
       <c r="E183">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F183">
         <v>10</v>
       </c>
       <c r="G183">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="H183">
         <v>22</v>
@@ -8656,13 +8656,13 @@
         <v>486</v>
       </c>
       <c r="E184">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F184">
         <v>10</v>
       </c>
       <c r="G184">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="H184">
         <v>22</v>
@@ -8683,13 +8683,13 @@
         <v>489</v>
       </c>
       <c r="E185">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F185">
         <v>10</v>
       </c>
       <c r="G185">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="H185">
         <v>22</v>
@@ -8710,13 +8710,13 @@
         <v>492</v>
       </c>
       <c r="E186">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F186">
         <v>10</v>
       </c>
       <c r="G186">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="H186">
         <v>25</v>
